--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="75">
   <si>
     <t>id_match</t>
   </si>
@@ -199,14 +199,72 @@
   </si>
   <si>
     <t>platense</t>
+  </si>
+  <si>
+    <t>l2pqAyGf</t>
+  </si>
+  <si>
+    <t>sheffield wed</t>
+  </si>
+  <si>
+    <t>norwich</t>
+  </si>
+  <si>
+    <t>Championship</t>
+  </si>
+  <si>
+    <t>3.30</t>
+  </si>
+  <si>
+    <t>2.20</t>
+  </si>
+  <si>
+    <t>dif_prob_mod_bm &gt; -0.1</t>
+  </si>
+  <si>
+    <t>25lm9eV0</t>
+  </si>
+  <si>
+    <t>southampton</t>
+  </si>
+  <si>
+    <t>coventry</t>
+  </si>
+  <si>
+    <t>1.70</t>
+  </si>
+  <si>
+    <t>4.20</t>
+  </si>
+  <si>
+    <t>4.33</t>
+  </si>
+  <si>
+    <t>YTrCHJNK</t>
+  </si>
+  <si>
+    <t>leeds</t>
+  </si>
+  <si>
+    <t>sunderland</t>
+  </si>
+  <si>
+    <t>1.33</t>
+  </si>
+  <si>
+    <t>5.00</t>
+  </si>
+  <si>
+    <t>9.50</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -236,7 +294,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,6 +527,72 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE1F3EA"/>
         <bgColor rgb="FFE1F3EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFECDD"/>
+        <bgColor rgb="FFCFECDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D9BE"/>
+        <bgColor rgb="FFA1D9BE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF3E9"/>
+        <bgColor rgb="FFDFF3E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD9BC"/>
+        <bgColor rgb="FF9FD9BC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9F0E5"/>
+        <bgColor rgb="FFD9F0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor rgb="FFFCFEFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CEAA"/>
+        <bgColor rgb="FF85CEAA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F5"/>
+        <bgColor rgb="FFF0F9F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D3B3"/>
+        <bgColor rgb="FF91D3B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6F0"/>
+        <bgColor rgb="FFE9F6F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0E5"/>
+        <bgColor rgb="FFDAF0E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -510,7 +634,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="81">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -666,6 +790,93 @@
     </xf>
     <xf borderId="3" fillId="39" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="40" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="13" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="18" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="27" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="41" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="42" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="43" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="44" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="19" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="41" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="27" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="18" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="45" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="46" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="15" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="47" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="48" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="49" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="50" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1433,6 +1644,215 @@
         <v>28</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="53">
+        <v>45391.65625</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="54">
+        <v>0.29</v>
+      </c>
+      <c r="K9" s="54">
+        <v>0.29</v>
+      </c>
+      <c r="L9" s="55">
+        <v>0.43</v>
+      </c>
+      <c r="M9" s="56">
+        <v>0.0606</v>
+      </c>
+      <c r="N9" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="O9" s="57">
+        <v>0.18</v>
+      </c>
+      <c r="P9" s="58">
+        <v>0.27</v>
+      </c>
+      <c r="Q9" s="59">
+        <v>0.55</v>
+      </c>
+      <c r="R9" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="S9" s="60">
+        <v>0.12329812</v>
+      </c>
+      <c r="T9" s="52">
+        <v>0.551869548</v>
+      </c>
+      <c r="U9" s="52">
+        <v>2.2</v>
+      </c>
+      <c r="V9" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="W9" s="62"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="64">
+        <v>45391.65625</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" s="65">
+        <v>0.56</v>
+      </c>
+      <c r="K10" s="66">
+        <v>0.23</v>
+      </c>
+      <c r="L10" s="67">
+        <v>0.22</v>
+      </c>
+      <c r="M10" s="68">
+        <v>0.0573</v>
+      </c>
+      <c r="N10" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O10" s="69">
+        <v>0.55</v>
+      </c>
+      <c r="P10" s="70">
+        <v>0.27</v>
+      </c>
+      <c r="Q10" s="71">
+        <v>0.18</v>
+      </c>
+      <c r="R10" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="S10" s="72">
+        <v>-0.004713291</v>
+      </c>
+      <c r="T10" s="63">
+        <v>0.551654684</v>
+      </c>
+      <c r="U10" s="63">
+        <v>1.7</v>
+      </c>
+      <c r="V10" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="W10" s="74">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="64">
+        <v>45391.666666666664</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="75">
+        <v>0.71</v>
+      </c>
+      <c r="K11" s="76">
+        <v>0.19</v>
+      </c>
+      <c r="L11" s="77">
+        <v>0.1</v>
+      </c>
+      <c r="M11" s="68">
+        <v>0.0571</v>
+      </c>
+      <c r="N11" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O11" s="78">
+        <v>0.64</v>
+      </c>
+      <c r="P11" s="67">
+        <v>0.22</v>
+      </c>
+      <c r="Q11" s="79">
+        <v>0.14</v>
+      </c>
+      <c r="R11" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="S11" s="80">
+        <v>-0.07574779</v>
+      </c>
+      <c r="T11" s="63">
+        <v>0.635489763</v>
+      </c>
+      <c r="U11" s="63">
+        <v>1.33</v>
+      </c>
+      <c r="V11" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="W11" s="62"/>
+    </row>
   </sheetData>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="98">
   <si>
     <t>id_match</t>
   </si>
@@ -256,6 +256,75 @@
   </si>
   <si>
     <t>9.50</t>
+  </si>
+  <si>
+    <t>bX3RMEa0</t>
+  </si>
+  <si>
+    <t>blackburn</t>
+  </si>
+  <si>
+    <t>dif_prob_mod_bm &lt; 0.0</t>
+  </si>
+  <si>
+    <t>6km0uBnR</t>
+  </si>
+  <si>
+    <t>tottenham</t>
+  </si>
+  <si>
+    <t>dif_prob_mod_bm &gt; -0.05</t>
+  </si>
+  <si>
+    <t>YkKnUd7Q</t>
+  </si>
+  <si>
+    <t>birmingham</t>
+  </si>
+  <si>
+    <t>8rBEPGFs</t>
+  </si>
+  <si>
+    <t>bristol city</t>
+  </si>
+  <si>
+    <t>huddersfield</t>
+  </si>
+  <si>
+    <t>IT65JTP7</t>
+  </si>
+  <si>
+    <t>burnley</t>
+  </si>
+  <si>
+    <t>brighton</t>
+  </si>
+  <si>
+    <t>SbldtiXK</t>
+  </si>
+  <si>
+    <t>manchester city</t>
+  </si>
+  <si>
+    <t>luton</t>
+  </si>
+  <si>
+    <t>dU6KzVfr</t>
+  </si>
+  <si>
+    <t>nottingham</t>
+  </si>
+  <si>
+    <t>wolves</t>
+  </si>
+  <si>
+    <t>WC4gMVuk</t>
+  </si>
+  <si>
+    <t>bournemouth</t>
+  </si>
+  <si>
+    <t>manchester utd</t>
   </si>
 </sst>
 </file>
@@ -294,7 +363,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="51">
+  <fills count="66">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,6 +662,96 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDAF0E5"/>
         <bgColor rgb="FFDAF0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8AD0AE"/>
+        <bgColor rgb="FF8AD0AE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF1E7"/>
+        <bgColor rgb="FFDCF1E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E1CB"/>
+        <bgColor rgb="FFB4E1CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7D6"/>
+        <bgColor rgb="FFC4E7D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2CE"/>
+        <bgColor rgb="FFB8E2CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EEE1"/>
+        <bgColor rgb="FFD4EEE1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDDC5"/>
+        <bgColor rgb="FFABDDC5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF8F3"/>
+        <bgColor rgb="FFEDF8F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC398"/>
+        <bgColor rgb="FF6BC398"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1FAF6"/>
+        <bgColor rgb="FFF1FAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FDFB"/>
+        <bgColor rgb="FFF8FDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C69D"/>
+        <bgColor rgb="FF72C69D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EE"/>
+        <bgColor rgb="FFE8F5EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor rgb="FFFBFDFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -634,7 +793,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="117">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -876,6 +1035,114 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="50" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="46" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="15" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="47" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="51" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="19" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="34" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="13" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="52" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="53" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="54" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="21" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="29" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="32" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="55" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="56" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="37" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="57" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="40" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="58" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="59" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="22" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="36" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="21" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="55" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="56" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="60" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="61" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="62" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="63" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="64" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="16" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="38" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="65" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1161,6 +1428,8 @@
       <c r="W1" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
@@ -1300,6 +1569,8 @@
       <c r="W3" s="10">
         <v>1.0</v>
       </c>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
@@ -1439,6 +1710,8 @@
       <c r="W5" s="10">
         <v>1.0</v>
       </c>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="s">
@@ -1712,6 +1985,8 @@
         <v>62</v>
       </c>
       <c r="W9" s="62"/>
+      <c r="X9" s="62"/>
+      <c r="Y9" s="62"/>
     </row>
     <row r="10">
       <c r="A10" s="63" t="s">
@@ -1783,6 +2058,8 @@
       <c r="W10" s="74">
         <v>1.0</v>
       </c>
+      <c r="X10" s="74"/>
+      <c r="Y10" s="74"/>
     </row>
     <row r="11">
       <c r="A11" s="63" t="s">
@@ -1852,6 +2129,552 @@
         <v>62</v>
       </c>
       <c r="W11" s="62"/>
+      <c r="X11" s="62"/>
+      <c r="Y11" s="62"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="53">
+        <v>45395.354166666664</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="52">
+        <v>1.33</v>
+      </c>
+      <c r="H12" s="52">
+        <v>5.0</v>
+      </c>
+      <c r="I12" s="52">
+        <v>10.0</v>
+      </c>
+      <c r="J12" s="81">
+        <v>0.71</v>
+      </c>
+      <c r="K12" s="82">
+        <v>0.19</v>
+      </c>
+      <c r="L12" s="83">
+        <v>0.1</v>
+      </c>
+      <c r="M12" s="56">
+        <v>0.052</v>
+      </c>
+      <c r="N12" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="O12" s="84">
+        <v>0.68</v>
+      </c>
+      <c r="P12" s="85">
+        <v>0.22</v>
+      </c>
+      <c r="Q12" s="83">
+        <v>0.1</v>
+      </c>
+      <c r="R12" s="52">
+        <v>-1.0</v>
+      </c>
+      <c r="S12" s="86">
+        <v>0.04</v>
+      </c>
+      <c r="T12" s="52">
+        <v>0.32</v>
+      </c>
+      <c r="U12" s="52">
+        <v>3.33</v>
+      </c>
+      <c r="V12" s="61" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="64">
+        <v>45395.354166666664</v>
+      </c>
+      <c r="C13" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="63">
+        <v>2.8</v>
+      </c>
+      <c r="H13" s="63">
+        <v>4.0</v>
+      </c>
+      <c r="I13" s="63">
+        <v>2.2</v>
+      </c>
+      <c r="J13" s="87">
+        <v>0.34</v>
+      </c>
+      <c r="K13" s="88">
+        <v>0.24</v>
+      </c>
+      <c r="L13" s="89">
+        <v>0.43</v>
+      </c>
+      <c r="M13" s="68">
+        <v>0.061688312</v>
+      </c>
+      <c r="N13" s="63">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="90">
+        <v>0.21</v>
+      </c>
+      <c r="P13" s="91">
+        <v>0.44</v>
+      </c>
+      <c r="Q13" s="92">
+        <v>0.35</v>
+      </c>
+      <c r="R13" s="63">
+        <v>0.0</v>
+      </c>
+      <c r="S13" s="93">
+        <v>0.207871625</v>
+      </c>
+      <c r="T13" s="63">
+        <v>0.443345631</v>
+      </c>
+      <c r="U13" s="63">
+        <v>4.0</v>
+      </c>
+      <c r="V13" s="73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="64">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="63">
+        <v>3.1</v>
+      </c>
+      <c r="H14" s="63">
+        <v>3.4</v>
+      </c>
+      <c r="I14" s="63">
+        <v>2.25</v>
+      </c>
+      <c r="J14" s="94">
+        <v>0.3</v>
+      </c>
+      <c r="K14" s="95">
+        <v>0.28</v>
+      </c>
+      <c r="L14" s="96">
+        <v>0.42</v>
+      </c>
+      <c r="M14" s="68">
+        <v>0.061</v>
+      </c>
+      <c r="N14" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="O14" s="93">
+        <v>0.32</v>
+      </c>
+      <c r="P14" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="Q14" s="98">
+        <v>0.41</v>
+      </c>
+      <c r="R14" s="63">
+        <v>-2.0</v>
+      </c>
+      <c r="S14" s="99">
+        <v>0.0</v>
+      </c>
+      <c r="T14" s="63">
+        <v>0.59</v>
+      </c>
+      <c r="U14" s="63">
+        <v>1.62</v>
+      </c>
+      <c r="V14" s="73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="64">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="63">
+        <v>2.3</v>
+      </c>
+      <c r="H15" s="63">
+        <v>3.2</v>
+      </c>
+      <c r="I15" s="63">
+        <v>3.3</v>
+      </c>
+      <c r="J15" s="98">
+        <v>0.41</v>
+      </c>
+      <c r="K15" s="94">
+        <v>0.3</v>
+      </c>
+      <c r="L15" s="100">
+        <v>0.29</v>
+      </c>
+      <c r="M15" s="68">
+        <v>0.05</v>
+      </c>
+      <c r="N15" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O15" s="101">
+        <v>0.49</v>
+      </c>
+      <c r="P15" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="Q15" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="R15" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="S15" s="102">
+        <v>0.07</v>
+      </c>
+      <c r="T15" s="63">
+        <v>0.49</v>
+      </c>
+      <c r="U15" s="63">
+        <v>2.3</v>
+      </c>
+      <c r="V15" s="73" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="53">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="52">
+        <v>3.5</v>
+      </c>
+      <c r="H16" s="52">
+        <v>3.75</v>
+      </c>
+      <c r="I16" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="J16" s="58">
+        <v>0.27</v>
+      </c>
+      <c r="K16" s="103">
+        <v>0.25</v>
+      </c>
+      <c r="L16" s="104">
+        <v>0.48</v>
+      </c>
+      <c r="M16" s="56">
+        <v>0.052380952</v>
+      </c>
+      <c r="N16" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="105">
+        <v>0.32</v>
+      </c>
+      <c r="P16" s="106">
+        <v>0.42</v>
+      </c>
+      <c r="Q16" s="107">
+        <v>0.26</v>
+      </c>
+      <c r="R16" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="S16" s="103">
+        <v>0.162065436</v>
+      </c>
+      <c r="T16" s="52">
+        <v>0.415459101</v>
+      </c>
+      <c r="U16" s="52">
+        <v>3.75</v>
+      </c>
+      <c r="V16" s="61" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="64">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="63">
+        <v>1.1</v>
+      </c>
+      <c r="H17" s="63">
+        <v>11.0</v>
+      </c>
+      <c r="I17" s="63">
+        <v>19.0</v>
+      </c>
+      <c r="J17" s="108">
+        <v>0.86</v>
+      </c>
+      <c r="K17" s="109">
+        <v>0.09</v>
+      </c>
+      <c r="L17" s="110">
+        <v>0.05</v>
+      </c>
+      <c r="M17" s="68">
+        <v>0.052631579</v>
+      </c>
+      <c r="N17" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O17" s="111">
+        <v>0.82</v>
+      </c>
+      <c r="P17" s="112">
+        <v>0.17</v>
+      </c>
+      <c r="Q17" s="99">
+        <v>0.01</v>
+      </c>
+      <c r="R17" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="S17" s="113">
+        <v>-0.047609234</v>
+      </c>
+      <c r="T17" s="63">
+        <v>0.81602713</v>
+      </c>
+      <c r="U17" s="63">
+        <v>1.1</v>
+      </c>
+      <c r="V17" s="73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="64">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="63">
+        <v>2.1</v>
+      </c>
+      <c r="H18" s="63">
+        <v>3.4</v>
+      </c>
+      <c r="I18" s="63">
+        <v>3.5</v>
+      </c>
+      <c r="J18" s="114">
+        <v>0.45</v>
+      </c>
+      <c r="K18" s="95">
+        <v>0.28</v>
+      </c>
+      <c r="L18" s="70">
+        <v>0.27</v>
+      </c>
+      <c r="M18" s="68">
+        <v>0.056022409</v>
+      </c>
+      <c r="N18" s="63">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="87">
+        <v>0.34</v>
+      </c>
+      <c r="P18" s="91">
+        <v>0.44</v>
+      </c>
+      <c r="Q18" s="67">
+        <v>0.22</v>
+      </c>
+      <c r="R18" s="63">
+        <v>0.0</v>
+      </c>
+      <c r="S18" s="97">
+        <v>0.16603443</v>
+      </c>
+      <c r="T18" s="63">
+        <v>0.444549019</v>
+      </c>
+      <c r="U18" s="63">
+        <v>3.4</v>
+      </c>
+      <c r="V18" s="73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="63" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="64">
+        <v>45395.5625</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="63">
+        <v>2.3</v>
+      </c>
+      <c r="H19" s="63">
+        <v>4.0</v>
+      </c>
+      <c r="I19" s="63">
+        <v>2.7</v>
+      </c>
+      <c r="J19" s="98">
+        <v>0.41</v>
+      </c>
+      <c r="K19" s="88">
+        <v>0.24</v>
+      </c>
+      <c r="L19" s="92">
+        <v>0.35</v>
+      </c>
+      <c r="M19" s="68">
+        <v>0.055152979</v>
+      </c>
+      <c r="N19" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="O19" s="95">
+        <v>0.28</v>
+      </c>
+      <c r="P19" s="92">
+        <v>0.35</v>
+      </c>
+      <c r="Q19" s="115">
+        <v>0.37</v>
+      </c>
+      <c r="R19" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="S19" s="116">
+        <v>0.019080418</v>
+      </c>
+      <c r="T19" s="63">
+        <v>0.370091483</v>
+      </c>
+      <c r="U19" s="63">
+        <v>2.7</v>
+      </c>
+      <c r="V19" s="73" t="s">
+        <v>80</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId2"/>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="86">
   <si>
     <t>id_match</t>
   </si>
@@ -289,42 +289,6 @@
   </si>
   <si>
     <t>huddersfield</t>
-  </si>
-  <si>
-    <t>IT65JTP7</t>
-  </si>
-  <si>
-    <t>burnley</t>
-  </si>
-  <si>
-    <t>brighton</t>
-  </si>
-  <si>
-    <t>SbldtiXK</t>
-  </si>
-  <si>
-    <t>manchester city</t>
-  </si>
-  <si>
-    <t>luton</t>
-  </si>
-  <si>
-    <t>dU6KzVfr</t>
-  </si>
-  <si>
-    <t>nottingham</t>
-  </si>
-  <si>
-    <t>wolves</t>
-  </si>
-  <si>
-    <t>WC4gMVuk</t>
-  </si>
-  <si>
-    <t>bournemouth</t>
-  </si>
-  <si>
-    <t>manchester utd</t>
   </si>
 </sst>
 </file>
@@ -363,7 +327,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="66">
+  <fills count="60">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -716,42 +680,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF8F3"/>
         <bgColor rgb="FFEDF8F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC398"/>
-        <bgColor rgb="FF6BC398"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1FAF6"/>
-        <bgColor rgb="FFF1FAF6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FDFB"/>
-        <bgColor rgb="FFF8FDFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C69D"/>
-        <bgColor rgb="FF72C69D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EE"/>
-        <bgColor rgb="FFE8F5EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor rgb="FFFBFDFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -793,7 +721,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="103">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1101,48 +1029,6 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="59" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="22" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="36" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="21" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="55" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="56" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="60" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="61" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="62" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="63" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="64" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="16" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="38" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="65" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2404,278 +2290,6 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="53">
-        <v>45395.458333333336</v>
-      </c>
-      <c r="C16" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="52">
-        <v>3.5</v>
-      </c>
-      <c r="H16" s="52">
-        <v>3.75</v>
-      </c>
-      <c r="I16" s="52">
-        <v>2.0</v>
-      </c>
-      <c r="J16" s="58">
-        <v>0.27</v>
-      </c>
-      <c r="K16" s="103">
-        <v>0.25</v>
-      </c>
-      <c r="L16" s="104">
-        <v>0.48</v>
-      </c>
-      <c r="M16" s="56">
-        <v>0.052380952</v>
-      </c>
-      <c r="N16" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="105">
-        <v>0.32</v>
-      </c>
-      <c r="P16" s="106">
-        <v>0.42</v>
-      </c>
-      <c r="Q16" s="107">
-        <v>0.26</v>
-      </c>
-      <c r="R16" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="S16" s="103">
-        <v>0.162065436</v>
-      </c>
-      <c r="T16" s="52">
-        <v>0.415459101</v>
-      </c>
-      <c r="U16" s="52">
-        <v>3.75</v>
-      </c>
-      <c r="V16" s="61" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="64">
-        <v>45395.458333333336</v>
-      </c>
-      <c r="C17" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="63" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="63">
-        <v>1.1</v>
-      </c>
-      <c r="H17" s="63">
-        <v>11.0</v>
-      </c>
-      <c r="I17" s="63">
-        <v>19.0</v>
-      </c>
-      <c r="J17" s="108">
-        <v>0.86</v>
-      </c>
-      <c r="K17" s="109">
-        <v>0.09</v>
-      </c>
-      <c r="L17" s="110">
-        <v>0.05</v>
-      </c>
-      <c r="M17" s="68">
-        <v>0.052631579</v>
-      </c>
-      <c r="N17" s="63">
-        <v>1.0</v>
-      </c>
-      <c r="O17" s="111">
-        <v>0.82</v>
-      </c>
-      <c r="P17" s="112">
-        <v>0.17</v>
-      </c>
-      <c r="Q17" s="99">
-        <v>0.01</v>
-      </c>
-      <c r="R17" s="63">
-        <v>1.0</v>
-      </c>
-      <c r="S17" s="113">
-        <v>-0.047609234</v>
-      </c>
-      <c r="T17" s="63">
-        <v>0.81602713</v>
-      </c>
-      <c r="U17" s="63">
-        <v>1.1</v>
-      </c>
-      <c r="V17" s="73" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="63" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="64">
-        <v>45395.458333333336</v>
-      </c>
-      <c r="C18" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="63">
-        <v>2.1</v>
-      </c>
-      <c r="H18" s="63">
-        <v>3.4</v>
-      </c>
-      <c r="I18" s="63">
-        <v>3.5</v>
-      </c>
-      <c r="J18" s="114">
-        <v>0.45</v>
-      </c>
-      <c r="K18" s="95">
-        <v>0.28</v>
-      </c>
-      <c r="L18" s="70">
-        <v>0.27</v>
-      </c>
-      <c r="M18" s="68">
-        <v>0.056022409</v>
-      </c>
-      <c r="N18" s="63">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="87">
-        <v>0.34</v>
-      </c>
-      <c r="P18" s="91">
-        <v>0.44</v>
-      </c>
-      <c r="Q18" s="67">
-        <v>0.22</v>
-      </c>
-      <c r="R18" s="63">
-        <v>0.0</v>
-      </c>
-      <c r="S18" s="97">
-        <v>0.16603443</v>
-      </c>
-      <c r="T18" s="63">
-        <v>0.444549019</v>
-      </c>
-      <c r="U18" s="63">
-        <v>3.4</v>
-      </c>
-      <c r="V18" s="73" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="63" t="s">
-        <v>95</v>
-      </c>
-      <c r="B19" s="64">
-        <v>45395.5625</v>
-      </c>
-      <c r="C19" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="63">
-        <v>2.3</v>
-      </c>
-      <c r="H19" s="63">
-        <v>4.0</v>
-      </c>
-      <c r="I19" s="63">
-        <v>2.7</v>
-      </c>
-      <c r="J19" s="98">
-        <v>0.41</v>
-      </c>
-      <c r="K19" s="88">
-        <v>0.24</v>
-      </c>
-      <c r="L19" s="92">
-        <v>0.35</v>
-      </c>
-      <c r="M19" s="68">
-        <v>0.055152979</v>
-      </c>
-      <c r="N19" s="63">
-        <v>2.0</v>
-      </c>
-      <c r="O19" s="95">
-        <v>0.28</v>
-      </c>
-      <c r="P19" s="92">
-        <v>0.35</v>
-      </c>
-      <c r="Q19" s="115">
-        <v>0.37</v>
-      </c>
-      <c r="R19" s="63">
-        <v>2.0</v>
-      </c>
-      <c r="S19" s="116">
-        <v>0.019080418</v>
-      </c>
-      <c r="T19" s="63">
-        <v>0.370091483</v>
-      </c>
-      <c r="U19" s="63">
-        <v>2.7</v>
-      </c>
-      <c r="V19" s="73" t="s">
-        <v>80</v>
-      </c>
-    </row>
   </sheetData>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="98">
   <si>
     <t>id_match</t>
   </si>
@@ -289,6 +289,42 @@
   </si>
   <si>
     <t>huddersfield</t>
+  </si>
+  <si>
+    <t>IT65JTP7</t>
+  </si>
+  <si>
+    <t>burnley</t>
+  </si>
+  <si>
+    <t>brighton</t>
+  </si>
+  <si>
+    <t>SbldtiXK</t>
+  </si>
+  <si>
+    <t>manchester city</t>
+  </si>
+  <si>
+    <t>luton</t>
+  </si>
+  <si>
+    <t>dU6KzVfr</t>
+  </si>
+  <si>
+    <t>nottingham</t>
+  </si>
+  <si>
+    <t>wolves</t>
+  </si>
+  <si>
+    <t>WC4gMVuk</t>
+  </si>
+  <si>
+    <t>bournemouth</t>
+  </si>
+  <si>
+    <t>manchester utd</t>
   </si>
 </sst>
 </file>
@@ -327,7 +363,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="60">
+  <fills count="66">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,6 +716,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF8F3"/>
         <bgColor rgb="FFEDF8F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC398"/>
+        <bgColor rgb="FF6BC398"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1FAF6"/>
+        <bgColor rgb="FFF1FAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FDFB"/>
+        <bgColor rgb="FFF8FDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C69D"/>
+        <bgColor rgb="FF72C69D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EE"/>
+        <bgColor rgb="FFE8F5EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor rgb="FFFBFDFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -721,7 +793,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="117">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1029,6 +1101,48 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="59" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="22" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="36" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="21" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="55" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="56" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="60" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="61" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="62" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="63" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="64" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="16" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="38" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="65" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2290,6 +2404,278 @@
         <v>38</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="53">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="52">
+        <v>3.5</v>
+      </c>
+      <c r="H16" s="52">
+        <v>3.75</v>
+      </c>
+      <c r="I16" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="J16" s="58">
+        <v>0.27</v>
+      </c>
+      <c r="K16" s="103">
+        <v>0.25</v>
+      </c>
+      <c r="L16" s="104">
+        <v>0.48</v>
+      </c>
+      <c r="M16" s="56">
+        <v>0.052380952</v>
+      </c>
+      <c r="N16" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="105">
+        <v>0.32</v>
+      </c>
+      <c r="P16" s="106">
+        <v>0.42</v>
+      </c>
+      <c r="Q16" s="107">
+        <v>0.26</v>
+      </c>
+      <c r="R16" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="S16" s="103">
+        <v>0.162065436</v>
+      </c>
+      <c r="T16" s="52">
+        <v>0.415459101</v>
+      </c>
+      <c r="U16" s="52">
+        <v>3.75</v>
+      </c>
+      <c r="V16" s="61" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="64">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="63">
+        <v>1.1</v>
+      </c>
+      <c r="H17" s="63">
+        <v>11.0</v>
+      </c>
+      <c r="I17" s="63">
+        <v>19.0</v>
+      </c>
+      <c r="J17" s="108">
+        <v>0.86</v>
+      </c>
+      <c r="K17" s="109">
+        <v>0.09</v>
+      </c>
+      <c r="L17" s="110">
+        <v>0.05</v>
+      </c>
+      <c r="M17" s="68">
+        <v>0.052631579</v>
+      </c>
+      <c r="N17" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O17" s="111">
+        <v>0.82</v>
+      </c>
+      <c r="P17" s="112">
+        <v>0.17</v>
+      </c>
+      <c r="Q17" s="99">
+        <v>0.01</v>
+      </c>
+      <c r="R17" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="S17" s="113">
+        <v>-0.047609234</v>
+      </c>
+      <c r="T17" s="63">
+        <v>0.81602713</v>
+      </c>
+      <c r="U17" s="63">
+        <v>1.1</v>
+      </c>
+      <c r="V17" s="73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="64">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="63">
+        <v>2.1</v>
+      </c>
+      <c r="H18" s="63">
+        <v>3.4</v>
+      </c>
+      <c r="I18" s="63">
+        <v>3.5</v>
+      </c>
+      <c r="J18" s="114">
+        <v>0.45</v>
+      </c>
+      <c r="K18" s="95">
+        <v>0.28</v>
+      </c>
+      <c r="L18" s="70">
+        <v>0.27</v>
+      </c>
+      <c r="M18" s="68">
+        <v>0.056022409</v>
+      </c>
+      <c r="N18" s="63">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="87">
+        <v>0.34</v>
+      </c>
+      <c r="P18" s="91">
+        <v>0.44</v>
+      </c>
+      <c r="Q18" s="67">
+        <v>0.22</v>
+      </c>
+      <c r="R18" s="63">
+        <v>0.0</v>
+      </c>
+      <c r="S18" s="97">
+        <v>0.16603443</v>
+      </c>
+      <c r="T18" s="63">
+        <v>0.444549019</v>
+      </c>
+      <c r="U18" s="63">
+        <v>3.4</v>
+      </c>
+      <c r="V18" s="73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="63" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="64">
+        <v>45395.5625</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="63">
+        <v>2.3</v>
+      </c>
+      <c r="H19" s="63">
+        <v>4.0</v>
+      </c>
+      <c r="I19" s="63">
+        <v>2.7</v>
+      </c>
+      <c r="J19" s="98">
+        <v>0.41</v>
+      </c>
+      <c r="K19" s="88">
+        <v>0.24</v>
+      </c>
+      <c r="L19" s="92">
+        <v>0.35</v>
+      </c>
+      <c r="M19" s="68">
+        <v>0.055152979</v>
+      </c>
+      <c r="N19" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="O19" s="95">
+        <v>0.28</v>
+      </c>
+      <c r="P19" s="92">
+        <v>0.35</v>
+      </c>
+      <c r="Q19" s="115">
+        <v>0.37</v>
+      </c>
+      <c r="R19" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="S19" s="116">
+        <v>0.019080418</v>
+      </c>
+      <c r="T19" s="63">
+        <v>0.370091483</v>
+      </c>
+      <c r="U19" s="63">
+        <v>2.7</v>
+      </c>
+      <c r="V19" s="73" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="108">
   <si>
     <t>id_match</t>
   </si>
@@ -289,6 +289,72 @@
   </si>
   <si>
     <t>huddersfield</t>
+  </si>
+  <si>
+    <t>IT65JTP7</t>
+  </si>
+  <si>
+    <t>burnley</t>
+  </si>
+  <si>
+    <t>brighton</t>
+  </si>
+  <si>
+    <t>SbldtiXK</t>
+  </si>
+  <si>
+    <t>manchester city</t>
+  </si>
+  <si>
+    <t>luton</t>
+  </si>
+  <si>
+    <t>dU6KzVfr</t>
+  </si>
+  <si>
+    <t>nottingham</t>
+  </si>
+  <si>
+    <t>wolves</t>
+  </si>
+  <si>
+    <t>WC4gMVuk</t>
+  </si>
+  <si>
+    <t>bournemouth</t>
+  </si>
+  <si>
+    <t>manchester utd</t>
+  </si>
+  <si>
+    <t>beWNelr3</t>
+  </si>
+  <si>
+    <t>lazio</t>
+  </si>
+  <si>
+    <t>dif_prob_mod_bm &lt; 0.1</t>
+  </si>
+  <si>
+    <t>t2MJmVwO</t>
+  </si>
+  <si>
+    <t>ath bilbao</t>
+  </si>
+  <si>
+    <t>vmuNnkgU</t>
+  </si>
+  <si>
+    <t>atl madrid</t>
+  </si>
+  <si>
+    <t>osasuna</t>
+  </si>
+  <si>
+    <t>4A6T7YOu</t>
+  </si>
+  <si>
+    <t>rayo vallecano</t>
   </si>
 </sst>
 </file>
@@ -327,7 +393,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="60">
+  <fills count="75">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,6 +746,96 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF8F3"/>
         <bgColor rgb="FFEDF8F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC398"/>
+        <bgColor rgb="FF6BC398"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1FAF6"/>
+        <bgColor rgb="FFF1FAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FDFB"/>
+        <bgColor rgb="FFF8FDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C69D"/>
+        <bgColor rgb="FF72C69D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EE"/>
+        <bgColor rgb="FFE8F5EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor rgb="FFFBFDFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED8BB"/>
+        <bgColor rgb="FF9ED8BB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F6EE"/>
+        <bgColor rgb="FFE7F6EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FBF8"/>
+        <bgColor rgb="FFF4FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD7BA"/>
+        <bgColor rgb="FF9CD7BA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CFAD"/>
+        <bgColor rgb="FF89CFAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7F2"/>
+        <bgColor rgb="FFECF7F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECBA5"/>
+        <bgColor rgb="FF7ECBA5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CCA7"/>
+        <bgColor rgb="FF80CCA7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FDFB"/>
+        <bgColor rgb="FFF9FDFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -721,7 +877,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="135">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1029,6 +1185,102 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="59" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="22" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="36" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="21" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="55" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="56" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="60" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="61" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="62" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="63" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="64" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="16" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="38" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="65" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="66" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="44" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="31" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="67" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="68" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="69" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="36" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="70" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="51" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="71" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="72" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="73" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="35" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="74" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2290,6 +2542,553 @@
         <v>38</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="53">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="52">
+        <v>3.5</v>
+      </c>
+      <c r="H16" s="52">
+        <v>3.75</v>
+      </c>
+      <c r="I16" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="J16" s="58">
+        <v>0.27</v>
+      </c>
+      <c r="K16" s="103">
+        <v>0.25</v>
+      </c>
+      <c r="L16" s="104">
+        <v>0.48</v>
+      </c>
+      <c r="M16" s="56">
+        <v>0.052380952</v>
+      </c>
+      <c r="N16" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="105">
+        <v>0.32</v>
+      </c>
+      <c r="P16" s="106">
+        <v>0.42</v>
+      </c>
+      <c r="Q16" s="107">
+        <v>0.26</v>
+      </c>
+      <c r="R16" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="S16" s="103">
+        <v>0.162065436</v>
+      </c>
+      <c r="T16" s="52">
+        <v>0.415459101</v>
+      </c>
+      <c r="U16" s="52">
+        <v>3.75</v>
+      </c>
+      <c r="V16" s="61" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="64">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="63">
+        <v>1.1</v>
+      </c>
+      <c r="H17" s="63">
+        <v>11.0</v>
+      </c>
+      <c r="I17" s="63">
+        <v>19.0</v>
+      </c>
+      <c r="J17" s="108">
+        <v>0.86</v>
+      </c>
+      <c r="K17" s="109">
+        <v>0.09</v>
+      </c>
+      <c r="L17" s="110">
+        <v>0.05</v>
+      </c>
+      <c r="M17" s="68">
+        <v>0.052631579</v>
+      </c>
+      <c r="N17" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O17" s="111">
+        <v>0.82</v>
+      </c>
+      <c r="P17" s="112">
+        <v>0.17</v>
+      </c>
+      <c r="Q17" s="99">
+        <v>0.01</v>
+      </c>
+      <c r="R17" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="S17" s="113">
+        <v>-0.047609234</v>
+      </c>
+      <c r="T17" s="63">
+        <v>0.81602713</v>
+      </c>
+      <c r="U17" s="63">
+        <v>1.1</v>
+      </c>
+      <c r="V17" s="73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="64">
+        <v>45395.458333333336</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="63">
+        <v>2.1</v>
+      </c>
+      <c r="H18" s="63">
+        <v>3.4</v>
+      </c>
+      <c r="I18" s="63">
+        <v>3.5</v>
+      </c>
+      <c r="J18" s="114">
+        <v>0.45</v>
+      </c>
+      <c r="K18" s="95">
+        <v>0.28</v>
+      </c>
+      <c r="L18" s="70">
+        <v>0.27</v>
+      </c>
+      <c r="M18" s="68">
+        <v>0.056022409</v>
+      </c>
+      <c r="N18" s="63">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="87">
+        <v>0.34</v>
+      </c>
+      <c r="P18" s="91">
+        <v>0.44</v>
+      </c>
+      <c r="Q18" s="67">
+        <v>0.22</v>
+      </c>
+      <c r="R18" s="63">
+        <v>0.0</v>
+      </c>
+      <c r="S18" s="97">
+        <v>0.16603443</v>
+      </c>
+      <c r="T18" s="63">
+        <v>0.444549019</v>
+      </c>
+      <c r="U18" s="63">
+        <v>3.4</v>
+      </c>
+      <c r="V18" s="73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="63" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="64">
+        <v>45395.5625</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="63">
+        <v>2.3</v>
+      </c>
+      <c r="H19" s="63">
+        <v>4.0</v>
+      </c>
+      <c r="I19" s="63">
+        <v>2.7</v>
+      </c>
+      <c r="J19" s="98">
+        <v>0.41</v>
+      </c>
+      <c r="K19" s="88">
+        <v>0.24</v>
+      </c>
+      <c r="L19" s="92">
+        <v>0.35</v>
+      </c>
+      <c r="M19" s="68">
+        <v>0.055152979</v>
+      </c>
+      <c r="N19" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="O19" s="95">
+        <v>0.28</v>
+      </c>
+      <c r="P19" s="92">
+        <v>0.35</v>
+      </c>
+      <c r="Q19" s="115">
+        <v>0.37</v>
+      </c>
+      <c r="R19" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="S19" s="116">
+        <v>0.019080418</v>
+      </c>
+      <c r="T19" s="63">
+        <v>0.370091483</v>
+      </c>
+      <c r="U19" s="63">
+        <v>2.7</v>
+      </c>
+      <c r="V19" s="73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="53">
+        <v>45431.541666666664</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="52">
+        <v>1.67</v>
+      </c>
+      <c r="H20" s="52">
+        <v>4.2</v>
+      </c>
+      <c r="I20" s="52">
+        <v>4.75</v>
+      </c>
+      <c r="J20" s="117">
+        <v>0.57</v>
+      </c>
+      <c r="K20" s="118">
+        <v>0.23</v>
+      </c>
+      <c r="L20" s="119">
+        <v>0.2</v>
+      </c>
+      <c r="M20" s="52">
+        <v>0.047424</v>
+      </c>
+      <c r="N20" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="O20" s="120">
+        <v>0.53</v>
+      </c>
+      <c r="P20" s="105">
+        <v>0.32</v>
+      </c>
+      <c r="Q20" s="121">
+        <v>0.15</v>
+      </c>
+      <c r="R20" s="52">
+        <v>-1.0</v>
+      </c>
+      <c r="S20" s="122">
+        <v>0.042716</v>
+      </c>
+      <c r="T20" s="52">
+        <v>0.471026</v>
+      </c>
+      <c r="U20" s="52">
+        <v>2.22905</v>
+      </c>
+      <c r="V20" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="W20" s="10">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="64">
+        <v>45431.583333333336</v>
+      </c>
+      <c r="C21" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="63">
+        <v>1.62</v>
+      </c>
+      <c r="H21" s="63">
+        <v>4.0</v>
+      </c>
+      <c r="I21" s="63">
+        <v>5.0</v>
+      </c>
+      <c r="J21" s="123">
+        <v>0.58</v>
+      </c>
+      <c r="K21" s="66">
+        <v>0.23</v>
+      </c>
+      <c r="L21" s="76">
+        <v>0.19</v>
+      </c>
+      <c r="M21" s="63">
+        <v>0.067284</v>
+      </c>
+      <c r="N21" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="O21" s="124">
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="125">
+        <v>0.33</v>
+      </c>
+      <c r="Q21" s="126">
+        <v>0.48</v>
+      </c>
+      <c r="R21" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="S21" s="126">
+        <v>0.317412</v>
+      </c>
+      <c r="T21" s="63">
+        <v>0.476154</v>
+      </c>
+      <c r="U21" s="63">
+        <v>6.0</v>
+      </c>
+      <c r="V21" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="64">
+        <v>45431.583333333336</v>
+      </c>
+      <c r="C22" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="63">
+        <v>1.36</v>
+      </c>
+      <c r="H22" s="63">
+        <v>4.75</v>
+      </c>
+      <c r="I22" s="63">
+        <v>8.5</v>
+      </c>
+      <c r="J22" s="127">
+        <v>0.69</v>
+      </c>
+      <c r="K22" s="124">
+        <v>0.2</v>
+      </c>
+      <c r="L22" s="128">
+        <v>0.11</v>
+      </c>
+      <c r="M22" s="63">
+        <v>0.063467</v>
+      </c>
+      <c r="N22" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O22" s="129">
+        <v>0.68</v>
+      </c>
+      <c r="P22" s="67">
+        <v>0.22</v>
+      </c>
+      <c r="Q22" s="77">
+        <v>0.1</v>
+      </c>
+      <c r="R22" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="S22" s="130">
+        <v>-0.03768</v>
+      </c>
+      <c r="T22" s="63">
+        <v>0.680028</v>
+      </c>
+      <c r="U22" s="63">
+        <v>1.33</v>
+      </c>
+      <c r="V22" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="64">
+        <v>45431.583333333336</v>
+      </c>
+      <c r="C23" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="63">
+        <v>1.27</v>
+      </c>
+      <c r="H23" s="63">
+        <v>5.75</v>
+      </c>
+      <c r="I23" s="63">
+        <v>11.0</v>
+      </c>
+      <c r="J23" s="131">
+        <v>0.75</v>
+      </c>
+      <c r="K23" s="112">
+        <v>0.17</v>
+      </c>
+      <c r="L23" s="109">
+        <v>0.09</v>
+      </c>
+      <c r="M23" s="63">
+        <v>0.052224</v>
+      </c>
+      <c r="N23" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O23" s="132">
+        <v>0.74</v>
+      </c>
+      <c r="P23" s="133">
+        <v>0.16</v>
+      </c>
+      <c r="Q23" s="128">
+        <v>0.11</v>
+      </c>
+      <c r="R23" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="S23" s="134">
+        <v>0.025991</v>
+      </c>
+      <c r="T23" s="63">
+        <v>0.736184</v>
+      </c>
+      <c r="U23" s="63">
+        <v>1.33</v>
+      </c>
+      <c r="V23" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="162">
   <si>
     <t>id_match</t>
   </si>
@@ -355,15 +355,179 @@
   </si>
   <si>
     <t>rayo vallecano</t>
+  </si>
+  <si>
+    <t>Yw6Y6j5s</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Atl. Tucuman</t>
+  </si>
+  <si>
+    <t>Copa de la Liga Profesional</t>
+  </si>
+  <si>
+    <t>3.50</t>
+  </si>
+  <si>
+    <t>4dFzGfJF</t>
+  </si>
+  <si>
+    <t>Newcastle</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>dif_prob_mod_bm &lt; 0%</t>
+  </si>
+  <si>
+    <t>IuDOIdZd</t>
+  </si>
+  <si>
+    <t>Nottingham</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>dif_prob_mod_bm &gt; 0%</t>
+  </si>
+  <si>
+    <t>n7P60FJS</t>
+  </si>
+  <si>
+    <t>Bournemouth</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>tOTufDdd</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Wolves</t>
+  </si>
+  <si>
+    <t>dWBSHGl3</t>
+  </si>
+  <si>
+    <t>West Ham</t>
+  </si>
+  <si>
+    <t>Tottenham</t>
+  </si>
+  <si>
+    <t>8AVXeZRq</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Luton</t>
+  </si>
+  <si>
+    <t>12.00</t>
+  </si>
+  <si>
+    <t>19.00</t>
+  </si>
+  <si>
+    <t>2XUyegsj</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
+    <t>Brighton</t>
+  </si>
+  <si>
+    <t>3.75</t>
+  </si>
+  <si>
+    <t>2.63</t>
+  </si>
+  <si>
+    <t>QB3qEYmS</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>6.50</t>
+  </si>
+  <si>
+    <t>10.00</t>
+  </si>
+  <si>
+    <t>nL4uFEYL</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Sheffield Utd</t>
+  </si>
+  <si>
+    <t>13.00</t>
+  </si>
+  <si>
+    <t>21.00</t>
+  </si>
+  <si>
+    <t>jgBWGz49</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Manchester Utd</t>
+  </si>
+  <si>
+    <t>1.91</t>
+  </si>
+  <si>
+    <t>4.00</t>
+  </si>
+  <si>
+    <t>3.60</t>
+  </si>
+  <si>
+    <t>GYcDdIoe</t>
+  </si>
+  <si>
+    <t>rotherham</t>
+  </si>
+  <si>
+    <t>plymouth</t>
+  </si>
+  <si>
+    <t>Gv9P4LuB</t>
+  </si>
+  <si>
+    <t>velez sarsfield</t>
+  </si>
+  <si>
+    <t>argentinos jrs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="d.m"/>
+    <numFmt numFmtId="167" formatCode="dd.mm.yyyy h:mm"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -393,7 +557,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="75">
+  <fills count="91">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,8 +1002,104 @@
         <bgColor rgb="FFF9FDFB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCFA"/>
+        <bgColor rgb="FFF8FCFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE5D1"/>
+        <bgColor rgb="FFBDE5D1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF6"/>
+        <bgColor rgb="FFF3FAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF7F1"/>
+        <bgColor rgb="FFEBF7F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFC"/>
+        <bgColor rgb="FFFAFDFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C397"/>
+        <bgColor rgb="FF69C397"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FBF7"/>
+        <bgColor rgb="FFF3FBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BF91"/>
+        <bgColor rgb="FF60BF91"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD6B9"/>
+        <bgColor rgb="FF9AD6B9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D9"/>
+        <bgColor rgb="FFC9E9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CCAA4"/>
+        <bgColor rgb="FF7CCAA4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C9A2"/>
+        <bgColor rgb="FF79C9A2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C295"/>
+        <bgColor rgb="FF67C295"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDFC7"/>
+        <bgColor rgb="FFAFDFC7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DCC3"/>
+        <bgColor rgb="FFA8DCC3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE4D0"/>
+        <bgColor rgb="FFBBE4D0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border/>
     <border>
       <top style="thin">
@@ -873,11 +1133,16 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="dotted">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="185">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1281,6 +1546,156 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="74" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="75" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="14" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="22" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="76" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="31" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="77" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="23" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="78" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="33" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="79" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="80" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="81" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="82" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="25" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="83" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="84" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="85" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="67" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="86" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="87" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="88" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="89" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="90" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="44" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="56" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="89" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="90" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="53" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="40" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="27" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="88" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="29" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="79" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3089,6 +3504,1066 @@
         <v>44</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="53">
+        <v>45382.770833333336</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="135" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="135" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" s="52">
+        <v>1.8</v>
+      </c>
+      <c r="H24" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="J24" s="120">
+        <v>0.53</v>
+      </c>
+      <c r="K24" s="58">
+        <v>0.27</v>
+      </c>
+      <c r="L24" s="82">
+        <v>0.19</v>
+      </c>
+      <c r="M24" s="56">
+        <v>0.041269841</v>
+      </c>
+      <c r="N24" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="O24" s="59">
+        <v>0.55</v>
+      </c>
+      <c r="P24" s="118">
+        <v>0.23</v>
+      </c>
+      <c r="Q24" s="85">
+        <v>0.22</v>
+      </c>
+      <c r="R24" s="136">
+        <v>1.0</v>
+      </c>
+      <c r="S24" s="137"/>
+      <c r="T24" s="137"/>
+      <c r="U24" s="137"/>
+      <c r="V24" s="138"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="64">
+        <v>45384.645833333336</v>
+      </c>
+      <c r="C25" s="63" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="63" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="H25" s="63">
+        <v>3.75</v>
+      </c>
+      <c r="I25" s="63">
+        <v>3.6</v>
+      </c>
+      <c r="J25" s="126">
+        <v>0.48</v>
+      </c>
+      <c r="K25" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="L25" s="70">
+        <v>0.27</v>
+      </c>
+      <c r="M25" s="68">
+        <v>0.044444</v>
+      </c>
+      <c r="N25" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O25" s="114">
+        <v>0.45</v>
+      </c>
+      <c r="P25" s="100">
+        <v>0.29</v>
+      </c>
+      <c r="Q25" s="70">
+        <v>0.27</v>
+      </c>
+      <c r="R25" s="139">
+        <v>1.0</v>
+      </c>
+      <c r="S25" s="140">
+        <v>0.03</v>
+      </c>
+      <c r="T25" s="63">
+        <v>0.55</v>
+      </c>
+      <c r="U25" s="141"/>
+      <c r="V25" s="73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="64">
+        <v>45384.645833333336</v>
+      </c>
+      <c r="C26" s="63" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="H26" s="63">
+        <v>3.75</v>
+      </c>
+      <c r="I26" s="63">
+        <v>3.6</v>
+      </c>
+      <c r="J26" s="126">
+        <v>0.48</v>
+      </c>
+      <c r="K26" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="L26" s="70">
+        <v>0.27</v>
+      </c>
+      <c r="M26" s="68">
+        <v>0.044444</v>
+      </c>
+      <c r="N26" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O26" s="114">
+        <v>0.45</v>
+      </c>
+      <c r="P26" s="100">
+        <v>0.29</v>
+      </c>
+      <c r="Q26" s="70">
+        <v>0.27</v>
+      </c>
+      <c r="R26" s="139">
+        <v>1.0</v>
+      </c>
+      <c r="S26" s="140">
+        <v>0.03</v>
+      </c>
+      <c r="T26" s="63">
+        <v>0.55</v>
+      </c>
+      <c r="U26" s="141"/>
+      <c r="V26" s="73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="64">
+        <v>45384.645833333336</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="63">
+        <v>2.63</v>
+      </c>
+      <c r="H27" s="63">
+        <v>3.4</v>
+      </c>
+      <c r="I27" s="63">
+        <v>2.7</v>
+      </c>
+      <c r="J27" s="142">
+        <v>0.36</v>
+      </c>
+      <c r="K27" s="95">
+        <v>0.28</v>
+      </c>
+      <c r="L27" s="92">
+        <v>0.35</v>
+      </c>
+      <c r="M27" s="68">
+        <v>0.044716</v>
+      </c>
+      <c r="N27" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="O27" s="142">
+        <v>0.36</v>
+      </c>
+      <c r="P27" s="143">
+        <v>0.25</v>
+      </c>
+      <c r="Q27" s="144">
+        <v>0.39</v>
+      </c>
+      <c r="R27" s="139">
+        <v>2.0</v>
+      </c>
+      <c r="S27" s="140">
+        <v>0.03</v>
+      </c>
+      <c r="T27" s="63">
+        <v>0.39</v>
+      </c>
+      <c r="U27" s="141"/>
+      <c r="V27" s="73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="64">
+        <v>45384.65625</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="63">
+        <v>1.95</v>
+      </c>
+      <c r="H28" s="63">
+        <v>3.75</v>
+      </c>
+      <c r="I28" s="63">
+        <v>3.6</v>
+      </c>
+      <c r="J28" s="101">
+        <v>0.49</v>
+      </c>
+      <c r="K28" s="143">
+        <v>0.25</v>
+      </c>
+      <c r="L28" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="M28" s="68">
+        <v>0.057265</v>
+      </c>
+      <c r="N28" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O28" s="145">
+        <v>0.53</v>
+      </c>
+      <c r="P28" s="143">
+        <v>0.25</v>
+      </c>
+      <c r="Q28" s="90">
+        <v>0.21</v>
+      </c>
+      <c r="R28" s="139">
+        <v>1.0</v>
+      </c>
+      <c r="S28" s="146">
+        <v>0.05</v>
+      </c>
+      <c r="T28" s="63">
+        <v>0.53</v>
+      </c>
+      <c r="U28" s="141"/>
+      <c r="V28" s="73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="64">
+        <v>45384.65625</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="63">
+        <v>2.45</v>
+      </c>
+      <c r="H29" s="63">
+        <v>3.6</v>
+      </c>
+      <c r="I29" s="63">
+        <v>2.75</v>
+      </c>
+      <c r="J29" s="144">
+        <v>0.39</v>
+      </c>
+      <c r="K29" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="L29" s="92">
+        <v>0.35</v>
+      </c>
+      <c r="M29" s="68">
+        <v>0.049577</v>
+      </c>
+      <c r="N29" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="O29" s="147">
+        <v>0.31</v>
+      </c>
+      <c r="P29" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="Q29" s="89">
+        <v>0.43</v>
+      </c>
+      <c r="R29" s="139">
+        <v>2.0</v>
+      </c>
+      <c r="S29" s="148">
+        <v>0.08</v>
+      </c>
+      <c r="T29" s="63">
+        <v>0.43</v>
+      </c>
+      <c r="U29" s="141"/>
+      <c r="V29" s="73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="64">
+        <v>45384.677083333336</v>
+      </c>
+      <c r="C30" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="63">
+        <v>3.3</v>
+      </c>
+      <c r="H30" s="63">
+        <v>4.2</v>
+      </c>
+      <c r="I30" s="63">
+        <v>1.95</v>
+      </c>
+      <c r="J30" s="100">
+        <v>0.29</v>
+      </c>
+      <c r="K30" s="66">
+        <v>0.23</v>
+      </c>
+      <c r="L30" s="101">
+        <v>0.49</v>
+      </c>
+      <c r="M30" s="68">
+        <v>0.053946</v>
+      </c>
+      <c r="N30" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="O30" s="143">
+        <v>0.25</v>
+      </c>
+      <c r="P30" s="143">
+        <v>0.25</v>
+      </c>
+      <c r="Q30" s="149">
+        <v>0.5</v>
+      </c>
+      <c r="R30" s="139">
+        <v>2.0</v>
+      </c>
+      <c r="S30" s="150">
+        <v>0.02</v>
+      </c>
+      <c r="T30" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="U30" s="141"/>
+      <c r="V30" s="73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="64">
+        <v>45385.645833333336</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="151" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="151">
+        <v>1.09</v>
+      </c>
+      <c r="H31" s="63" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="152">
+        <v>0.87</v>
+      </c>
+      <c r="K31" s="153">
+        <v>0.08</v>
+      </c>
+      <c r="L31" s="110">
+        <v>0.05</v>
+      </c>
+      <c r="M31" s="68">
+        <v>0.053396105</v>
+      </c>
+      <c r="N31" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O31" s="154">
+        <v>0.92</v>
+      </c>
+      <c r="P31" s="155">
+        <v>0.06</v>
+      </c>
+      <c r="Q31" s="99">
+        <v>0.01</v>
+      </c>
+      <c r="R31" s="139">
+        <v>1.0</v>
+      </c>
+      <c r="S31" s="146">
+        <v>0.05</v>
+      </c>
+      <c r="T31" s="63">
+        <v>0.92</v>
+      </c>
+      <c r="U31" s="141"/>
+      <c r="V31" s="73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" s="64">
+        <v>45385.645833333336</v>
+      </c>
+      <c r="C32" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="151" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G32" s="151">
+        <v>2.45</v>
+      </c>
+      <c r="H32" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="I32" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="J32" s="144">
+        <v>0.39</v>
+      </c>
+      <c r="K32" s="143">
+        <v>0.25</v>
+      </c>
+      <c r="L32" s="142">
+        <v>0.36</v>
+      </c>
+      <c r="M32" s="68">
+        <v>0.055058069</v>
+      </c>
+      <c r="N32" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O32" s="156">
+        <v>0.59</v>
+      </c>
+      <c r="P32" s="67">
+        <v>0.22</v>
+      </c>
+      <c r="Q32" s="76">
+        <v>0.19</v>
+      </c>
+      <c r="R32" s="139">
+        <v>1.0</v>
+      </c>
+      <c r="S32" s="157">
+        <v>0.21</v>
+      </c>
+      <c r="T32" s="63">
+        <v>0.59</v>
+      </c>
+      <c r="U32" s="141"/>
+      <c r="V32" s="73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="64">
+        <v>45385.677083333336</v>
+      </c>
+      <c r="C33" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="151" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" s="151">
+        <v>1.25</v>
+      </c>
+      <c r="H33" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="I33" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="J33" s="158">
+        <v>0.76</v>
+      </c>
+      <c r="K33" s="159">
+        <v>0.15</v>
+      </c>
+      <c r="L33" s="109">
+        <v>0.09</v>
+      </c>
+      <c r="M33" s="68">
+        <v>0.053846154</v>
+      </c>
+      <c r="N33" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O33" s="160">
+        <v>0.78</v>
+      </c>
+      <c r="P33" s="79">
+        <v>0.14</v>
+      </c>
+      <c r="Q33" s="153">
+        <v>0.08</v>
+      </c>
+      <c r="R33" s="139">
+        <v>1.0</v>
+      </c>
+      <c r="S33" s="150">
+        <v>0.02</v>
+      </c>
+      <c r="T33" s="63">
+        <v>0.78</v>
+      </c>
+      <c r="U33" s="141"/>
+      <c r="V33" s="73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="64">
+        <v>45386.645833333336</v>
+      </c>
+      <c r="C34" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="E34" s="151" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" s="151">
+        <v>1.08</v>
+      </c>
+      <c r="H34" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="I34" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="J34" s="161">
+        <v>0.88</v>
+      </c>
+      <c r="K34" s="162">
+        <v>0.07</v>
+      </c>
+      <c r="L34" s="110">
+        <v>0.05</v>
+      </c>
+      <c r="M34" s="68">
+        <v>0.05046805</v>
+      </c>
+      <c r="N34" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O34" s="108">
+        <v>0.86</v>
+      </c>
+      <c r="P34" s="128">
+        <v>0.11</v>
+      </c>
+      <c r="Q34" s="72">
+        <v>0.03</v>
+      </c>
+      <c r="R34" s="139">
+        <v>1.0</v>
+      </c>
+      <c r="S34" s="150">
+        <v>0.02</v>
+      </c>
+      <c r="T34" s="63">
+        <v>0.14</v>
+      </c>
+      <c r="U34" s="141"/>
+      <c r="V34" s="73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="64">
+        <v>45386.677083333336</v>
+      </c>
+      <c r="C35" s="63" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G35" s="63" t="s">
+        <v>153</v>
+      </c>
+      <c r="H35" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="I35" s="63" t="s">
+        <v>155</v>
+      </c>
+      <c r="J35" s="149">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="88">
+        <v>0.24</v>
+      </c>
+      <c r="L35" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="M35" s="68">
+        <v>0.051337987</v>
+      </c>
+      <c r="N35" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O35" s="163">
+        <v>0.47</v>
+      </c>
+      <c r="P35" s="100">
+        <v>0.29</v>
+      </c>
+      <c r="Q35" s="88">
+        <v>0.24</v>
+      </c>
+      <c r="R35" s="63">
+        <v>-1.0</v>
+      </c>
+      <c r="S35" s="150">
+        <v>0.02</v>
+      </c>
+      <c r="T35" s="63">
+        <v>0.53</v>
+      </c>
+      <c r="U35" s="63">
+        <v>1.894736842</v>
+      </c>
+      <c r="V35" s="73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36" s="64">
+        <v>45386.677083333336</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G36" s="63" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="I36" s="63" t="s">
+        <v>155</v>
+      </c>
+      <c r="J36" s="149">
+        <v>0.5</v>
+      </c>
+      <c r="K36" s="88">
+        <v>0.24</v>
+      </c>
+      <c r="L36" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="M36" s="68">
+        <v>0.051337987</v>
+      </c>
+      <c r="N36" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="O36" s="163">
+        <v>0.47</v>
+      </c>
+      <c r="P36" s="100">
+        <v>0.29</v>
+      </c>
+      <c r="Q36" s="88">
+        <v>0.24</v>
+      </c>
+      <c r="R36" s="63">
+        <v>-1.0</v>
+      </c>
+      <c r="S36" s="150">
+        <v>0.02</v>
+      </c>
+      <c r="T36" s="63">
+        <v>0.53</v>
+      </c>
+      <c r="U36" s="63">
+        <v>1.894736842</v>
+      </c>
+      <c r="V36" s="73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" s="164">
+        <v>45387.666666666664</v>
+      </c>
+      <c r="C37" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="D37" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="E37" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="G37" s="63">
+        <v>4.2</v>
+      </c>
+      <c r="H37" s="63">
+        <v>3.6</v>
+      </c>
+      <c r="I37" s="63">
+        <v>1.85</v>
+      </c>
+      <c r="J37" s="66">
+        <v>0.23</v>
+      </c>
+      <c r="K37" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="L37" s="165">
+        <v>0.51</v>
+      </c>
+      <c r="M37" s="68">
+        <v>0.06</v>
+      </c>
+      <c r="N37" s="63">
+        <v>2.0</v>
+      </c>
+      <c r="O37" s="125">
+        <v>0.33</v>
+      </c>
+      <c r="P37" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="Q37" s="166">
+        <v>0.4</v>
+      </c>
+      <c r="R37" s="63">
+        <v>-2.0</v>
+      </c>
+      <c r="S37" s="112">
+        <v>0.11</v>
+      </c>
+      <c r="T37" s="63">
+        <v>0.6</v>
+      </c>
+      <c r="U37" s="63">
+        <v>1.938461538</v>
+      </c>
+      <c r="V37" s="73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="167" t="s">
+        <v>156</v>
+      </c>
+      <c r="B38" s="168">
+        <v>45387.666666666664</v>
+      </c>
+      <c r="C38" s="167" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" s="167" t="s">
+        <v>158</v>
+      </c>
+      <c r="E38" s="167" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="167" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" s="167">
+        <v>4.2</v>
+      </c>
+      <c r="H38" s="167">
+        <v>3.6</v>
+      </c>
+      <c r="I38" s="167">
+        <v>1.85</v>
+      </c>
+      <c r="J38" s="169">
+        <v>0.23</v>
+      </c>
+      <c r="K38" s="170">
+        <v>0.26</v>
+      </c>
+      <c r="L38" s="171">
+        <v>0.51</v>
+      </c>
+      <c r="M38" s="172">
+        <v>0.06</v>
+      </c>
+      <c r="N38" s="167">
+        <v>2.0</v>
+      </c>
+      <c r="O38" s="173">
+        <v>0.33</v>
+      </c>
+      <c r="P38" s="170">
+        <v>0.26</v>
+      </c>
+      <c r="Q38" s="174">
+        <v>0.4</v>
+      </c>
+      <c r="R38" s="167">
+        <v>-2.0</v>
+      </c>
+      <c r="S38" s="175">
+        <v>0.11</v>
+      </c>
+      <c r="T38" s="167">
+        <v>0.6</v>
+      </c>
+      <c r="U38" s="167">
+        <v>1.938461538</v>
+      </c>
+      <c r="V38" s="176" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="167" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="177">
+        <v>45387.8125</v>
+      </c>
+      <c r="C39" s="167" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" s="167" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" s="167" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="167" t="s">
+        <v>111</v>
+      </c>
+      <c r="G39" s="167">
+        <v>2.15</v>
+      </c>
+      <c r="H39" s="167" t="s">
+        <v>60</v>
+      </c>
+      <c r="I39" s="167" t="s">
+        <v>155</v>
+      </c>
+      <c r="J39" s="178">
+        <v>0.44</v>
+      </c>
+      <c r="K39" s="179">
+        <v>0.29</v>
+      </c>
+      <c r="L39" s="180">
+        <v>0.27</v>
+      </c>
+      <c r="M39" s="172">
+        <v>0.046</v>
+      </c>
+      <c r="N39" s="167">
+        <v>1.0</v>
+      </c>
+      <c r="O39" s="181">
+        <v>0.47</v>
+      </c>
+      <c r="P39" s="182">
+        <v>0.3</v>
+      </c>
+      <c r="Q39" s="169">
+        <v>0.23</v>
+      </c>
+      <c r="R39" s="167">
+        <v>1.0</v>
+      </c>
+      <c r="S39" s="183">
+        <v>0.02</v>
+      </c>
+      <c r="T39" s="167">
+        <v>0.47</v>
+      </c>
+      <c r="U39" s="184">
+        <v>2.15</v>
+      </c>
+      <c r="V39" s="167" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -1054,28 +1054,28 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3137173358551308</v>
+        <v>0.3163272478320253</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.5315363677345756</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.148467812605421</v>
+        <v>0.1521363844333992</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3064873643909752</v>
+        <v>0.3002088805861026</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3064873643909752</v>
+        <v>0.3002088805861026</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.5315363677345756</v>
       </c>
       <c r="W7" t="n">
         <v>4.1</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>37.64703960776137</v>
+        <v>37.20754574142029</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.64703960776137</v>
+        <v>37.20754574142029</v>
       </c>
     </row>
     <row r="8">
@@ -1670,28 +1670,28 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3670770600203078</v>
+        <v>0.3522794075213345</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4077433881239975</v>
+        <v>0.3992244010656373</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2251795518556948</v>
+        <v>0.2484961914130281</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1713797517603611</v>
+        <v>0.162860764702001</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1713797517603611</v>
+        <v>0.162860764702001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4077433881239975</v>
+        <v>0.3992244010656373</v>
       </c>
       <c r="W14" t="n">
         <v>4</v>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>28.54203716867982</v>
+        <v>27.94570807459461</v>
       </c>
       <c r="Z14" t="n">
-        <v>28.54203716867982</v>
+        <v>27.94570807459461</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,14 +429,1283 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A2"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_match</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>prob_home_bm</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>prob_draw_bm</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>prob_away_bm</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>overround</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>predicted_result</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>prob_class_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>prob_class_0</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>prob_class_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>copiado_formaciones</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>result_to_bet</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_result_to_bet</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>prob_result_to_bet</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>odd_to_bet</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>multiplier</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>stake_to_bet</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>id_match</t>
-        </is>
+          <t>hK8xvrmh</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>167</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2928767382461451</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2644026109166588</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4427206508371961</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05058636453985299</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1782451111666511</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3571235536153105</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4646313352180383</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.02191068438084226</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.02191068438084226</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4646313352180383</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>32.52419346526268</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>32.52419346526268</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>rwisKhLu</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>167</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4603234298608499</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2775479503572771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05970030288538197</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2571887055520775</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3187289200171914</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4240823744307311</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.146534424073454</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.146534424073454</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.4240823744307311</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>29.68576621015118</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>29.68576621015118</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2u7rIWkh</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>167</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4851944345344275</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2365322868355333</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2782732786300393</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05693815987933637</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3069573833806068</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.432377296398577</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2606653202208161</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1958450095630437</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1958450095630437</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.432377296398577</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>30.26641074790039</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>30.26641074790039</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>167</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.313989239046887</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2478862413528055</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4381245196003075</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0616075071399429</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5402763867114466</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2716252169503502</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1880983963382031</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2262871476645597</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.2262871476645597</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5402763867114466</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>37.81934706980126</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>37.81934706980126</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>167</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4415584415584415</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2792207792207792</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2792207792207792</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.05335157318741457</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05171002128636167</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.5831063597486422</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3651836189649961</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.303885580527863</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.303885580527863</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5831063597486422</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>40.81744518240495</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>40.81744518240495</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MTkoJCzn</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45462.98958333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>167</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5579074690051407</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.231327487148473</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2107650438463864</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05435995536425953</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3137173358551308</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.5378148515394482</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.148467812605421</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3064873643909752</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.3064873643909752</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5378148515394482</v>
+      </c>
+      <c r="W7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>37.64703960776137</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>37.64703960776137</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zg5jGAK4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.286028602860286</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.242024202420242</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4719471947194719</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05944055944055959</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1248404827603851</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.4023580553124324</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4728014619271825</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0008542672077105906</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.0008542672077105906</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.4728014619271825</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>33.09610233490277</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>33.09610233490277</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ld9fFUZA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>167</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4545454545454546</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2727272727272728</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2727272727272728</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.04761904761904745</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2898941193190928</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4422466191872576</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2678592614936495</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1695193464599848</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.1695193464599848</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.4422466191872576</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>30.95726334310803</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>30.95726334310803</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WKbaElkH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>167</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4509283819628647</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2705570291777188</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2785145888594164</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.05602240896358546</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.4957383107137407</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.3722175717727494</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1320441175135099</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.04480992875087608</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.04480992875087608</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.4957383107137407</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>34.70168174996185</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>34.70168174996185</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ABc3D84N</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>167</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3647199046483909</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2634088200238379</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3718712753277712</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.05455002513826046</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3471049403890203</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3545298080055802</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2983652516053995</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.09112098798174229</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.09112098798174229</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.3545298080055802</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>24.81708656039061</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>24.81708656039061</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vo27CSJT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4880098022054963</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2321022230001751</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2798879747943288</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.05084059890372661</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4856464530380509</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.378293936563841</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1360596103981081</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.00236334916744535</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.00236334916744535</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4856464530380509</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>33.99525171266357</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>33.99525171266357</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>167</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4971246449109679</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2315873345804753</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2712880205085568</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0531769341627597</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.4721479090124855</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3170924136355052</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.2107596773520092</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.02497673589848237</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.02497673589848237</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4721479090124855</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>33.05035363087399</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>33.05035363087399</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4727272727272727</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2363636363636364</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2909090909090909</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05769230769230771</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3670770600203078</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.4077433881239975</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2251795518556948</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1713797517603611</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1713797517603611</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4077433881239975</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>28.54203716867982</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>28.54203716867982</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -429,15 +429,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id_match</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>date</t>
@@ -567,20 +562,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -590,85 +585,85 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2928767382461451</v>
+        <v>0.6386964914272737</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2644026109166588</v>
+        <v>0.2100601794027478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4427206508371961</v>
+        <v>0.1512433291699784</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05058636453985299</v>
+        <v>0.0578978978978979</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1782451111666511</v>
+        <v>0.4436791468412691</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3571235536153105</v>
+        <v>0.3705221432445802</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4646313352180383</v>
+        <v>0.1857987099141508</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02191068438084226</v>
+        <v>-0.1950173445860046</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02191068438084226</v>
+        <v>0.1950173445860046</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4646313352180383</v>
+        <v>0.5563208531587309</v>
       </c>
       <c r="W2" t="n">
-        <v>2.15</v>
+        <v>2.616279069767442</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>32.52419346526268</v>
+        <v>38.94245972111116</v>
       </c>
       <c r="Z2" t="n">
-        <v>32.52419346526268</v>
+        <v>38.94245972111116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -678,85 +673,85 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.449677174325864</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2552221800227877</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2951006456513482</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.05896074646074645</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2571887055520775</v>
+        <v>0.3319918150420612</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3187289200171914</v>
+        <v>0.2821118769142622</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4240823744307311</v>
+        <v>0.3858963080436765</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.146534424073454</v>
+        <v>0.09079566239232822</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.146534424073454</v>
+        <v>0.09079566239232822</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4240823744307311</v>
+        <v>0.3858963080436765</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>29.68576621015118</v>
+        <v>27.01274156305735</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.68576621015118</v>
+        <v>27.01274156305735</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -766,85 +761,85 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4851944345344275</v>
+        <v>0.6098357297414951</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2365322868355333</v>
+        <v>0.2183014736949925</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2782732786300393</v>
+        <v>0.1718627965635123</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05693815987933637</v>
+        <v>0.05792635435785254</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3069573833806068</v>
+        <v>0.5605383605228289</v>
       </c>
       <c r="P4" t="n">
-        <v>0.432377296398577</v>
+        <v>0.3535581894345241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2606653202208161</v>
+        <v>0.08590345004264675</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1958450095630437</v>
+        <v>-0.04929736921866623</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1958450095630437</v>
+        <v>-0.04929736921866623</v>
       </c>
       <c r="V4" t="n">
-        <v>0.432377296398577</v>
+        <v>0.5605383605228289</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>30.26641074790039</v>
+        <v>39.23768523659803</v>
       </c>
       <c r="Z4" t="n">
-        <v>30.26641074790039</v>
+        <v>39.23768523659803</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -854,85 +849,85 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>2.15</v>
+        <v>5.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.313989239046887</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2478862413528055</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4381245196003075</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0616075071399429</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5402763867114466</v>
+        <v>0.4065117704358618</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2716252169503502</v>
+        <v>0.4180952329923645</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1880983963382031</v>
+        <v>0.1753929965717735</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2262871476645597</v>
+        <v>0.1998843898261959</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2262871476645597</v>
+        <v>0.1998843898261959</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5402763867114466</v>
+        <v>0.4180952329923645</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>37.81934706980126</v>
+        <v>29.26666630946551</v>
       </c>
       <c r="Z5" t="n">
-        <v>37.81934706980126</v>
+        <v>29.26666630946551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -942,85 +937,85 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05335157318741457</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05171002128636167</v>
+        <v>0.4336241512981687</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5831063597486422</v>
+        <v>0.3839572154861549</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3651836189649961</v>
+        <v>0.1824186332156764</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.303885580527863</v>
+        <v>-0.1122160234211114</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.303885580527863</v>
+        <v>0.1122160234211114</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5831063597486422</v>
+        <v>0.5663758487018313</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4</v>
+        <v>2.079231692677071</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>40.81744518240495</v>
+        <v>39.64630940912819</v>
       </c>
       <c r="Z6" t="n">
-        <v>40.81744518240495</v>
+        <v>39.64630940912819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.98958333334</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1030,85 +1025,85 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5579074690051407</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="K7" t="n">
-        <v>0.231327487148473</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2107650438463864</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05435995536425953</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3137173358551308</v>
+        <v>0.4538576876343147</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.3445537488859154</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.148467812605421</v>
+        <v>0.20158856347977</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3064873643909752</v>
+        <v>-0.07245810183936946</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3064873643909752</v>
+        <v>0.07245810183936946</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.5461423123656852</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>37.64703960776137</v>
+        <v>38.22996186559796</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.64703960776137</v>
+        <v>38.22996186559796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>austin fc</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1118,85 +1113,85 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.286028602860286</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="K8" t="n">
-        <v>0.242024202420242</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4719471947194719</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05944055944055959</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1248404827603851</v>
+        <v>0.3797770002987284</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4023580553124324</v>
+        <v>0.2412557721298951</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4728014619271825</v>
+        <v>0.3789672275713766</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0008542672077105906</v>
+        <v>-0.1595488423979008</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0008542672077105906</v>
+        <v>0.1595488423979008</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4728014619271825</v>
+        <v>0.6202229997012716</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>2.048780487804879</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>33.09610233490277</v>
+        <v>43.41560997908901</v>
       </c>
       <c r="Z8" t="n">
-        <v>33.09610233490277</v>
+        <v>43.41560997908901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1206,85 +1201,85 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04761904761904745</v>
+        <v>0.06060606060606055</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2898941193190928</v>
+        <v>0.3757201307377791</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4422466191872576</v>
+        <v>0.3500274915414723</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2678592614936495</v>
+        <v>0.2742523777207485</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1695193464599848</v>
+        <v>-0.0528512978336495</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1695193464599848</v>
+        <v>0.0528512978336495</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4422466191872576</v>
+        <v>0.6242798692622209</v>
       </c>
       <c r="W9" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>30.95726334310803</v>
+        <v>43.69959084835546</v>
       </c>
       <c r="Z9" t="n">
-        <v>30.95726334310803</v>
+        <v>43.69959084835546</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1294,85 +1289,85 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4509283819628647</v>
+        <v>0.5129935875801552</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.2372595342558218</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2785145888594164</v>
+        <v>0.2497468781640229</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05602240896358546</v>
+        <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4957383107137407</v>
+        <v>0.2618796408719433</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3722175717727494</v>
+        <v>0.3590715274375488</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1320441175135099</v>
+        <v>0.3790488316905077</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.04480992875087608</v>
+        <v>0.1293019535264847</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.04480992875087608</v>
+        <v>0.1293019535264847</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4957383107137407</v>
+        <v>0.3790488316905077</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>34.70168174996185</v>
+        <v>26.53341821833554</v>
       </c>
       <c r="Z10" t="n">
-        <v>34.70168174996185</v>
+        <v>26.53341821833554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1382,85 +1377,85 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3647199046483909</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2634088200238379</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3718712753277712</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05455002513826046</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3471049403890203</v>
+        <v>0.3086285968254135</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3545298080055802</v>
+        <v>0.5316170522423062</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2983652516053995</v>
+        <v>0.1597543509322801</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09112098798174229</v>
+        <v>0.3210907364528325</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09112098798174229</v>
+        <v>0.3210907364528325</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3545298080055802</v>
+        <v>0.5316170522423062</v>
       </c>
       <c r="W11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>24.81708656039061</v>
+        <v>37.21319365696143</v>
       </c>
       <c r="Z11" t="n">
-        <v>24.81708656039061</v>
+        <v>37.21319365696143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1470,85 +1465,85 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4880098022054963</v>
+        <v>0.550173120294781</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2321022230001751</v>
+        <v>0.2160033035799371</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2798879747943288</v>
+        <v>0.2338235761252819</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05084059890372661</v>
+        <v>0.06918217633473711</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4856464530380509</v>
+        <v>0.289341441372672</v>
       </c>
       <c r="P12" t="n">
-        <v>0.378293936563841</v>
+        <v>0.243865103015309</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1360596103981081</v>
+        <v>0.4667934556120188</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.00236334916744535</v>
+        <v>0.2329698794867369</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.00236334916744535</v>
+        <v>0.2329698794867369</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4856464530380509</v>
+        <v>0.4667934556120188</v>
       </c>
       <c r="W12" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>33.99525171266357</v>
+        <v>32.67554189284132</v>
       </c>
       <c r="Z12" t="n">
-        <v>33.99525171266357</v>
+        <v>32.67554189284132</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1558,85 +1553,85 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4971246449109679</v>
+        <v>0.6880733944954128</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2315873345804753</v>
+        <v>0.1871559633027523</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2712880205085568</v>
+        <v>0.1247706422018349</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0531769341627597</v>
+        <v>0.06862745098039214</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4721479090124855</v>
+        <v>0.6190558219313727</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3170924136355052</v>
+        <v>0.3026384164933133</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2107596773520092</v>
+        <v>0.07830576157531427</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.02497673589848237</v>
+        <v>-0.06901757256404017</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.02497673589848237</v>
+        <v>0.06901757256404017</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4721479090124855</v>
+        <v>0.3809441780686273</v>
       </c>
       <c r="W13" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>33.05035363087399</v>
+        <v>26.66609246480391</v>
       </c>
       <c r="Z13" t="n">
-        <v>33.05035363087399</v>
+        <v>26.66609246480391</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1646,66 +1641,1386 @@
         <v>1671</v>
       </c>
       <c r="G14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4295665634674923</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2554179566563468</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.315015479876161</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05814905814905802</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5205753914335942</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.4044264527514825</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.07499815581492324</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.09100882796610194</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.09100882796610194</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5205753914335942</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>36.4402774003516</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>36.4402774003516</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6045340050377834</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.23727959697733</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1581863979848867</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.05360934182590227</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.4209874955756275</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4367556184360717</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1422568859883006</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1994760214587418</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.1994760214587418</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4367556184360717</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>30.57289329052502</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>30.57289329052502</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6386964914272737</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2100601794027478</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1512433291699784</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0578978978978979</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.4436791468412691</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3705221432445802</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1857987099141508</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.1950173445860046</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.1950173445860046</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.5563208531587309</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.616279069767442</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>38.94245972111116</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>38.94245972111116</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.449677174325864</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2552221800227877</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2951006456513482</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.05896074646074645</v>
+      </c>
+      <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="O17" t="n">
+        <v>0.3319918150420612</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.2821118769142622</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3858963080436765</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.09079566239232822</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.09079566239232822</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.3858963080436765</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>27.01274156305735</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>27.01274156305735</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6098357297414951</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2183014736949925</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1718627965635123</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.05792635435785254</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5605383605228289</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.3535581894345241</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.08590345004264675</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.04929736921866623</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.04929736921866623</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.5605383605228289</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>39.23768523659803</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>39.23768523659803</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6018171661844011</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2182108431661685</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1799719906494304</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.05836574785251614</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.4065117704358618</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4180952329923645</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1753929965717735</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1998843898261959</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.1998843898261959</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.4180952329923645</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>29.26666630946551</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>29.26666630946551</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H20" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.4727272727272727</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2363636363636364</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.2909090909090909</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.05769230769230771</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="I20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.05898156429801493</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4336241512981687</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.3839572154861549</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1824186332156764</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.1122160234211114</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.1122160234211114</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.5663758487018313</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.079231692677071</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>39.64630940912819</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>39.64630940912819</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4538576876343147</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.3445537488859154</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.20158856347977</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.07245810183936946</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.07245810183936946</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.5461423123656852</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>38.22996186559796</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>38.22996186559796</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45465.89583333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5393258426966292</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2359550561797753</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2247191011235955</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.05952380952380953</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.3797770002987284</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.2412557721298951</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3789672275713766</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.1595488423979008</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.1595488423979008</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.6202229997012716</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.048780487804879</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>43.41560997908901</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>43.41560997908901</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45465.89583333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.06060606060606055</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.3757201307377791</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3500274915414723</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.2742523777207485</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.0528512978336495</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.0528512978336495</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.6242798692622209</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>43.69959084835546</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>43.69959084835546</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45465.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5129935875801552</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2372595342558218</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2497468781640229</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.05369843527738261</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.2618796408719433</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3590715274375488</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3790488316905077</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1293019535264847</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1293019535264847</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.3790488316905077</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>26.53341821833554</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>26.53341821833554</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45465.9375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0.3670770600203078</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.4077433881239975</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.2251795518556948</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.1713797517603611</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="O25" t="n">
+        <v>0.3086285968254135</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.5316170522423062</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1597543509322801</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3210907364528325</v>
+      </c>
+      <c r="T25" t="n">
         <v>0</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.1713797517603611</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.4077433881239975</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="U25" t="n">
+        <v>0.3210907364528325</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.5316170522423062</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>37.21319365696143</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>37.21319365696143</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45465.9375</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I26" t="n">
         <v>4</v>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
-        </is>
-      </c>
-      <c r="Y14" t="n">
-        <v>28.54203716867982</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>28.54203716867982</v>
+      <c r="J26" t="n">
+        <v>0.550173120294781</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2160033035799371</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2338235761252819</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.06918217633473711</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.289341441372672</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.243865103015309</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.4667934556120188</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2329698794867369</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2329698794867369</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.4667934556120188</v>
+      </c>
+      <c r="W26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>32.67554189284132</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>32.67554189284132</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6880733944954128</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.1871559633027523</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1247706422018349</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.06862745098039214</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.6190558219313727</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.3026384164933133</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.07830576157531427</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.06901757256404017</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.06901757256404017</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.3809441780686273</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>26.66609246480391</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>26.66609246480391</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4295665634674923</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2554179566563468</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.315015479876161</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.05814905814905802</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.5205753914335942</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4044264527514825</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.07499815581492324</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.09100882796610194</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.09100882796610194</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.5205753914335942</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>36.4402774003516</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>36.4402774003516</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6045340050377834</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.23727959697733</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1581863979848867</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.05360934182590227</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.4209874955756275</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.4367556184360717</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.1422568859883006</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.1994760214587418</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.1994760214587418</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.4367556184360717</v>
+      </c>
+      <c r="W29" t="n">
+        <v>4</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>30.57289329052502</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>30.57289329052502</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3021,6 +3021,1238 @@
       </c>
       <c r="Z29" t="n">
         <v>30.57289329052502</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.6386964914272737</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.2100601794027478</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1512433291699784</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.0578978978978979</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.4436791468412699</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.3705221432445809</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1857987099141491</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-0.1950173445860038</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.1950173445860038</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.55632085315873</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.616279069767442</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>38.9424597211111</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>38.9424597211111</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.449677174325864</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.2552221800227877</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2951006456513482</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.05896074646074645</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.3319918150420605</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.282111876914261</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3858963080436785</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.09079566239233022</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.09079566239233022</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.3858963080436785</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>27.01274156305749</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>27.01274156305749</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6098357297414951</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2183014736949925</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1718627965635123</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.05792635435785254</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.5605383605228302</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.3535581894345236</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.08590345004264613</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-0.0492973692186649</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-0.0492973692186649</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.5605383605228302</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>39.23768523659812</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>39.23768523659812</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6018171661844011</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.2182108431661685</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.1799719906494304</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.05836574785251614</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4065117704358609</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.4180952329923648</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1753929965717745</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.1998843898261963</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.1998843898261963</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.4180952329923648</v>
+      </c>
+      <c r="W33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>29.26666630946553</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>29.26666630946553</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.05898156429801493</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.4336241512981688</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.3839572154861547</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.1824186332156764</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-0.1122160234211113</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.1122160234211113</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.5663758487018312</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.079231692677071</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>39.64630940912819</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>39.64630940912819</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.4518940673972829</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.361204355622729</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.1869015769799884</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-0.07442172207640124</v>
+      </c>
+      <c r="T35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.07442172207640124</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.5481059326027171</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>38.3674152821902</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>38.3674152821902</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.05898156429801493</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.3773370378645719</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.2414047650172821</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.3812581971181459</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.1631742474035144</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.1631742474035144</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.3812581971181459</v>
+      </c>
+      <c r="W36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>26.68807379827021</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>26.68807379827021</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.06060606060606055</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.3757201307377797</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.3500274915414737</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2742523777207464</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-0.05285129783364895</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.05285129783364895</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.6242798692622203</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>43.69959084835543</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>43.69959084835543</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.5129935875801552</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.2372595342558218</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2497468781640229</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.05369843527738261</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.3720081039411632</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.337583047308818</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.2904088487500189</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>-0.140985483638992</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.140985483638992</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.6279918960588368</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.948717948717949</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>43.95943272411857</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>43.95943272411857</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.3086285968254163</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.5316170522423029</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.1597543509322807</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.3210907364528293</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.3210907364528293</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.5316170522423029</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>37.2131936569612</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>37.2131936569612</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.550173120294781</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.2160033035799371</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.2338235761252819</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.06918217633473711</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.2928339855178089</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.2472243808527774</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.4599416336294134</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.2261180575041315</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.2261180575041315</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.4599416336294134</v>
+      </c>
+      <c r="W40" t="n">
+        <v>4</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>32.19591435405894</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>32.19591435405894</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.6880733944954128</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.1871559633027523</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1247706422018349</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.06862745098039214</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.6149171520084532</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.3027250780585539</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.0823577699329931</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-0.07315624248695962</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.07315624248695962</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.3850828479915468</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>26.95579935940827</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>26.95579935940827</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.4295665634674923</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.2554179566563468</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.315015479876161</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.05814905814905802</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.520575391433595</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.4044264527514819</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.07499815581492314</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.09100882796610271</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.09100882796610271</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.520575391433595</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>36.44027740035165</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>36.44027740035165</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>167</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.6045340050377834</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.23727959697733</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1581863979848867</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.05360934182590227</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.420987495575627</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.4367556184360714</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.1422568859883015</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.1994760214587414</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.1994760214587414</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.4367556184360714</v>
+      </c>
+      <c r="W43" t="n">
+        <v>4</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y43" t="n">
+        <v>30.572893290525</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>30.572893290525</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z43"/>
+  <dimension ref="A1:Z57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4255,6 +4255,1238 @@
         <v>30.572893290525</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>167</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6386964914272737</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.2100601794027478</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.1512433291699784</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.0578978978978979</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.4436791468412699</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.3705221432445809</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.1857987099141491</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>-0.1950173445860038</v>
+      </c>
+      <c r="T44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.1950173445860038</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.55632085315873</v>
+      </c>
+      <c r="W44" t="n">
+        <v>2.616279069767442</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y44" t="n">
+        <v>38.9424597211111</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>38.9424597211111</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>167</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.449677174325864</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.2552221800227877</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.2951006456513482</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.05896074646074645</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.3319918150420605</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.282111876914261</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.3858963080436785</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.09079566239233022</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.09079566239233022</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.3858963080436785</v>
+      </c>
+      <c r="W45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y45" t="n">
+        <v>27.01274156305749</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>27.01274156305749</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>167</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.6098357297414951</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.2183014736949925</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1718627965635123</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.05792635435785254</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.5605383605228302</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.3535581894345236</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.08590345004264613</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-0.0492973692186649</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-0.0492973692186649</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.5605383605228302</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y46" t="n">
+        <v>39.23768523659812</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>39.23768523659812</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>167</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.6018171661844011</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.2182108431661685</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1799719906494304</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.05836574785251614</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.4065117704358609</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.4180952329923648</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.1753929965717745</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.1998843898261963</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.1998843898261963</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.4180952329923648</v>
+      </c>
+      <c r="W47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y47" t="n">
+        <v>29.26666630946553</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>29.26666630946553</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>167</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.05898156429801493</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.4336241512981688</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.3839572154861547</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.1824186332156764</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-0.1122160234211113</v>
+      </c>
+      <c r="T48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.1122160234211113</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.5663758487018312</v>
+      </c>
+      <c r="W48" t="n">
+        <v>2.079231692677071</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y48" t="n">
+        <v>39.64630940912819</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>39.64630940912819</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>167</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.4518940673972829</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.361204355622729</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.1869015769799884</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>-0.07442172207640124</v>
+      </c>
+      <c r="T49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.07442172207640124</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.5481059326027171</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y49" t="n">
+        <v>38.3674152821902</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>38.3674152821902</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>167</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.05898156429801493</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.3773370378645719</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.2414047650172821</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.3812581971181459</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.1631742474035144</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.1631742474035144</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.3812581971181459</v>
+      </c>
+      <c r="W50" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y50" t="n">
+        <v>26.68807379827021</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>26.68807379827021</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>167</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.06060606060606055</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.3757201307377797</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.3500274915414737</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.2742523777207464</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>-0.05285129783364895</v>
+      </c>
+      <c r="T51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.05285129783364895</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.6242798692622203</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y51" t="n">
+        <v>43.69959084835543</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>43.69959084835543</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>167</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.5129935875801552</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.2372595342558218</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.2497468781640229</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.05369843527738261</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.3720081039411632</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.337583047308818</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.2904088487500189</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>-0.140985483638992</v>
+      </c>
+      <c r="T52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0.140985483638992</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.6279918960588368</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.948717948717949</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y52" t="n">
+        <v>43.95943272411857</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>43.95943272411857</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>167</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.3086285968254163</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.5316170522423029</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.1597543509322807</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.3210907364528293</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.3210907364528293</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.5316170522423029</v>
+      </c>
+      <c r="W53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y53" t="n">
+        <v>37.2131936569612</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>37.2131936569612</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>167</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.550173120294781</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.2160033035799371</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.2338235761252819</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.06918217633473711</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.2928339855178089</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.2472243808527774</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.4599416336294134</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.2261180575041315</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.2261180575041315</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.4599416336294134</v>
+      </c>
+      <c r="W54" t="n">
+        <v>4</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y54" t="n">
+        <v>32.19591435405894</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>32.19591435405894</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>167</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.6880733944954128</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.1871559633027523</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1247706422018349</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.06862745098039214</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.6125718165728418</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.3031664238939512</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.0842617595332071</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-0.07550157792257106</v>
+      </c>
+      <c r="T55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.07550157792257106</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.3874281834271582</v>
+      </c>
+      <c r="W55" t="n">
+        <v>3</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y55" t="n">
+        <v>27.11997283990108</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>27.11997283990108</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>167</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.4295665634674923</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.2554179566563468</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.315015479876161</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.05814905814905802</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.520575391433595</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.4044264527514819</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.07499815581492314</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.09100882796610271</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.09100882796610271</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.520575391433595</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y56" t="n">
+        <v>36.44027740035165</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>36.44027740035165</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>167</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>6</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.6045340050377834</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.23727959697733</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1581863979848867</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.05360934182590227</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.420987495575627</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.4367556184360714</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.1422568859883015</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.1994760214587414</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0.1994760214587414</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.4367556184360714</v>
+      </c>
+      <c r="W57" t="n">
+        <v>4</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y57" t="n">
+        <v>30.572893290525</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>30.572893290525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -849,66 +849,66 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="n">
         <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6018171661844011</v>
+        <v>0.5888816959792844</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2182108431661685</v>
+        <v>0.2203206345234275</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1799719906494304</v>
+        <v>0.1907976694972882</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05836574785251614</v>
+        <v>0.0482308328343739</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4065117704358609</v>
+        <v>0.4061314979160774</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4180952329923648</v>
+        <v>0.3980054538324055</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1753929965717745</v>
+        <v>0.1958630482515173</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1998843898261963</v>
+        <v>-0.182750198063207</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1998843898261963</v>
+        <v>0.182750198063207</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4180952329923648</v>
+        <v>0.5938685020839225</v>
       </c>
       <c r="W5" t="n">
-        <v>4.33</v>
+        <v>2.320471596998928</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>29.26666630946553</v>
+        <v>41.57079514587458</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.26666630946553</v>
+        <v>41.57079514587458</v>
       </c>
     </row>
     <row r="6">
@@ -961,28 +961,28 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4336241512981688</v>
+        <v>0.4342780967767457</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3839572154861547</v>
+        <v>0.3880867595947963</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1824186332156764</v>
+        <v>0.1776351436284577</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1122160234211113</v>
+        <v>-0.1115620779425343</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1122160234211113</v>
+        <v>0.1115620779425343</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5663758487018312</v>
+        <v>0.5657219032232543</v>
       </c>
       <c r="W6" t="n">
         <v>2.079231692677071</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>39.64630940912819</v>
+        <v>39.6005332256278</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.64630940912819</v>
+        <v>39.6005332256278</v>
       </c>
     </row>
     <row r="7">
@@ -1025,66 +1025,66 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.4998268098372012</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2435053688950468</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2566678212677519</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05299631615421085</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4536949757806798</v>
+        <v>0.4518940673972829</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3438612530005293</v>
+        <v>0.361204355622729</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2024437712187911</v>
+        <v>0.1869015769799884</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07262081369300438</v>
+        <v>-0.0479327424399183</v>
       </c>
       <c r="T7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07262081369300438</v>
+        <v>-0.0479327424399183</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463050242193201</v>
+        <v>0.4518940673972829</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>38.24135169535241</v>
+        <v>31.63258471780981</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.24135169535241</v>
+        <v>31.63258471780981</v>
       </c>
     </row>
     <row r="8">
@@ -1201,25 +1201,25 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="H9" t="n">
         <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.4192972007147112</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.2858844550327576</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.2948183442525313</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06060606060606055</v>
+        <v>0.0599747474747474</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -1237,30 +1237,30 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.05285129783364895</v>
+        <v>-0.0435770699769315</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05285129783364895</v>
+        <v>-0.0435770699769315</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6242798692622203</v>
+        <v>0.3757201307377797</v>
       </c>
       <c r="W9" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>43.69959084835543</v>
+        <v>26.30040915164458</v>
       </c>
       <c r="Z9" t="n">
-        <v>43.69959084835543</v>
+        <v>26.30040915164458</v>
       </c>
     </row>
     <row r="10">
@@ -1310,45 +1310,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.261879640871944</v>
+        <v>0.3720081039411632</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3590715274375495</v>
+        <v>0.337583047308818</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3790488316905065</v>
+        <v>0.2904088487500189</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1293019535264836</v>
+        <v>-0.140985483638992</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1293019535264836</v>
+        <v>0.140985483638992</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3790488316905065</v>
+        <v>0.6279918960588368</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>1.948717948717949</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>26.53341821833546</v>
+        <v>43.95943272411857</v>
       </c>
       <c r="Z10" t="n">
-        <v>26.53341821833546</v>
+        <v>43.95943272411857</v>
       </c>
     </row>
     <row r="11">
@@ -1377,25 +1377,25 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6543046357615894</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1997350993377483</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1459602649006622</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05402764204942079</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1413,19 +1413,19 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3210907364528293</v>
+        <v>0.3318819529045546</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3210907364528293</v>
+        <v>0.3318819529045546</v>
       </c>
       <c r="V11" t="n">
         <v>0.5316170522423029</v>
       </c>
       <c r="W11" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1465,25 +1465,25 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="H12" t="n">
         <v>4.33</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.550173120294781</v>
+        <v>0.5362840799830516</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2160033035799371</v>
+        <v>0.2167429884458061</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2338235761252819</v>
+        <v>0.2469729315711422</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06918217633473711</v>
+        <v>0.06553334838250358</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2261180575041315</v>
+        <v>0.2129687020582712</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2261180575041315</v>
+        <v>0.2129687020582712</v>
       </c>
       <c r="V12" t="n">
         <v>0.4599416336294134</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1556,19 +1556,19 @@
         <v>1.36</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>0.6880733944954128</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1871559633027523</v>
+        <v>0.1782437745740498</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1247706422018349</v>
+        <v>0.1336828309305373</v>
       </c>
       <c r="M13" t="n">
         <v>0.06862745098039214</v>
@@ -1577,28 +1577,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6144560676244835</v>
+        <v>0.6171776308469605</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3028120818651876</v>
+        <v>0.3042189688659127</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08273185051032889</v>
+        <v>0.07860340028712649</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07361732687092937</v>
+        <v>-0.07089576364845229</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07361732687092937</v>
+        <v>0.07089576364845229</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3855439323755165</v>
+        <v>0.3828223691530395</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.98807526628616</v>
+        <v>26.79756584071276</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.98807526628616</v>
+        <v>26.79756584071276</v>
       </c>
     </row>
     <row r="14">
@@ -1729,25 +1729,25 @@
         <v>1671</v>
       </c>
       <c r="G15" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6045340050377834</v>
+        <v>0.6538661131292164</v>
       </c>
       <c r="K15" t="n">
-        <v>0.23727959697733</v>
+        <v>0.210690192008303</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1581863979848867</v>
+        <v>0.1354436948624805</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05360934182590227</v>
+        <v>0.05473453749315826</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1765,19 +1765,19 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1994760214587414</v>
+        <v>0.2260654264277684</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1994760214587414</v>
+        <v>0.2260654264277684</v>
       </c>
       <c r="V15" t="n">
         <v>0.4367556184360714</v>
       </c>
       <c r="W15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1310,45 +1310,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3720081039411632</v>
+        <v>0.261879640871944</v>
       </c>
       <c r="P10" t="n">
-        <v>0.337583047308818</v>
+        <v>0.3590715274375495</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2904088487500189</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="T10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6279918960588368</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="W10" t="n">
-        <v>1.948717948717949</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
       <c r="Z10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
     </row>
     <row r="11">
@@ -1577,28 +1577,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6171776308469605</v>
+        <v>0.6145717138326878</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3042189688659127</v>
+        <v>0.3027902689485072</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07860340028712649</v>
+        <v>0.08263801721880513</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07089576364845229</v>
+        <v>-0.073501680662725</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07089576364845229</v>
+        <v>0.073501680662725</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3828223691530395</v>
+        <v>0.3854282861673122</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.79756584071276</v>
+        <v>26.97998003171185</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.79756584071276</v>
+        <v>26.97998003171185</v>
       </c>
     </row>
     <row r="14">
@@ -1789,6 +1789,1842 @@
       </c>
       <c r="Z15" t="n">
         <v>30.572893290525</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2462720620015046</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.4923339539454937</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2613939840530014</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.5076660460545063</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>35.53662322381544</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>35.53662322381544</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4486050669888325</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4047008090404339</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1466941239707336</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.5513949330111676</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>38.59764531078173</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>38.59764531078173</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.3145692862666382</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4692743552439834</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2161563584893785</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.5307256447560167</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>37.15079513292117</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>37.15079513292117</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3395212219234734</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.2837467714942478</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3767320065822789</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.6232679934177211</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>43.62875953924048</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>43.62875953924048</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.319004676081902</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.4197691100698566</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2612262138482416</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.5802308899301434</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>40.61616229511004</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>40.61616229511004</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3468466868897144</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.3604566226280601</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2926966904822257</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.6395433773719399</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>44.76803641603579</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>44.76803641603579</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.352099940595717</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.4534281625400888</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.194471896864194</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.5465718374599111</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>38.26002862219378</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>38.26002862219378</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.1884751250500326</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.2882272408643515</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.5232976340856157</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.4767023659143843</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>33.3691656140069</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>33.3691656140069</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4491415382196292</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3649273122968265</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1859311494835444</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.5508584617803708</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>38.56009232462596</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>38.56009232462596</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5262868708033219</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3324678315859552</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1412452976107228</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0.4737131291966781</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>33.15991904376747</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>33.15991904376747</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.603789322280942</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.3291009915269105</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.06710968619214784</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.396210677719058</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>27.73474744033406</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>27.73474744033406</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.3410847389107385</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.4719125839273521</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.1870026771619094</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>0.5280874160726479</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>36.96611912508535</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>36.96611912508535</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.458906160045076</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4271192785075237</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.1139745614474004</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>0.5410938399549241</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>37.87656879684469</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>37.87656879684469</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.4542204032452292</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.3865699443481483</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.1592096524066227</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.5457795967547708</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>38.20457177283396</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>38.20457177283396</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.5050016708574175</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.3849675921712908</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1100307369712915</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>0.4949983291425825</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>34.64988303998077</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>34.64988303998077</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.182866834220039</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.2334437671118067</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.5836893986681545</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>0.4163106013318455</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>29.14174209322918</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>29.14174209322918</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.2902861035528271</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.33017548571028</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3795384107368928</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.6204615892631072</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>43.43231124841751</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>43.43231124841751</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4444862769605148</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.3738661777520266</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1816475452874586</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0.5555137230394852</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>38.88596061276397</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>38.88596061276397</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.1556738986571048</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.4360717482454501</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4082543530974453</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.5639282517545499</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>39.47497762281849</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>39.47497762281849</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.2291534607267637</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.361229768531829</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.4096167707414073</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>0.5903832292585927</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>41.32682604810149</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>41.32682604810149</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.4395550098211475</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.4157662140662979</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.1446787761125546</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0.5604449901788525</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>39.23114931251968</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>39.23114931251968</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.3588073437515735</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.3478863234417136</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2933063328067126</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0.6411926562484265</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>44.88348593738985</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>44.88348593738985</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.4478269336701768</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.3227439799731163</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.2294290863567066</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0.5521730663298232</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>38.65211464308763</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>38.65211464308763</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.3640386993361091</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.3611765105361796</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.2747847901277112</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0.6359613006638909</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>44.51729104647237</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>44.51729104647237</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.3336436547157847</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.4931748276163314</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1731815176678841</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0.5068251723836686</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>35.4777620668568</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>35.4777620668568</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.3032410599203441</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.4777524411613178</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.219006498918338</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>0.5222475588386822</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>36.55732911870776</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>36.55732911870776</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.3204829122770161</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.4160459857279659</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.2634711019950181</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>0.5839540142720341</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>40.87678099904239</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>40.87678099904239</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -562,20 +562,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45471.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -584,86 +584,66 @@
       <c r="F2" t="n">
         <v>1671</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6386964914272737</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.2100601794027478</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.1512433291699784</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.0578978978978979</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4436791468412699</v>
+        <v>0.2462720620015046</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3705221432445809</v>
+        <v>0.4923339539454937</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1857987099141491</v>
+        <v>0.2613939840530014</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>-0.1950173445860038</v>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1950173445860038</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.55632085315873</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.616279069767442</v>
-      </c>
+        <v>0.5076660460545063</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>38.9424597211111</v>
+        <v>35.53662322381544</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.9424597211111</v>
+        <v>35.53662322381544</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -672,86 +652,66 @@
       <c r="F3" t="n">
         <v>1671</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.449677174325864</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.2552221800227877</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.2951006456513482</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.05896074646074645</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3319918150420605</v>
+        <v>0.4486050669888325</v>
       </c>
       <c r="P3" t="n">
-        <v>0.282111876914261</v>
+        <v>0.4047008090404339</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3858963080436785</v>
+        <v>0.1466941239707336</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
-        <v>0.09079566239233022</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.09079566239233022</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3858963080436785</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.2</v>
-      </c>
+        <v>0.5513949330111676</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>27.01274156305749</v>
+        <v>38.59764531078173</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.01274156305749</v>
+        <v>38.59764531078173</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -760,86 +720,66 @@
       <c r="F4" t="n">
         <v>1671</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6098357297414951</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2183014736949925</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1718627965635123</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.05792635435785254</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5605383605228302</v>
+        <v>0.3145692862666382</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3535581894345236</v>
+        <v>0.4692743552439834</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08590345004264613</v>
+        <v>0.2161563584893785</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
-        <v>-0.0492973692186649</v>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.0492973692186649</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5605383605228302</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.55</v>
-      </c>
+        <v>0.5307256447560167</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>39.23768523659812</v>
+        <v>37.15079513292117</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.23768523659812</v>
+        <v>37.15079513292117</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -848,86 +788,66 @@
       <c r="F5" t="n">
         <v>1671</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5888816959792844</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.2203206345234275</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.1907976694972882</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.0482308328343739</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4061314979160774</v>
+        <v>0.3395212219234734</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3980054538324055</v>
+        <v>0.2837467714942478</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1958630482515173</v>
+        <v>0.3767320065822789</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
-        <v>-0.182750198063207</v>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.182750198063207</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5938685020839225</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.320471596998928</v>
-      </c>
+        <v>0.6232679934177211</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>41.57079514587458</v>
+        <v>43.62875953924048</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.57079514587458</v>
+        <v>43.62875953924048</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -936,86 +856,66 @@
       <c r="F6" t="n">
         <v>1671</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.54584017471928</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.2360758755660886</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.2180839497146315</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.05898156429801493</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4342780967767457</v>
+        <v>0.319004676081902</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3880867595947963</v>
+        <v>0.4197691100698566</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1776351436284577</v>
+        <v>0.2612262138482416</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>-0.1115620779425343</v>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1115620779425343</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5657219032232543</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.079231692677071</v>
-      </c>
+        <v>0.5802308899301434</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>39.6005332256278</v>
+        <v>40.61616229511004</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6005332256278</v>
+        <v>40.61616229511004</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45473.02083333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1024,86 +924,66 @@
       <c r="F7" t="n">
         <v>1671</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.4998268098372012</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.2435053688950468</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.2566678212677519</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.05299631615421085</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4518940673972829</v>
+        <v>0.3468466868897144</v>
       </c>
       <c r="P7" t="n">
-        <v>0.361204355622729</v>
+        <v>0.3604566226280601</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1869015769799884</v>
+        <v>0.2926966904822257</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
-        <v>-0.0479327424399183</v>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.0479327424399183</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4518940673972829</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.9</v>
-      </c>
+        <v>0.6395433773719399</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>31.63258471780981</v>
+        <v>44.76803641603579</v>
       </c>
       <c r="Z7" t="n">
-        <v>31.63258471780981</v>
+        <v>44.76803641603579</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45473.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1112,77 +992,57 @@
       <c r="F8" t="n">
         <v>1671</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.54584017471928</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.2360758755660886</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.2180839497146315</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.05898156429801493</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3773370378645719</v>
+        <v>0.352099940595717</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2414047650172821</v>
+        <v>0.4534281625400888</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3812581971181459</v>
+        <v>0.194471896864194</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
-        <v>0.1631742474035144</v>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.1631742474035144</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3812581971181459</v>
-      </c>
-      <c r="W8" t="n">
-        <v>4.33</v>
-      </c>
+        <v>0.5465718374599111</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>26.68807379827021</v>
+        <v>38.26002862219378</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.68807379827021</v>
+        <v>38.26002862219378</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45473.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1191,7 +1051,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1200,86 +1060,66 @@
       <c r="F9" t="n">
         <v>1671</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.4192972007147112</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2858844550327576</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.2948183442525313</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.0599747474747474</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3757201307377797</v>
+        <v>0.1884751250500326</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3500274915414737</v>
+        <v>0.2882272408643515</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2742523777207464</v>
+        <v>0.5232976340856157</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
-        <v>-0.0435770699769315</v>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.0435770699769315</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3757201307377797</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.25</v>
-      </c>
+        <v>0.4767023659143843</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>26.30040915164458</v>
+        <v>33.3691656140069</v>
       </c>
       <c r="Z9" t="n">
-        <v>26.30040915164458</v>
+        <v>33.3691656140069</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45473.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1288,174 +1128,134 @@
       <c r="F10" t="n">
         <v>1671</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5129935875801552</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2372595342558218</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.2497468781640229</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.05369843527738261</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.261879640871944</v>
+        <v>0.4491415382196292</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3590715274375495</v>
+        <v>0.3649273122968265</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3790488316905065</v>
+        <v>0.1859311494835444</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
-        <v>0.1293019535264836</v>
-      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.1293019535264836</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3790488316905065</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.8</v>
-      </c>
+        <v>0.5508584617803708</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>26.53341821833546</v>
+        <v>38.56009232462596</v>
       </c>
       <c r="Z10" t="n">
-        <v>26.53341821833546</v>
+        <v>38.56009232462596</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>colorado rapids</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cf montreal</t>
-        </is>
-      </c>
       <c r="E11" t="n">
         <v>167</v>
       </c>
       <c r="F11" t="n">
         <v>1671</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.6543046357615894</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.1997350993377483</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.1459602649006622</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.05402764204942079</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3086285968254163</v>
+        <v>0.5262868708033219</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5316170522423029</v>
+        <v>0.3324678315859552</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1597543509322807</v>
+        <v>0.1412452976107228</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
-        <v>0.3318819529045546</v>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.3318819529045546</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5316170522423029</v>
-      </c>
-      <c r="W11" t="n">
-        <v>4.75</v>
-      </c>
+        <v>0.4737131291966781</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>37.2131936569612</v>
+        <v>33.15991904376747</v>
       </c>
       <c r="Z11" t="n">
-        <v>37.2131936569612</v>
+        <v>33.15991904376747</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1464,86 +1264,66 @@
       <c r="F12" t="n">
         <v>1671</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.5362840799830516</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.2167429884458061</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.2469729315711422</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.06553334838250358</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2928339855178089</v>
+        <v>0.603789322280942</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2472243808527774</v>
+        <v>0.3291009915269105</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4599416336294134</v>
+        <v>0.06710968619214784</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
-        <v>0.2129687020582712</v>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.2129687020582712</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4599416336294134</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.8</v>
-      </c>
+        <v>0.396210677719058</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>32.19591435405894</v>
+        <v>27.73474744033406</v>
       </c>
       <c r="Z12" t="n">
-        <v>32.19591435405894</v>
+        <v>27.73474744033406</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1552,86 +1332,66 @@
       <c r="F13" t="n">
         <v>1671</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.6880733944954128</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.1782437745740498</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.1336828309305373</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.06862745098039214</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6145717138326878</v>
+        <v>0.3410847389107385</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3027902689485072</v>
+        <v>0.4719125839273521</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08263801721880513</v>
+        <v>0.1870026771619094</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
-        <v>-0.073501680662725</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.073501680662725</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3854282861673122</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3</v>
-      </c>
+        <v>0.5280874160726479</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.97998003171185</v>
+        <v>36.96611912508535</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.97998003171185</v>
+        <v>36.96611912508535</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1640,86 +1400,66 @@
       <c r="F14" t="n">
         <v>1671</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.4295665634674923</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2554179566563468</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.315015479876161</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.05814905814905802</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.520575391433595</v>
+        <v>0.458906160045076</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4044264527514819</v>
+        <v>0.4271192785075237</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07499815581492314</v>
+        <v>0.1139745614474004</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
-        <v>0.09100882796610271</v>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.09100882796610271</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.520575391433595</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.2</v>
-      </c>
+        <v>0.5410938399549241</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>36.44027740035165</v>
+        <v>37.87656879684469</v>
       </c>
       <c r="Z14" t="n">
-        <v>36.44027740035165</v>
+        <v>37.87656879684469</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1728,86 +1468,66 @@
       <c r="F15" t="n">
         <v>1671</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.6538661131292164</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.210690192008303</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.1354436948624805</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.05473453749315826</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.420987495575627</v>
+        <v>0.4542204032452292</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4367556184360714</v>
+        <v>0.3865699443481483</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1422568859883015</v>
+        <v>0.1592096524066227</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
-        <v>0.2260654264277684</v>
-      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.2260654264277684</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4367556184360714</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.5</v>
-      </c>
+        <v>0.5457795967547708</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>30.572893290525</v>
+        <v>38.20457177283396</v>
       </c>
       <c r="Z15" t="n">
-        <v>30.572893290525</v>
+        <v>38.20457177283396</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>W0zNyInr</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45471.97916666666</v>
+        <v>45476.9375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1824,27 +1544,27 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2462720620015046</v>
+        <v>0.5050016708574175</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4923339539454937</v>
+        <v>0.3849675921712908</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2613939840530014</v>
+        <v>0.1100307369712915</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5076660460545063</v>
+        <v>0.4949983291425825</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
@@ -1853,29 +1573,29 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>35.53662322381544</v>
+        <v>34.64988303998077</v>
       </c>
       <c r="Z16" t="n">
-        <v>35.53662322381544</v>
+        <v>34.64988303998077</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1892,27 +1612,27 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4486050669888325</v>
+        <v>0.182866834220039</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4047008090404339</v>
+        <v>0.2334437671118067</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1466941239707336</v>
+        <v>0.5836893986681545</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5513949330111676</v>
+        <v>0.4163106013318455</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
@@ -1921,29 +1641,29 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>38.59764531078173</v>
+        <v>29.14174209322918</v>
       </c>
       <c r="Z17" t="n">
-        <v>38.59764531078173</v>
+        <v>29.14174209322918</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1960,27 +1680,27 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3145692862666382</v>
+        <v>0.2902861035528271</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4692743552439834</v>
+        <v>0.33017548571028</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2161563584893785</v>
+        <v>0.3795384107368928</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5307256447560167</v>
+        <v>0.6204615892631072</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
@@ -1989,29 +1709,29 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>37.15079513292117</v>
+        <v>43.43231124841751</v>
       </c>
       <c r="Z18" t="n">
-        <v>37.15079513292117</v>
+        <v>43.43231124841751</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2028,27 +1748,27 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3395212219234734</v>
+        <v>0.4444862769605148</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2837467714942478</v>
+        <v>0.3738661777520266</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3767320065822789</v>
+        <v>0.1816475452874586</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.6232679934177211</v>
+        <v>0.5555137230394852</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
@@ -2057,29 +1777,29 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>43.62875953924048</v>
+        <v>38.88596061276397</v>
       </c>
       <c r="Z19" t="n">
-        <v>43.62875953924048</v>
+        <v>38.88596061276397</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2099,13 +1819,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.319004676081902</v>
+        <v>0.1556738986571048</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4197691100698566</v>
+        <v>0.4360717482454501</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2612262138482416</v>
+        <v>0.4082543530974453</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2116,7 +1836,7 @@
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.5802308899301434</v>
+        <v>0.5639282517545499</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
@@ -2125,29 +1845,29 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>40.61616229511004</v>
+        <v>39.47497762281849</v>
       </c>
       <c r="Z20" t="n">
-        <v>40.61616229511004</v>
+        <v>39.47497762281849</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>vRwVZeHf</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45476.98958333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2164,27 +1884,27 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3468466868897144</v>
+        <v>0.2291534607267637</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3604566226280601</v>
+        <v>0.361229768531829</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2926966904822257</v>
+        <v>0.4096167707414073</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.6395433773719399</v>
+        <v>0.5903832292585927</v>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
@@ -2193,29 +1913,29 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>44.76803641603579</v>
+        <v>41.32682604810149</v>
       </c>
       <c r="Z21" t="n">
-        <v>44.76803641603579</v>
+        <v>41.32682604810149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>IHxZYFW0</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2232,27 +1952,27 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.352099940595717</v>
+        <v>0.4395550098211475</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4534281625400888</v>
+        <v>0.4157662140662979</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.194471896864194</v>
+        <v>0.1446787761125546</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.5465718374599111</v>
+        <v>0.5604449901788525</v>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
@@ -2261,29 +1981,29 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>38.26002862219378</v>
+        <v>39.23114931251968</v>
       </c>
       <c r="Z22" t="n">
-        <v>38.26002862219378</v>
+        <v>39.23114931251968</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2300,27 +2020,27 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1884751250500326</v>
+        <v>0.3588073437515735</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2882272408643515</v>
+        <v>0.3478863234417136</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5232976340856157</v>
+        <v>0.2933063328067126</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.4767023659143843</v>
+        <v>0.6411926562484265</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
@@ -2329,29 +2049,29 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>33.3691656140069</v>
+        <v>44.88348593738985</v>
       </c>
       <c r="Z23" t="n">
-        <v>33.3691656140069</v>
+        <v>44.88348593738985</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2371,13 +2091,13 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4491415382196292</v>
+        <v>0.4478269336701768</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3649273122968265</v>
+        <v>0.3227439799731163</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1859311494835444</v>
+        <v>0.2294290863567066</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2388,7 +2108,7 @@
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.5508584617803708</v>
+        <v>0.5521730663298232</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
@@ -2397,29 +2117,29 @@
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>38.56009232462596</v>
+        <v>38.65211464308763</v>
       </c>
       <c r="Z24" t="n">
-        <v>38.56009232462596</v>
+        <v>38.65211464308763</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>OU7ZWg1D</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45477.0625</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2439,13 +2159,13 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5262868708033219</v>
+        <v>0.3640386993361091</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3324678315859552</v>
+        <v>0.3611765105361796</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1412452976107228</v>
+        <v>0.2747847901277112</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2456,7 +2176,7 @@
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.4737131291966781</v>
+        <v>0.6359613006638909</v>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
@@ -2465,29 +2185,29 @@
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>33.15991904376747</v>
+        <v>44.51729104647237</v>
       </c>
       <c r="Z25" t="n">
-        <v>33.15991904376747</v>
+        <v>44.51729104647237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>xYeHewvE</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45478.02083333334</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>minnesota united</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2504,27 +2224,27 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0.603789322280942</v>
+        <v>0.3336436547157847</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3291009915269105</v>
+        <v>0.4931748276163314</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.06710968619214784</v>
+        <v>0.1731815176678841</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.396210677719058</v>
+        <v>0.5068251723836686</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
@@ -2533,29 +2253,29 @@
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>27.73474744033406</v>
+        <v>35.4777620668568</v>
       </c>
       <c r="Z26" t="n">
-        <v>27.73474744033406</v>
+        <v>35.4777620668568</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>jy0LfcgK</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45478.0625</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2575,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3410847389107385</v>
+        <v>0.3032410599203441</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4719125839273521</v>
+        <v>0.4777524411613178</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1870026771619094</v>
+        <v>0.219006498918338</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2592,7 +2312,7 @@
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.5280874160726479</v>
+        <v>0.5222475588386822</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
@@ -2601,29 +2321,29 @@
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>36.96611912508535</v>
+        <v>36.55732911870776</v>
       </c>
       <c r="Z27" t="n">
-        <v>36.96611912508535</v>
+        <v>36.55732911870776</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>YakQgH8Q</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45478.10416666666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2640,27 +2360,27 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0.458906160045076</v>
+        <v>0.3204829122770161</v>
       </c>
       <c r="P28" t="n">
-        <v>0.4271192785075237</v>
+        <v>0.4160459857279659</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1139745614474004</v>
+        <v>0.2634711019950181</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="n">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.5410938399549241</v>
+        <v>0.5839540142720341</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
@@ -2669,29 +2389,29 @@
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>37.87656879684469</v>
+        <v>40.87678099904239</v>
       </c>
       <c r="Z28" t="n">
-        <v>37.87656879684469</v>
+        <v>40.87678099904239</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2700,66 +2420,86 @@
       <c r="F29" t="n">
         <v>1671</v>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6386964914272737</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.2100601794027478</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1512433291699784</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.0578978978978979</v>
+      </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.4542204032452292</v>
+        <v>0.442947785562681</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3865699443481483</v>
+        <v>0.3696567110004065</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1592096524066227</v>
+        <v>0.1873955034369123</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>-0.1957487058645927</v>
+      </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>0.1957487058645927</v>
+      </c>
       <c r="V29" t="n">
-        <v>0.5457795967547708</v>
-      </c>
-      <c r="W29" t="inlineStr"/>
+        <v>0.557052214437319</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.616279069767442</v>
+      </c>
       <c r="X29" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>38.20457177283396</v>
+        <v>38.99365501061233</v>
       </c>
       <c r="Z29" t="n">
-        <v>38.20457177283396</v>
+        <v>38.99365501061233</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>W0zNyInr</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45476.9375</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2768,66 +2508,86 @@
       <c r="F30" t="n">
         <v>1671</v>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.449677174325864</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.2552221800227877</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.2951006456513482</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.05896074646074645</v>
+      </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0.5050016708574175</v>
+        <v>0.330849415970903</v>
       </c>
       <c r="P30" t="n">
-        <v>0.3849675921712908</v>
+        <v>0.2884875394026187</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1100307369712915</v>
+        <v>0.3806630446264782</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>0.08556239897512991</v>
+      </c>
       <c r="T30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U30" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.08556239897512991</v>
+      </c>
       <c r="V30" t="n">
-        <v>0.4949983291425825</v>
-      </c>
-      <c r="W30" t="inlineStr"/>
+        <v>0.3806630446264782</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.2</v>
+      </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>34.64988303998077</v>
+        <v>26.64641312385347</v>
       </c>
       <c r="Z30" t="n">
-        <v>34.64988303998077</v>
+        <v>26.64641312385347</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>QJcftbvR</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2836,66 +2596,86 @@
       <c r="F31" t="n">
         <v>1671</v>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6098357297414951</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.2183014736949925</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.1718627965635123</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.05792635435785254</v>
+      </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.182866834220039</v>
+        <v>0.5622116073024658</v>
       </c>
       <c r="P31" t="n">
-        <v>0.2334437671118067</v>
+        <v>0.3421246695652593</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.5836893986681545</v>
+        <v>0.09566372313227506</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>-0.04762412243902936</v>
+      </c>
       <c r="T31" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-0.04762412243902936</v>
+      </c>
       <c r="V31" t="n">
-        <v>0.4163106013318455</v>
-      </c>
-      <c r="W31" t="inlineStr"/>
+        <v>0.5622116073024658</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.55</v>
+      </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>29.14174209322918</v>
+        <v>39.3548125111726</v>
       </c>
       <c r="Z31" t="n">
-        <v>29.14174209322918</v>
+        <v>39.3548125111726</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>p4vRzx2l</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2904,66 +2684,86 @@
       <c r="F32" t="n">
         <v>1671</v>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5888816959792844</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2203206345234275</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1907976694972882</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.0482308328343739</v>
+      </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.2902861035528271</v>
+        <v>0.4064097840638316</v>
       </c>
       <c r="P32" t="n">
-        <v>0.33017548571028</v>
+        <v>0.406249628466087</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.3795384107368928</v>
+        <v>0.1873405874700815</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>-0.1824719119154528</v>
+      </c>
       <c r="T32" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.1824719119154528</v>
+      </c>
       <c r="V32" t="n">
-        <v>0.6204615892631072</v>
-      </c>
-      <c r="W32" t="inlineStr"/>
+        <v>0.5935902159361683</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.320471596998928</v>
+      </c>
       <c r="X32" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>43.43231124841751</v>
+        <v>41.55131511553179</v>
       </c>
       <c r="Z32" t="n">
-        <v>43.43231124841751</v>
+        <v>41.55131511553179</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>88KCueOd</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2972,66 +2772,86 @@
       <c r="F33" t="n">
         <v>1671</v>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.05898156429801493</v>
+      </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0.4444862769605148</v>
+        <v>0.431972689407671</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3738661777520266</v>
+        <v>0.3757237719572734</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1816475452874586</v>
+        <v>0.1923035386350555</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>-0.113867485311609</v>
+      </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>0.113867485311609</v>
+      </c>
       <c r="V33" t="n">
-        <v>0.5555137230394852</v>
-      </c>
-      <c r="W33" t="inlineStr"/>
+        <v>0.568027310592329</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.079231692677071</v>
+      </c>
       <c r="X33" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>38.88596061276397</v>
+        <v>39.76191174146303</v>
       </c>
       <c r="Z33" t="n">
-        <v>38.88596061276397</v>
+        <v>39.76191174146303</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>naJGvFw3</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3040,66 +2860,86 @@
       <c r="F34" t="n">
         <v>1671</v>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.4998268098372012</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.2435053688950468</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.2566678212677519</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.05299631615421085</v>
+      </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1556738986571048</v>
+        <v>0.4352110096174183</v>
       </c>
       <c r="P34" t="n">
-        <v>0.4360717482454501</v>
+        <v>0.4322347323892172</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.4082543530974453</v>
+        <v>0.1325542579933644</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>-0.06461580021978297</v>
+      </c>
       <c r="T34" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U34" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.06461580021978297</v>
+      </c>
       <c r="V34" t="n">
-        <v>0.5639282517545499</v>
-      </c>
-      <c r="W34" t="inlineStr"/>
+        <v>0.5647889903825818</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.898684210526316</v>
+      </c>
       <c r="X34" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>39.47497762281849</v>
+        <v>39.53522932678072</v>
       </c>
       <c r="Z34" t="n">
-        <v>39.47497762281849</v>
+        <v>39.53522932678072</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>vRwVZeHf</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45476.98958333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3108,66 +2948,86 @@
       <c r="F35" t="n">
         <v>1671</v>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.05898156429801493</v>
+      </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.2291534607267637</v>
+        <v>0.4585357639156413</v>
       </c>
       <c r="P35" t="n">
-        <v>0.361229768531829</v>
+        <v>0.3362499079698303</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4096167707414073</v>
+        <v>0.2052143281145281</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>-0.08730441080363877</v>
+      </c>
       <c r="T35" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.08730441080363877</v>
+      </c>
       <c r="V35" t="n">
-        <v>0.5903832292585927</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
+        <v>0.5414642360843587</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.079231692677071</v>
+      </c>
       <c r="X35" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>41.32682604810149</v>
+        <v>37.90249652590511</v>
       </c>
       <c r="Z35" t="n">
-        <v>41.32682604810149</v>
+        <v>37.90249652590511</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>IHxZYFW0</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3176,66 +3036,86 @@
       <c r="F36" t="n">
         <v>1671</v>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.4192972007147112</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.2858844550327576</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2948183442525313</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.0599747474747474</v>
+      </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.4395550098211475</v>
+        <v>0.3762812603021553</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4157662140662979</v>
+        <v>0.3362450625534014</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.1446787761125546</v>
+        <v>0.2874736771444432</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>-0.04301594041255591</v>
+      </c>
       <c r="T36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-0.04301594041255591</v>
+      </c>
       <c r="V36" t="n">
-        <v>0.5604449901788525</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
+        <v>0.3762812603021553</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.25</v>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>39.23114931251968</v>
+        <v>26.33968822115087</v>
       </c>
       <c r="Z36" t="n">
-        <v>39.23114931251968</v>
+        <v>26.33968822115087</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>UN8LwZh9</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3244,66 +3124,86 @@
       <c r="F37" t="n">
         <v>1671</v>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.5129935875801552</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.2372595342558218</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2497468781640229</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.05369843527738261</v>
+      </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.3588073437515735</v>
+        <v>0.2433648073553128</v>
       </c>
       <c r="P37" t="n">
-        <v>0.3478863234417136</v>
+        <v>0.3403588267448442</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2933063328067126</v>
+        <v>0.4162763658998431</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
       </c>
-      <c r="S37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>0.1665294877358202</v>
+      </c>
       <c r="T37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.1665294877358202</v>
+      </c>
       <c r="V37" t="n">
-        <v>0.6411926562484265</v>
-      </c>
-      <c r="W37" t="inlineStr"/>
+        <v>0.4162763658998431</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.8</v>
+      </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>44.88348593738985</v>
+        <v>29.13934561298902</v>
       </c>
       <c r="Z37" t="n">
-        <v>44.88348593738985</v>
+        <v>29.13934561298902</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>pv9VXZo7</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45466.0625</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3312,57 +3212,77 @@
       <c r="F38" t="n">
         <v>1671</v>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6543046357615894</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.1997350993377483</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1459602649006622</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.05402764204942079</v>
+      </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.4478269336701768</v>
+        <v>0.3128952493758644</v>
       </c>
       <c r="P38" t="n">
-        <v>0.3227439799731163</v>
+        <v>0.5361372692209605</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.2294290863567066</v>
+        <v>0.150967481403175</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>0.3364021698832122</v>
+      </c>
       <c r="T38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.3364021698832122</v>
+      </c>
       <c r="V38" t="n">
-        <v>0.5521730663298232</v>
-      </c>
-      <c r="W38" t="inlineStr"/>
+        <v>0.5361372692209605</v>
+      </c>
+      <c r="W38" t="n">
+        <v>4.75</v>
+      </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>38.65211464308763</v>
+        <v>37.52960884546724</v>
       </c>
       <c r="Z38" t="n">
-        <v>38.65211464308763</v>
+        <v>37.52960884546724</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>OU7ZWg1D</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45477.0625</v>
+        <v>45466.0625</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -3371,7 +3291,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3380,66 +3300,86 @@
       <c r="F39" t="n">
         <v>1671</v>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.05898156429801493</v>
+      </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0.3640386993361091</v>
+        <v>0.2957512568246276</v>
       </c>
       <c r="P39" t="n">
-        <v>0.3611765105361796</v>
+        <v>0.2512322781440824</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2747847901277112</v>
+        <v>0.4530164650312902</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0.2169405894652016</v>
+      </c>
       <c r="T39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U39" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.2169405894652016</v>
+      </c>
       <c r="V39" t="n">
-        <v>0.6359613006638909</v>
-      </c>
-      <c r="W39" t="inlineStr"/>
+        <v>0.4530164650312902</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4</v>
+      </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>44.51729104647237</v>
+        <v>31.71115255219031</v>
       </c>
       <c r="Z39" t="n">
-        <v>44.51729104647237</v>
+        <v>31.71115255219031</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xYeHewvE</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45478.02083333334</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3448,66 +3388,86 @@
       <c r="F40" t="n">
         <v>1671</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="I40" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.6880733944954128</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.1782437745740498</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.1336828309305373</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.06862745098039214</v>
+      </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.3336436547157847</v>
+        <v>0.6288124535672187</v>
       </c>
       <c r="P40" t="n">
-        <v>0.4931748276163314</v>
+        <v>0.3013673527911105</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1731815176678841</v>
+        <v>0.06982019364167102</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>-0.05926094092819412</v>
+      </c>
       <c r="T40" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U40" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.05926094092819412</v>
+      </c>
       <c r="V40" t="n">
-        <v>0.5068251723836686</v>
-      </c>
-      <c r="W40" t="inlineStr"/>
+        <v>0.3711875464327813</v>
+      </c>
+      <c r="W40" t="n">
+        <v>3</v>
+      </c>
       <c r="X40" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>35.4777620668568</v>
+        <v>25.98312825029469</v>
       </c>
       <c r="Z40" t="n">
-        <v>35.4777620668568</v>
+        <v>25.98312825029469</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>jy0LfcgK</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45478.0625</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3516,66 +3476,86 @@
       <c r="F41" t="n">
         <v>1671</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.439632042928325</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.2554618627826753</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.3049060942889996</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.05796719450132803</v>
+      </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3032410599203441</v>
+        <v>0.5201066341798269</v>
       </c>
       <c r="P41" t="n">
-        <v>0.4777524411613178</v>
+        <v>0.4046451603515387</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.219006498918338</v>
+        <v>0.07524820546863475</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>0.08047459125150191</v>
+      </c>
       <c r="T41" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.08047459125150191</v>
+      </c>
       <c r="V41" t="n">
-        <v>0.5222475588386822</v>
-      </c>
-      <c r="W41" t="inlineStr"/>
+        <v>0.5201066341798269</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2.15</v>
+      </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>36.55732911870776</v>
+        <v>36.40746439258788</v>
       </c>
       <c r="Z41" t="n">
-        <v>36.55732911870776</v>
+        <v>36.40746439258788</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>YakQgH8Q</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45478.10416666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3584,47 +3564,67 @@
       <c r="F42" t="n">
         <v>1671</v>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.6538661131292164</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.210690192008303</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.1354436948624805</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.05473453749315826</v>
+      </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.3204829122770161</v>
+        <v>0.3745130758574692</v>
       </c>
       <c r="P42" t="n">
-        <v>0.4160459857279659</v>
+        <v>0.4403573203792</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.2634711019950181</v>
+        <v>0.1851296037633309</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
-      <c r="S42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>0.229667128370897</v>
+      </c>
       <c r="T42" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U42" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.229667128370897</v>
+      </c>
       <c r="V42" t="n">
-        <v>0.5839540142720341</v>
-      </c>
-      <c r="W42" t="inlineStr"/>
+        <v>0.4403573203792</v>
+      </c>
+      <c r="W42" t="n">
+        <v>4.5</v>
+      </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>40.87678099904239</v>
+        <v>30.825012426544</v>
       </c>
       <c r="Z42" t="n">
-        <v>40.87678099904239</v>
+        <v>30.825012426544</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -2398,20 +2398,20 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.0625</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2421,85 +2421,85 @@
         <v>1671</v>
       </c>
       <c r="G29" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="I29" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.6543046357615894</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.1997350993377483</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.1459602649006622</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.05402764204942079</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0.442947785562681</v>
+        <v>0.3128952493758644</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3696567110004065</v>
+        <v>0.5361372692209605</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1873955034369123</v>
+        <v>0.150967481403175</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.1957487058645927</v>
+        <v>0.3364021698832122</v>
       </c>
       <c r="T29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1957487058645927</v>
+        <v>0.3364021698832122</v>
       </c>
       <c r="V29" t="n">
-        <v>0.557052214437319</v>
+        <v>0.5361372692209605</v>
       </c>
       <c r="W29" t="n">
-        <v>2.616279069767442</v>
+        <v>4.75</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>38.99365501061233</v>
+        <v>37.52960884546724</v>
       </c>
       <c r="Z29" t="n">
-        <v>38.99365501061233</v>
+        <v>37.52960884546724</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.0625</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2509,55 +2509,55 @@
         <v>1671</v>
       </c>
       <c r="G30" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="H30" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>0.449677174325864</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2552221800227877</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2951006456513482</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="M30" t="n">
-        <v>0.05896074646074645</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N30" t="n">
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0.330849415970903</v>
+        <v>0.2957512568246276</v>
       </c>
       <c r="P30" t="n">
-        <v>0.2884875394026187</v>
+        <v>0.2512322781440824</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4530164650312902</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.2169405894652016</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.2169405894652016</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4530164650312902</v>
       </c>
       <c r="W30" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -2565,29 +2565,29 @@
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>26.64641312385347</v>
+        <v>31.71115255219031</v>
       </c>
       <c r="Z30" t="n">
-        <v>26.64641312385347</v>
+        <v>31.71115255219031</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2597,85 +2597,85 @@
         <v>1671</v>
       </c>
       <c r="G31" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="H31" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="I31" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6098357297414951</v>
+        <v>0.6880733944954128</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2183014736949925</v>
+        <v>0.1782437745740498</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1718627965635123</v>
+        <v>0.1336828309305373</v>
       </c>
       <c r="M31" t="n">
-        <v>0.05792635435785254</v>
+        <v>0.06862745098039214</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.6288124535672187</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3421246695652593</v>
+        <v>0.3013673527911105</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.09566372313227506</v>
+        <v>0.06982019364167102</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.04762412243902936</v>
+        <v>-0.05926094092819412</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.04762412243902936</v>
+        <v>0.05926094092819412</v>
       </c>
       <c r="V31" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.3711875464327813</v>
       </c>
       <c r="W31" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>39.3548125111726</v>
+        <v>25.98312825029469</v>
       </c>
       <c r="Z31" t="n">
-        <v>39.3548125111726</v>
+        <v>25.98312825029469</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2685,85 +2685,85 @@
         <v>1671</v>
       </c>
       <c r="G32" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="H32" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5888816959792844</v>
+        <v>0.439632042928325</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2203206345234275</v>
+        <v>0.2554618627826753</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1907976694972882</v>
+        <v>0.3049060942889996</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0482308328343739</v>
+        <v>0.05796719450132803</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.4064097840638316</v>
+        <v>0.5201066341798269</v>
       </c>
       <c r="P32" t="n">
-        <v>0.406249628466087</v>
+        <v>0.4046451603515387</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1873405874700815</v>
+        <v>0.07524820546863475</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.1824719119154528</v>
+        <v>0.08047459125150191</v>
       </c>
       <c r="T32" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1824719119154528</v>
+        <v>0.08047459125150191</v>
       </c>
       <c r="V32" t="n">
-        <v>0.5935902159361683</v>
+        <v>0.5201066341798269</v>
       </c>
       <c r="W32" t="n">
-        <v>2.320471596998928</v>
+        <v>2.15</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>41.55131511553179</v>
+        <v>36.40746439258788</v>
       </c>
       <c r="Z32" t="n">
-        <v>41.55131511553179</v>
+        <v>36.40746439258788</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2773,72 +2773,72 @@
         <v>1671</v>
       </c>
       <c r="G33" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>0.54584017471928</v>
+        <v>0.6538661131292164</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.210690192008303</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.1354436948624805</v>
       </c>
       <c r="M33" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05473453749315826</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.431972689407671</v>
+        <v>0.3745130758574692</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3757237719572734</v>
+        <v>0.4403573203792</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1923035386350555</v>
+        <v>0.1851296037633309</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.113867485311609</v>
+        <v>0.229667128370897</v>
       </c>
       <c r="T33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0.113867485311609</v>
+        <v>0.229667128370897</v>
       </c>
       <c r="V33" t="n">
-        <v>0.568027310592329</v>
+        <v>0.4403573203792</v>
       </c>
       <c r="W33" t="n">
-        <v>2.079231692677071</v>
+        <v>4.5</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>39.76191174146303</v>
+        <v>30.825012426544</v>
       </c>
       <c r="Z33" t="n">
-        <v>39.76191174146303</v>
+        <v>30.825012426544</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2861,85 +2861,85 @@
         <v>1671</v>
       </c>
       <c r="G34" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="H34" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4998268098372012</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2435053688950468</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2566678212677519</v>
+        <v>0.126027397260274</v>
       </c>
       <c r="M34" t="n">
-        <v>0.05299631615421085</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.4352110096174183</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="P34" t="n">
-        <v>0.4322347323892172</v>
+        <v>0.3071275721315585</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1325542579933644</v>
+        <v>0.2167331663208083</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.06461580021978297</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="T34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0.06461580021978297</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="V34" t="n">
-        <v>0.5647889903825818</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="W34" t="n">
-        <v>1.898684210526316</v>
+        <v>1.38</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>39.53522932678072</v>
+        <v>33.32974830833433</v>
       </c>
       <c r="Z34" t="n">
-        <v>39.53522932678072</v>
+        <v>33.32974830833433</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2949,85 +2949,85 @@
         <v>1671</v>
       </c>
       <c r="G35" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I35" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>0.54584017471928</v>
+        <v>0.4295665634674923</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2554179566563468</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.315015479876161</v>
       </c>
       <c r="M35" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05814905814905802</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.4585357639156413</v>
+        <v>0.1700536136842038</v>
       </c>
       <c r="P35" t="n">
-        <v>0.3362499079698303</v>
+        <v>0.4010800352937268</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2052143281145281</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.08730441080363877</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="T35" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08730441080363877</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="V35" t="n">
-        <v>0.5414642360843587</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="W35" t="n">
-        <v>2.079231692677071</v>
+        <v>3</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>37.90249652590511</v>
+        <v>30.02064457154486</v>
       </c>
       <c r="Z35" t="n">
-        <v>37.90249652590511</v>
+        <v>30.02064457154486</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3037,85 +3037,85 @@
         <v>1671</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="H36" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4192972007147112</v>
+        <v>0.5968169761273209</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2858844550327576</v>
+        <v>0.2122015915119363</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2948183442525313</v>
+        <v>0.1909814323607427</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0599747474747474</v>
+        <v>0.04722222222222228</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.2399392096277449</v>
       </c>
       <c r="P36" t="n">
-        <v>0.3362450625534014</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2874736771444432</v>
+        <v>0.2765471637796623</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="V36" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="W36" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>26.33968822115087</v>
+        <v>33.8459538614815</v>
       </c>
       <c r="Z36" t="n">
-        <v>26.33968822115087</v>
+        <v>33.8459538614815</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3125,85 +3125,85 @@
         <v>1671</v>
       </c>
       <c r="G37" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5129935875801552</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2372595342558218</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2497468781640229</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="M37" t="n">
-        <v>0.05369843527738261</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2433648073553128</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="P37" t="n">
-        <v>0.3403588267448442</v>
+        <v>0.2448591035222365</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.2593936174066264</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.1665294877358202</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0.1665294877358202</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="V37" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="W37" t="n">
-        <v>3.8</v>
+        <v>1.57</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>29.13934561298902</v>
+        <v>34.70230953497961</v>
       </c>
       <c r="Z37" t="n">
-        <v>29.13934561298902</v>
+        <v>34.70230953497961</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3213,85 +3213,85 @@
         <v>1671</v>
       </c>
       <c r="G38" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="H38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I38" t="n">
         <v>4.75</v>
       </c>
-      <c r="I38" t="n">
-        <v>6.5</v>
-      </c>
       <c r="J38" t="n">
-        <v>0.6543046357615894</v>
+        <v>0.5746381507885073</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1997350993377483</v>
+        <v>0.225750702095485</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1459602649006622</v>
+        <v>0.1996111471160078</v>
       </c>
       <c r="M38" t="n">
-        <v>0.05402764204942079</v>
+        <v>0.05468215994531778</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.3128952493758644</v>
+        <v>0.2064575634094828</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.150967481403175</v>
+        <v>0.3588579657884538</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="V38" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="W38" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>37.52960884546724</v>
+        <v>30.42791295614444</v>
       </c>
       <c r="Z38" t="n">
-        <v>37.52960884546724</v>
+        <v>30.42791295614444</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3301,85 +3301,85 @@
         <v>1671</v>
       </c>
       <c r="G39" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="H39" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
-        <v>0.54584017471928</v>
+        <v>0.4194683346364347</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.2550820953870211</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.3254495699765442</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05954230092161117</v>
       </c>
       <c r="N39" t="n">
         <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0.2957512568246276</v>
+        <v>0.1470755222311179</v>
       </c>
       <c r="P39" t="n">
-        <v>0.2512322781440824</v>
+        <v>0.3804223516987789</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="T39" t="n">
         <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="V39" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="W39" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>31.71115255219031</v>
+        <v>33.07514882490723</v>
       </c>
       <c r="Z39" t="n">
-        <v>31.71115255219031</v>
+        <v>33.07514882490723</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3389,85 +3389,85 @@
         <v>1671</v>
       </c>
       <c r="G40" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="H40" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6880733944954128</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1782437745740498</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1336828309305373</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M40" t="n">
-        <v>0.06862745098039214</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>0.6288124535672187</v>
+        <v>0.3723226691402557</v>
       </c>
       <c r="P40" t="n">
-        <v>0.3013673527911105</v>
+        <v>0.1948158673714422</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.06982019364167102</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.05926094092819412</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="T40" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0.05926094092819412</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="V40" t="n">
-        <v>0.3711875464327813</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="W40" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>25.98312825029469</v>
+        <v>30.30030244418116</v>
       </c>
       <c r="Z40" t="n">
-        <v>25.98312825029469</v>
+        <v>30.30030244418116</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3477,85 +3477,85 @@
         <v>1671</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="H41" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
-        <v>0.439632042928325</v>
+        <v>0.3619297617627173</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2554618627826753</v>
+        <v>0.2719643638388418</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.3661058743984409</v>
       </c>
       <c r="M41" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.05055780721179959</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.3328004140349778</v>
       </c>
       <c r="P41" t="n">
-        <v>0.4046451603515387</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.07524820546863475</v>
+        <v>0.2404153444966831</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0.08047459125150191</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0.08047459125150191</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="V41" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="W41" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>36.40746439258788</v>
+        <v>29.87489690278373</v>
       </c>
       <c r="Z41" t="n">
-        <v>36.40746439258788</v>
+        <v>29.87489690278373</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3565,66 +3565,66 @@
         <v>1671</v>
       </c>
       <c r="G42" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="H42" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.5180518051805181</v>
       </c>
       <c r="K42" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2257225722572257</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.2562256225622562</v>
       </c>
       <c r="M42" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.05481359579720224</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>0.3745130758574692</v>
+        <v>0.2032595674696957</v>
       </c>
       <c r="P42" t="n">
-        <v>0.4403573203792</v>
+        <v>0.2226757413052</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.1851296037633309</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.229667128370897</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0.229667128370897</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="V42" t="n">
-        <v>0.4403573203792</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="W42" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>30.825012426544</v>
+        <v>40.18452838575731</v>
       </c>
       <c r="Z42" t="n">
-        <v>30.825012426544</v>
+        <v>40.18452838575731</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -2574,20 +2574,20 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2597,85 +2597,85 @@
         <v>1671</v>
       </c>
       <c r="G31" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H31" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6880733944954128</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1782437745740498</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1336828309305373</v>
+        <v>0.126027397260274</v>
       </c>
       <c r="M31" t="n">
-        <v>0.06862745098039214</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6288124535672187</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3013673527911105</v>
+        <v>0.3071275721315585</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.06982019364167102</v>
+        <v>0.2167331663208083</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.05926094092819412</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="T31" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0.05926094092819412</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="V31" t="n">
-        <v>0.3711875464327813</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="W31" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>25.98312825029469</v>
+        <v>33.32974830833433</v>
       </c>
       <c r="Z31" t="n">
-        <v>25.98312825029469</v>
+        <v>33.32974830833433</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2685,85 +2685,85 @@
         <v>1671</v>
       </c>
       <c r="G32" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="H32" t="n">
         <v>3.7</v>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>0.439632042928325</v>
+        <v>0.4295665634674923</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2554618627826753</v>
+        <v>0.2554179566563468</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.315015479876161</v>
       </c>
       <c r="M32" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.05814905814905802</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.1700536136842038</v>
       </c>
       <c r="P32" t="n">
-        <v>0.4046451603515387</v>
+        <v>0.4010800352937268</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.07524820546863475</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.08047459125150191</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0.08047459125150191</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="V32" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="W32" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>36.40746439258788</v>
+        <v>30.02064457154486</v>
       </c>
       <c r="Z32" t="n">
-        <v>36.40746439258788</v>
+        <v>30.02064457154486</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2773,72 +2773,72 @@
         <v>1671</v>
       </c>
       <c r="G33" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="H33" t="n">
         <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.5968169761273209</v>
       </c>
       <c r="K33" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2122015915119363</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.1909814323607427</v>
       </c>
       <c r="M33" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.04722222222222228</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.3745130758574692</v>
+        <v>0.2399392096277449</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4403573203792</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1851296037633309</v>
+        <v>0.2765471637796623</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.229667128370897</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0.229667128370897</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="V33" t="n">
-        <v>0.4403573203792</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="W33" t="n">
         <v>4.5</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>30.825012426544</v>
+        <v>33.8459538614815</v>
       </c>
       <c r="Z33" t="n">
-        <v>30.825012426544</v>
+        <v>33.8459538614815</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2861,55 +2861,55 @@
         <v>1671</v>
       </c>
       <c r="G34" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="I34" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6849315068493151</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="K34" t="n">
-        <v>0.189041095890411</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="L34" t="n">
-        <v>0.126027397260274</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="M34" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="P34" t="n">
-        <v>0.3071275721315585</v>
+        <v>0.2448591035222365</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2167331663208083</v>
+        <v>0.2593936174066264</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.2087922453016819</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.2087922453016819</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="V34" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="W34" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>33.32974830833433</v>
+        <v>34.70230953497961</v>
       </c>
       <c r="Z34" t="n">
-        <v>33.32974830833433</v>
+        <v>34.70230953497961</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2949,55 +2949,55 @@
         <v>1671</v>
       </c>
       <c r="G35" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="H35" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4295665634674923</v>
+        <v>0.5746381507885073</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2554179566563468</v>
+        <v>0.225750702095485</v>
       </c>
       <c r="L35" t="n">
-        <v>0.315015479876161</v>
+        <v>0.1996111471160078</v>
       </c>
       <c r="M35" t="n">
-        <v>0.05814905814905802</v>
+        <v>0.05468215994531778</v>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1700536136842038</v>
+        <v>0.2064575634094828</v>
       </c>
       <c r="P35" t="n">
-        <v>0.4010800352937268</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.3588579657884538</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1138508711459084</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1138508711459084</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="V35" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="W35" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -3005,16 +3005,16 @@
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>30.02064457154486</v>
+        <v>30.42791295614444</v>
       </c>
       <c r="Z35" t="n">
-        <v>30.02064457154486</v>
+        <v>30.42791295614444</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3037,55 +3037,55 @@
         <v>1671</v>
       </c>
       <c r="G36" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="H36" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5968169761273209</v>
+        <v>0.4194683346364347</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2122015915119363</v>
+        <v>0.2550820953870211</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1909814323607427</v>
+        <v>0.3254495699765442</v>
       </c>
       <c r="M36" t="n">
-        <v>0.04722222222222228</v>
+        <v>0.05954230092161117</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>0.2399392096277449</v>
+        <v>0.1470755222311179</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4835136265925929</v>
+        <v>0.3804223516987789</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2765471637796623</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.2713120350806566</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>0.2713120350806566</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="V36" t="n">
-        <v>0.4835136265925929</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="W36" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -3093,29 +3093,29 @@
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>33.8459538614815</v>
+        <v>33.07514882490723</v>
       </c>
       <c r="Z36" t="n">
-        <v>33.8459538614815</v>
+        <v>33.07514882490723</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3125,55 +3125,55 @@
         <v>1671</v>
       </c>
       <c r="G37" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
         <v>4.33</v>
       </c>
-      <c r="I37" t="n">
-        <v>5.25</v>
-      </c>
       <c r="J37" t="n">
-        <v>0.6018171661844011</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2182108431661685</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1799719906494304</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M37" t="n">
-        <v>0.05836574785251614</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.4957472790711372</v>
+        <v>0.3723226691402557</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2448591035222365</v>
+        <v>0.1948158673714422</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2593936174066264</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>-0.1060698871132638</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.1060698871132638</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="V37" t="n">
-        <v>0.4957472790711372</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="W37" t="n">
-        <v>1.57</v>
+        <v>4.33</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -3181,29 +3181,29 @@
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>34.70230953497961</v>
+        <v>30.30030244418116</v>
       </c>
       <c r="Z37" t="n">
-        <v>34.70230953497961</v>
+        <v>30.30030244418116</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3213,55 +3213,55 @@
         <v>1671</v>
       </c>
       <c r="G38" t="n">
-        <v>1.65</v>
+        <v>2.63</v>
       </c>
       <c r="H38" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I38" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5746381507885073</v>
+        <v>0.3619297617627173</v>
       </c>
       <c r="K38" t="n">
-        <v>0.225750702095485</v>
+        <v>0.2719643638388418</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1996111471160078</v>
+        <v>0.3661058743984409</v>
       </c>
       <c r="M38" t="n">
-        <v>0.05468215994531778</v>
+        <v>0.05055780721179959</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2064575634094828</v>
+        <v>0.3328004140349778</v>
       </c>
       <c r="P38" t="n">
-        <v>0.4346844708020633</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.3588579657884538</v>
+        <v>0.2404153444966831</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2089337687065784</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0.2089337687065784</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="V38" t="n">
-        <v>0.4346844708020633</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="W38" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -3269,29 +3269,29 @@
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>30.42791295614444</v>
+        <v>29.87489690278373</v>
       </c>
       <c r="Z38" t="n">
-        <v>30.42791295614444</v>
+        <v>29.87489690278373</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3301,55 +3301,55 @@
         <v>1671</v>
       </c>
       <c r="G39" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="H39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I39" t="n">
         <v>3.7</v>
       </c>
-      <c r="I39" t="n">
-        <v>2.9</v>
-      </c>
       <c r="J39" t="n">
-        <v>0.4194683346364347</v>
+        <v>0.5180518051805181</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2550820953870211</v>
+        <v>0.2257225722572257</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3254495699765442</v>
+        <v>0.2562256225622562</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05954230092161117</v>
+        <v>0.05481359579720224</v>
       </c>
       <c r="N39" t="n">
         <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1470755222311179</v>
+        <v>0.2032595674696957</v>
       </c>
       <c r="P39" t="n">
-        <v>0.3804223516987789</v>
+        <v>0.2226757413052</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4725021260701033</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0.1470525560935591</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="T39" t="n">
         <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0.1470525560935591</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="V39" t="n">
-        <v>0.4725021260701033</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="W39" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -3357,29 +3357,29 @@
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>33.07514882490723</v>
+        <v>40.18452838575731</v>
       </c>
       <c r="Z39" t="n">
-        <v>33.07514882490723</v>
+        <v>40.18452838575731</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3389,55 +3389,55 @@
         <v>1671</v>
       </c>
       <c r="G40" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="J40" t="n">
-        <v>0.54584017471928</v>
+        <v>0.7083825265643447</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.1570247933884298</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.1345926800472255</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.06140350877192979</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.3723226691402557</v>
+        <v>0.3869700516647428</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1948158673714422</v>
+        <v>0.4439708949612933</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.4328614634883022</v>
+        <v>0.1690590533739638</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.2147775137736708</v>
+        <v>0.2869461015728636</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0.2147775137736708</v>
+        <v>0.2869461015728636</v>
       </c>
       <c r="V40" t="n">
-        <v>0.4328614634883022</v>
+        <v>0.4439708949612933</v>
       </c>
       <c r="W40" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -3445,29 +3445,29 @@
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>30.30030244418116</v>
+        <v>31.07796264729053</v>
       </c>
       <c r="Z40" t="n">
-        <v>30.30030244418116</v>
+        <v>31.07796264729053</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3477,55 +3477,55 @@
         <v>1671</v>
       </c>
       <c r="G41" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="H41" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3619297617627173</v>
+        <v>0.439632042928325</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2719643638388418</v>
+        <v>0.2554618627826753</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3661058743984409</v>
+        <v>0.3049060942889996</v>
       </c>
       <c r="M41" t="n">
-        <v>0.05055780721179959</v>
+        <v>0.05796719450132803</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3328004140349778</v>
+        <v>0.3641650161969446</v>
       </c>
       <c r="P41" t="n">
-        <v>0.426784241468339</v>
+        <v>0.2900694571601281</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2404153444966831</v>
+        <v>0.3457655266429275</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0.1548198776294972</v>
+        <v>-0.07546702673138045</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1548198776294972</v>
+        <v>-0.07546702673138045</v>
       </c>
       <c r="V41" t="n">
-        <v>0.426784241468339</v>
+        <v>0.3641650161969446</v>
       </c>
       <c r="W41" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -3533,29 +3533,29 @@
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>29.87489690278373</v>
+        <v>25.49155113378612</v>
       </c>
       <c r="Z41" t="n">
-        <v>29.87489690278373</v>
+        <v>25.49155113378612</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3565,55 +3565,55 @@
         <v>1671</v>
       </c>
       <c r="G42" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="H42" t="n">
         <v>4.2</v>
       </c>
       <c r="I42" t="n">
-        <v>3.7</v>
+        <v>5.75</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5180518051805181</v>
+        <v>0.6102722850464338</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2257225722572257</v>
+        <v>0.2252195337671363</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2562256225622562</v>
+        <v>0.16450818118643</v>
       </c>
       <c r="M42" t="n">
-        <v>0.05481359579720224</v>
+        <v>0.05716957189607941</v>
       </c>
       <c r="N42" t="n">
         <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2032595674696957</v>
+        <v>0.2443995218260647</v>
       </c>
       <c r="P42" t="n">
-        <v>0.2226757413052</v>
+        <v>0.2882032729522528</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.5740646912251044</v>
+        <v>0.4673972052216825</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.3178390686628482</v>
+        <v>0.3028890240352525</v>
       </c>
       <c r="T42" t="n">
         <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0.3178390686628482</v>
+        <v>0.3028890240352525</v>
       </c>
       <c r="V42" t="n">
-        <v>0.5740646912251044</v>
+        <v>0.4673972052216825</v>
       </c>
       <c r="W42" t="n">
-        <v>3.7</v>
+        <v>5.75</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>40.18452838575731</v>
+        <v>32.71780436551778</v>
       </c>
       <c r="Z42" t="n">
-        <v>40.18452838575731</v>
+        <v>32.71780436551778</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -3389,55 +3389,55 @@
         <v>1671</v>
       </c>
       <c r="G40" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7083825265643447</v>
+        <v>0.7239382239382238</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1570247933884298</v>
+        <v>0.1505791505791506</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1345926800472255</v>
+        <v>0.1254826254826255</v>
       </c>
       <c r="M40" t="n">
-        <v>0.06140350877192979</v>
+        <v>0.06256410256410261</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.3869700516647428</v>
+        <v>0.3349990233680442</v>
       </c>
       <c r="P40" t="n">
-        <v>0.4439708949612933</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1690590533739638</v>
+        <v>0.280873440818991</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.2869461015728636</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0.2869461015728636</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="V40" t="n">
-        <v>0.4439708949612933</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="W40" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>31.07796264729053</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="Z40" t="n">
-        <v>31.07796264729053</v>
+        <v>26.88892750690754</v>
       </c>
     </row>
     <row r="41">
@@ -3498,34 +3498,34 @@
         <v>0.05796719450132803</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3641650161969446</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2900694571601281</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.3457655266429275</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.07546702673138045</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>-0.07546702673138045</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="V41" t="n">
-        <v>0.3641650161969446</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="W41" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>25.49155113378612</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z41" t="n">
-        <v>25.49155113378612</v>
+        <v>30.74138453903112</v>
       </c>
     </row>
     <row r="42">
@@ -3589,28 +3589,28 @@
         <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2443995218260647</v>
+        <v>0.2068043869608158</v>
       </c>
       <c r="P42" t="n">
-        <v>0.2882032729522528</v>
+        <v>0.242857704879984</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.4673972052216825</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.3028890240352525</v>
+        <v>0.3858297269727703</v>
       </c>
       <c r="T42" t="n">
         <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0.3028890240352525</v>
+        <v>0.3858297269727703</v>
       </c>
       <c r="V42" t="n">
-        <v>0.4673972052216825</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="W42" t="n">
         <v>5.75</v>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>32.71780436551778</v>
+        <v>38.52365357114402</v>
       </c>
       <c r="Z42" t="n">
-        <v>32.71780436551778</v>
+        <v>38.52365357114402</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -3565,25 +3565,25 @@
         <v>1671</v>
       </c>
       <c r="G42" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H42" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I42" t="n">
         <v>5.75</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6102722850464338</v>
+        <v>0.6038755619308649</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2252195337671363</v>
+        <v>0.2312401542027946</v>
       </c>
       <c r="L42" t="n">
-        <v>0.16450818118643</v>
+        <v>0.1648842838663405</v>
       </c>
       <c r="M42" t="n">
-        <v>0.05716957189607941</v>
+        <v>0.05475815766188674</v>
       </c>
       <c r="N42" t="n">
         <v>2</v>
@@ -3601,13 +3601,13 @@
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.3858297269727703</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="T42" t="n">
         <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0.3858297269727703</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="V42" t="n">
         <v>0.5503379081592003</v>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z42"/>
+  <dimension ref="A1:Z56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,20 +562,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45471.97916666666</v>
+        <v>45466.0625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -584,66 +584,86 @@
       <c r="F2" t="n">
         <v>1671</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6543046357615894</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1997350993377483</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1459602649006622</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05402764204942079</v>
+      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2462720620015046</v>
+        <v>0.3128952493758644</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4923339539454937</v>
+        <v>0.5361372692209605</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2613939840530014</v>
+        <v>0.150967481403175</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0.3364021698832122</v>
+      </c>
       <c r="T2" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.3364021698832122</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.5076660460545063</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>0.5361372692209605</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.75</v>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>35.53662322381544</v>
+        <v>37.52960884546724</v>
       </c>
       <c r="Z2" t="n">
-        <v>35.53662322381544</v>
+        <v>37.52960884546724</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45466.0625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -652,66 +672,86 @@
       <c r="F3" t="n">
         <v>1671</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05898156429801493</v>
+      </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4486050669888325</v>
+        <v>0.2957512568246276</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4047008090404339</v>
+        <v>0.2512322781440824</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1466941239707336</v>
+        <v>0.4530164650312902</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0.2169405894652016</v>
+      </c>
       <c r="T3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.2169405894652016</v>
+      </c>
       <c r="V3" t="n">
-        <v>0.5513949330111676</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>0.4530164650312902</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4</v>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>38.59764531078173</v>
+        <v>31.71115255219031</v>
       </c>
       <c r="Z3" t="n">
-        <v>38.59764531078173</v>
+        <v>31.71115255219031</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -720,66 +760,86 @@
       <c r="F4" t="n">
         <v>1671</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6849315068493151</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.189041095890411</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.126027397260274</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05797101449275366</v>
+      </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3145692862666382</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4692743552439834</v>
+        <v>0.3071275721315585</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2161563584893785</v>
+        <v>0.2167331663208083</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>-0.2087922453016819</v>
+      </c>
       <c r="T4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.2087922453016819</v>
+      </c>
       <c r="V4" t="n">
-        <v>0.5307256447560167</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>0.4761392615476333</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.38</v>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>37.15079513292117</v>
+        <v>33.32974830833433</v>
       </c>
       <c r="Z4" t="n">
-        <v>37.15079513292117</v>
+        <v>33.32974830833433</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -788,66 +848,86 @@
       <c r="F5" t="n">
         <v>1671</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4295665634674923</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2554179566563468</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.315015479876161</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05814905814905802</v>
+      </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3395212219234734</v>
+        <v>0.1700536136842038</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2837467714942478</v>
+        <v>0.4010800352937268</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3767320065822789</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0.1138508711459084</v>
+      </c>
       <c r="T5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1138508711459084</v>
+      </c>
       <c r="V5" t="n">
-        <v>0.6232679934177211</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>0.4288663510220694</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>43.62875953924048</v>
+        <v>30.02064457154486</v>
       </c>
       <c r="Z5" t="n">
-        <v>43.62875953924048</v>
+        <v>30.02064457154486</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -856,66 +936,86 @@
       <c r="F6" t="n">
         <v>1671</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5968169761273209</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2122015915119363</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1909814323607427</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.04722222222222228</v>
+      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.319004676081902</v>
+        <v>0.2399392096277449</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4197691100698566</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2612262138482416</v>
+        <v>0.2765471637796623</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0.2713120350806566</v>
+      </c>
       <c r="T6" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.2713120350806566</v>
+      </c>
       <c r="V6" t="n">
-        <v>0.5802308899301434</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
+        <v>0.4835136265925929</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4.5</v>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>40.61616229511004</v>
+        <v>33.8459538614815</v>
       </c>
       <c r="Z6" t="n">
-        <v>40.61616229511004</v>
+        <v>33.8459538614815</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -924,66 +1024,86 @@
       <c r="F7" t="n">
         <v>1671</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6018171661844011</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2182108431661685</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1799719906494304</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05836574785251614</v>
+      </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3468466868897144</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3604566226280601</v>
+        <v>0.2448591035222365</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2926966904822257</v>
+        <v>0.2593936174066264</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>-0.1060698871132638</v>
+      </c>
       <c r="T7" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.1060698871132638</v>
+      </c>
       <c r="V7" t="n">
-        <v>0.6395433773719399</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
+        <v>0.4957472790711372</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.57</v>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>44.76803641603579</v>
+        <v>34.70230953497961</v>
       </c>
       <c r="Z7" t="n">
-        <v>44.76803641603579</v>
+        <v>34.70230953497961</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -992,66 +1112,86 @@
       <c r="F8" t="n">
         <v>1671</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5746381507885073</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.225750702095485</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1996111471160078</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05468215994531778</v>
+      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.352099940595717</v>
+        <v>0.2064575634094828</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4534281625400888</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.194471896864194</v>
+        <v>0.3588579657884538</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0.2089337687065784</v>
+      </c>
       <c r="T8" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2089337687065784</v>
+      </c>
       <c r="V8" t="n">
-        <v>0.5465718374599111</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
+        <v>0.4346844708020633</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.2</v>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>38.26002862219378</v>
+        <v>30.42791295614444</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.26002862219378</v>
+        <v>30.42791295614444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1060,61 +1200,81 @@
       <c r="F9" t="n">
         <v>1671</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4194683346364347</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2550820953870211</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3254495699765442</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.05954230092161117</v>
+      </c>
       <c r="N9" t="n">
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1884751250500326</v>
+        <v>0.1470755222311179</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2882272408643515</v>
+        <v>0.3804223516987789</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5232976340856157</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0.1470525560935591</v>
+      </c>
       <c r="T9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.1470525560935591</v>
+      </c>
       <c r="V9" t="n">
-        <v>0.4767023659143843</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>0.4725021260701033</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.9</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>33.3691656140069</v>
+        <v>33.07514882490723</v>
       </c>
       <c r="Z9" t="n">
-        <v>33.3691656140069</v>
+        <v>33.07514882490723</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1128,66 +1288,86 @@
       <c r="F10" t="n">
         <v>1671</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.05898156429801493</v>
+      </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4491415382196292</v>
+        <v>0.3723226691402557</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3649273122968265</v>
+        <v>0.1948158673714422</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1859311494835444</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0.2147775137736708</v>
+      </c>
       <c r="T10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2147775137736708</v>
+      </c>
       <c r="V10" t="n">
-        <v>0.5508584617803708</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
+        <v>0.4328614634883022</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.33</v>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>38.56009232462596</v>
+        <v>30.30030244418116</v>
       </c>
       <c r="Z10" t="n">
-        <v>38.56009232462596</v>
+        <v>30.30030244418116</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1196,66 +1376,86 @@
       <c r="F11" t="n">
         <v>1671</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3619297617627173</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2719643638388418</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3661058743984409</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.05055780721179959</v>
+      </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5262868708033219</v>
+        <v>0.3328004140349778</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3324678315859552</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1412452976107228</v>
+        <v>0.2404153444966831</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0.1548198776294972</v>
+      </c>
       <c r="T11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.1548198776294972</v>
+      </c>
       <c r="V11" t="n">
-        <v>0.4737131291966781</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
+        <v>0.426784241468339</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.5</v>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>33.15991904376747</v>
+        <v>29.87489690278373</v>
       </c>
       <c r="Z11" t="n">
-        <v>33.15991904376747</v>
+        <v>29.87489690278373</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1264,134 +1464,174 @@
       <c r="F12" t="n">
         <v>1671</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5180518051805181</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2257225722572257</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2562256225622562</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.05481359579720224</v>
+      </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.603789322280942</v>
+        <v>0.2032595674696957</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3291009915269105</v>
+        <v>0.2226757413052</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.06710968619214784</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0.3178390686628482</v>
+      </c>
       <c r="T12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.3178390686628482</v>
+      </c>
       <c r="V12" t="n">
-        <v>0.396210677719058</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
+        <v>0.5740646912251044</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.7</v>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>27.73474744033406</v>
+        <v>40.18452838575731</v>
       </c>
       <c r="Z12" t="n">
-        <v>27.73474744033406</v>
+        <v>40.18452838575731</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>san jose earthquakes</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
       <c r="E13" t="n">
         <v>167</v>
       </c>
       <c r="F13" t="n">
         <v>1671</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7239382239382238</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1505791505791506</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1254826254826255</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.06256410256410261</v>
+      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3410847389107385</v>
+        <v>0.3349990233680442</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4719125839273521</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1870026771619094</v>
+        <v>0.280873440818991</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0.2335483852338142</v>
+      </c>
       <c r="T13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.2335483852338142</v>
+      </c>
       <c r="V13" t="n">
-        <v>0.5280874160726479</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
+        <v>0.3841275358129648</v>
+      </c>
+      <c r="W13" t="n">
+        <v>6.25</v>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>36.96611912508535</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="Z13" t="n">
-        <v>36.96611912508535</v>
+        <v>26.88892750690754</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1400,66 +1640,86 @@
       <c r="F14" t="n">
         <v>1671</v>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.439632042928325</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2554618627826753</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3049060942889996</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05796719450132803</v>
+      </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>0.458906160045076</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4271192785075237</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1139745614474004</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0.1342565419828735</v>
+      </c>
       <c r="T14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1342565419828735</v>
+      </c>
       <c r="V14" t="n">
-        <v>0.5410938399549241</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.1</v>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>37.87656879684469</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z14" t="n">
-        <v>37.87656879684469</v>
+        <v>30.74138453903112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1468,66 +1728,86 @@
       <c r="F15" t="n">
         <v>1671</v>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6038755619308649</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2312401542027946</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1648842838663405</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.05475815766188674</v>
+      </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4542204032452292</v>
+        <v>0.2068043869608158</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3865699443481483</v>
+        <v>0.242857704879984</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1592096524066227</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0.3854536242928598</v>
+      </c>
       <c r="T15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.3854536242928598</v>
+      </c>
       <c r="V15" t="n">
-        <v>0.5457795967547708</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
+        <v>0.5503379081592003</v>
+      </c>
+      <c r="W15" t="n">
+        <v>5.75</v>
+      </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>38.20457177283396</v>
+        <v>38.52365357114402</v>
       </c>
       <c r="Z15" t="n">
-        <v>38.20457177283396</v>
+        <v>38.52365357114402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>W0zNyInr</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45476.9375</v>
+        <v>45471.97916666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1536,66 +1816,86 @@
       <c r="F16" t="n">
         <v>1671</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.483021608861449</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2478663519157435</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2691120392228073</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.06169269327164084</v>
+      </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5050016708574175</v>
+        <v>0.1642468697849789</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3849675921712908</v>
+        <v>0.3239081110463583</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1100307369712915</v>
+        <v>0.5118450191686629</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0.2427329799458556</v>
+      </c>
       <c r="T16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2427329799458556</v>
+      </c>
       <c r="V16" t="n">
-        <v>0.4949983291425825</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
+        <v>0.5118450191686629</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.5</v>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>34.64988303998077</v>
+        <v>35.8291513418064</v>
       </c>
       <c r="Z16" t="n">
-        <v>34.64988303998077</v>
+        <v>35.8291513418064</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>QJcftbvR</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1604,66 +1904,86 @@
       <c r="F17" t="n">
         <v>1671</v>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.542180339508165</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2344929968372814</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2233266636545537</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.06612992017616293</v>
+      </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.182866834220039</v>
+        <v>0.5495201590542395</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2334437671118067</v>
+        <v>0.2376684911701525</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5836893986681545</v>
+        <v>0.2128113497756081</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>0.007339819546074433</v>
+      </c>
       <c r="T17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.007339819546074433</v>
+      </c>
       <c r="V17" t="n">
-        <v>0.4163106013318455</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
+        <v>0.5495201590542395</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.73</v>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>29.14174209322918</v>
+        <v>38.46641113379676</v>
       </c>
       <c r="Z17" t="n">
-        <v>29.14174209322918</v>
+        <v>38.46641113379676</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>p4vRzx2l</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1672,66 +1992,86 @@
       <c r="F18" t="n">
         <v>1671</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3236831523924407</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.268194611982308</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4081222356252514</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.06532448061683449</v>
+      </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2902861035528271</v>
+        <v>0.1112666056438713</v>
       </c>
       <c r="P18" t="n">
-        <v>0.33017548571028</v>
+        <v>0.4673436835784407</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.3795384107368928</v>
+        <v>0.4213897107776879</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0.1991490715961327</v>
+      </c>
       <c r="T18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.1991490715961327</v>
+      </c>
       <c r="V18" t="n">
-        <v>0.6204615892631072</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
+        <v>0.4673436835784407</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.5</v>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>43.43231124841751</v>
+        <v>32.71405785049085</v>
       </c>
       <c r="Z18" t="n">
-        <v>43.43231124841751</v>
+        <v>32.71405785049085</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>88KCueOd</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1740,66 +2080,86 @@
       <c r="F19" t="n">
         <v>1671</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3223762376237624</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2526732673267326</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4249504950495049</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.06964331102262133</v>
+      </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4444862769605148</v>
+        <v>0.2885538219241844</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3738661777520266</v>
+        <v>0.4315579098143414</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1816475452874586</v>
+        <v>0.2798882682614742</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0.1788846424876088</v>
+      </c>
       <c r="T19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.1788846424876088</v>
+      </c>
       <c r="V19" t="n">
-        <v>0.5555137230394852</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
+        <v>0.4315579098143414</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.7</v>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>38.88596061276397</v>
+        <v>30.2090536870039</v>
       </c>
       <c r="Z19" t="n">
-        <v>38.88596061276397</v>
+        <v>30.2090536870039</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>naJGvFw3</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1808,66 +2168,86 @@
       <c r="F20" t="n">
         <v>1671</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5546995377503853</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2357473035439137</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2095531587057011</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.06045751633986929</v>
+      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1556738986571048</v>
+        <v>0.2696524984710746</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4360717482454501</v>
+        <v>0.4044565330362194</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4082543530974453</v>
+        <v>0.325890968492706</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0.1687092294923057</v>
+      </c>
       <c r="T20" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.1687092294923057</v>
+      </c>
       <c r="V20" t="n">
-        <v>0.5639282517545499</v>
-      </c>
-      <c r="W20" t="inlineStr"/>
+        <v>0.4044565330362194</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4</v>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>39.47497762281849</v>
+        <v>28.31195731253536</v>
       </c>
       <c r="Z20" t="n">
-        <v>39.47497762281849</v>
+        <v>28.31195731253536</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>vRwVZeHf</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45476.98958333334</v>
+        <v>45473.02083333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1876,66 +2256,86 @@
       <c r="F21" t="n">
         <v>1671</v>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3567060741948635</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2680391357521402</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3752547900529964</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.06594242259641492</v>
+      </c>
       <c r="N21" t="n">
         <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2291534607267637</v>
+        <v>0.1056844427493848</v>
       </c>
       <c r="P21" t="n">
-        <v>0.361229768531829</v>
+        <v>0.4070576290052907</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4096167707414073</v>
+        <v>0.4872579282453244</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0.112003138192328</v>
+      </c>
       <c r="T21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.112003138192328</v>
+      </c>
       <c r="V21" t="n">
-        <v>0.5903832292585927</v>
-      </c>
-      <c r="W21" t="inlineStr"/>
+        <v>0.4872579282453244</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.5</v>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>41.32682604810149</v>
+        <v>34.10805497717271</v>
       </c>
       <c r="Z21" t="n">
-        <v>41.32682604810149</v>
+        <v>34.10805497717271</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>IHxZYFW0</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45473.02083333334</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1944,66 +2344,86 @@
       <c r="F22" t="n">
         <v>1671</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5220012055455093</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2610006027727547</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0642802155504234</v>
+      </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4395550098211475</v>
+        <v>0.2019387812030422</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4157662140662979</v>
+        <v>0.289818025706767</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1446787761125546</v>
+        <v>0.5082431930901908</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0.2912450014084549</v>
+      </c>
       <c r="T22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.2912450014084549</v>
+      </c>
       <c r="V22" t="n">
-        <v>0.5604449901788525</v>
-      </c>
-      <c r="W22" t="inlineStr"/>
+        <v>0.5082431930901908</v>
+      </c>
+      <c r="W22" t="n">
+        <v>4.33</v>
+      </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>39.23114931251968</v>
+        <v>35.57702351631336</v>
       </c>
       <c r="Z22" t="n">
-        <v>39.23114931251968</v>
+        <v>35.57702351631336</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>UN8LwZh9</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45473.02083333334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2012,66 +2432,86 @@
       <c r="F23" t="n">
         <v>1671</v>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3958218801539307</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2770753161077515</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.3271028037383177</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.06150793650793651</v>
+      </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3588073437515735</v>
+        <v>0.0761032136620981</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3478863234417136</v>
+        <v>0.3219959001578103</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2933063328067126</v>
+        <v>0.6019008861800916</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0.2747980824417739</v>
+      </c>
       <c r="T23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U23" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2747980824417739</v>
+      </c>
       <c r="V23" t="n">
-        <v>0.6411926562484265</v>
-      </c>
-      <c r="W23" t="inlineStr"/>
+        <v>0.6019008861800916</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.88</v>
+      </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>44.88348593738985</v>
+        <v>42.13306203260642</v>
       </c>
       <c r="Z23" t="n">
-        <v>44.88348593738985</v>
+        <v>42.13306203260642</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>pv9VXZo7</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45473.02083333334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2080,66 +2520,86 @@
       <c r="F24" t="n">
         <v>1671</v>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5228187919463088</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2476510067114094</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2295302013422819</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.06261588931678785</v>
+      </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4478269336701768</v>
+        <v>0.3408279566753958</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3227439799731163</v>
+        <v>0.1450477685978707</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2294290863567066</v>
+        <v>0.5141242747267334</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>0.2845940733844515</v>
+      </c>
       <c r="T24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U24" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.2845940733844515</v>
+      </c>
       <c r="V24" t="n">
-        <v>0.5521730663298232</v>
-      </c>
-      <c r="W24" t="inlineStr"/>
+        <v>0.5141242747267334</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4.1</v>
+      </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>38.65211464308763</v>
+        <v>35.98869923087134</v>
       </c>
       <c r="Z24" t="n">
-        <v>38.65211464308763</v>
+        <v>35.98869923087134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>OU7ZWg1D</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45477.0625</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2148,66 +2608,86 @@
       <c r="F25" t="n">
         <v>1671</v>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.6272727272727273</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2090909090909091</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1636363636363637</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.06280193236714959</v>
+      </c>
       <c r="N25" t="n">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3640386993361091</v>
+        <v>0.4548433740951673</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3611765105361796</v>
+        <v>0.3177878431154366</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2747847901277112</v>
+        <v>0.227368782789396</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>-0.17242935317756</v>
+      </c>
       <c r="T25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.17242935317756</v>
+      </c>
       <c r="V25" t="n">
-        <v>0.6359613006638909</v>
-      </c>
-      <c r="W25" t="inlineStr"/>
+        <v>0.4548433740951673</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>44.51729104647237</v>
+        <v>31.83903618666172</v>
       </c>
       <c r="Z25" t="n">
-        <v>44.51729104647237</v>
+        <v>31.83903618666172</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>xYeHewvE</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45478.02083333334</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2216,66 +2696,86 @@
       <c r="F26" t="n">
         <v>1671</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4931506849315068</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2465753424657534</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2602739726027397</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.06725146198830423</v>
+      </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3336436547157847</v>
+        <v>0.4638753279776394</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4931748276163314</v>
+        <v>0.359396816040525</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1731815176678841</v>
+        <v>0.1767278559818356</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>-0.02927535695386735</v>
+      </c>
       <c r="T26" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.02927535695386735</v>
+      </c>
       <c r="V26" t="n">
-        <v>0.5068251723836686</v>
-      </c>
-      <c r="W26" t="inlineStr"/>
+        <v>0.4638753279776394</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.9</v>
+      </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>35.4777620668568</v>
+        <v>32.47127295843476</v>
       </c>
       <c r="Z26" t="n">
-        <v>35.4777620668568</v>
+        <v>32.47127295843476</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>jy0LfcgK</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45478.0625</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2284,66 +2784,86 @@
       <c r="F27" t="n">
         <v>1671</v>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2615384615384615</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.06209150326797408</v>
+      </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3032410599203441</v>
+        <v>0.2337930636330741</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4777524411613178</v>
+        <v>0.2864780022701863</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.219006498918338</v>
+        <v>0.4797289340967397</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0.1104981648659705</v>
+      </c>
       <c r="T27" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U27" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.1104981648659705</v>
+      </c>
       <c r="V27" t="n">
-        <v>0.5222475588386822</v>
-      </c>
-      <c r="W27" t="inlineStr"/>
+        <v>0.4797289340967397</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.55</v>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>36.55732911870776</v>
+        <v>33.58102538677178</v>
       </c>
       <c r="Z27" t="n">
-        <v>36.55732911870776</v>
+        <v>33.58102538677178</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>YakQgH8Q</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45478.10416666666</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2352,66 +2872,86 @@
       <c r="F28" t="n">
         <v>1671</v>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.5835764902042518</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.236348478532722</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1800750312630263</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.05776014109347427</v>
+      </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0.3204829122770161</v>
+        <v>0.2292248832373925</v>
       </c>
       <c r="P28" t="n">
-        <v>0.4160459857279659</v>
+        <v>0.3239337003004357</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2634711019950181</v>
+        <v>0.4468414164621718</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0.2667663851991455</v>
+      </c>
       <c r="T28" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U28" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.2667663851991455</v>
+      </c>
       <c r="V28" t="n">
-        <v>0.5839540142720341</v>
-      </c>
-      <c r="W28" t="inlineStr"/>
+        <v>0.4468414164621718</v>
+      </c>
+      <c r="W28" t="n">
+        <v>5.25</v>
+      </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>40.87678099904239</v>
+        <v>31.27889915235203</v>
       </c>
       <c r="Z28" t="n">
-        <v>40.87678099904239</v>
+        <v>31.27889915235203</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2421,85 +2961,85 @@
         <v>1671</v>
       </c>
       <c r="G29" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="H29" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="I29" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6543046357615894</v>
+        <v>0.5152153240048907</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1997350993377483</v>
+        <v>0.2548227143051216</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1459602649006622</v>
+        <v>0.2299619616899878</v>
       </c>
       <c r="M29" t="n">
-        <v>0.05402764204942079</v>
+        <v>0.06062079672635434</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0.3128952493758644</v>
+        <v>0.1096026689551528</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.6508783927570068</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.150967481403175</v>
+        <v>0.2395189382878405</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.3960556784518852</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.3960556784518852</v>
       </c>
       <c r="V29" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.6508783927570068</v>
       </c>
       <c r="W29" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>37.52960884546724</v>
+        <v>45.56148749299047</v>
       </c>
       <c r="Z29" t="n">
-        <v>37.52960884546724</v>
+        <v>45.56148749299047</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>W0zNyInr</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45476.9375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2508,86 +3048,66 @@
       <c r="F30" t="n">
         <v>1671</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.54584017471928</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.2180839497146315</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.2360758755660886</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.05898156429801493</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2957512568246276</v>
+        <v>0.2910801910715639</v>
       </c>
       <c r="P30" t="n">
-        <v>0.2512322781440824</v>
+        <v>0.3187300557940925</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.3901897531343437</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="S30" t="n">
-        <v>0.2169405894652016</v>
-      </c>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0.2169405894652016</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>0.4530164650312902</v>
-      </c>
-      <c r="W30" t="n">
-        <v>4</v>
-      </c>
+        <v>0.6098102468656563</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>31.71115255219031</v>
+        <v>42.68671728059594</v>
       </c>
       <c r="Z30" t="n">
-        <v>31.71115255219031</v>
+        <v>42.68671728059594</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2596,77 +3116,57 @@
       <c r="F31" t="n">
         <v>1671</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H31" t="n">
-        <v>5</v>
-      </c>
-      <c r="I31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.6849315068493151</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.189041095890411</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.126027397260274</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.05797101449275366</v>
-      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.11859282169494</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3071275721315585</v>
+        <v>0.2891652246559143</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2167331663208083</v>
+        <v>0.5922419536491457</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="n">
-        <v>-0.2087922453016819</v>
-      </c>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>-0.2087922453016819</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>0.4761392615476333</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.38</v>
-      </c>
+        <v>0.4077580463508543</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>33.32974830833433</v>
+        <v>28.5430632445598</v>
       </c>
       <c r="Z31" t="n">
-        <v>33.32974830833433</v>
+        <v>28.5430632445598</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2675,7 +3175,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2684,86 +3184,66 @@
       <c r="F32" t="n">
         <v>1671</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.4295665634674923</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.2554179566563468</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.315015479876161</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.05814905814905802</v>
-      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1700536136842038</v>
+        <v>0.1300286073032101</v>
       </c>
       <c r="P32" t="n">
-        <v>0.4010800352937268</v>
+        <v>0.2959344201278853</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.5740369725689046</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="S32" t="n">
-        <v>0.1138508711459084</v>
-      </c>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.1138508711459084</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>0.4288663510220694</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3</v>
-      </c>
+        <v>0.4259630274310954</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>30.02064457154486</v>
+        <v>29.81741192017668</v>
       </c>
       <c r="Z32" t="n">
-        <v>30.02064457154486</v>
+        <v>29.81741192017668</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2772,86 +3252,66 @@
       <c r="F33" t="n">
         <v>1671</v>
       </c>
-      <c r="G33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I33" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.5968169761273209</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.2122015915119363</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.1909814323607427</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.04722222222222228</v>
-      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2399392096277449</v>
+        <v>0.3021367112651189</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4835136265925929</v>
+        <v>0.3118254466460983</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2765471637796623</v>
+        <v>0.3860378420887828</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
-      <c r="S33" t="n">
-        <v>0.2713120350806566</v>
-      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.2713120350806566</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
-        <v>0.4835136265925929</v>
-      </c>
-      <c r="W33" t="n">
-        <v>4.5</v>
-      </c>
+        <v>0.6139621579112171</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>33.8459538614815</v>
+        <v>42.9773510537852</v>
       </c>
       <c r="Z33" t="n">
-        <v>33.8459538614815</v>
+        <v>42.9773510537852</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2860,86 +3320,66 @@
       <c r="F34" t="n">
         <v>1671</v>
       </c>
-      <c r="G34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H34" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I34" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.6018171661844011</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.2182108431661685</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.1799719906494304</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.05836574785251614</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>0.4957472790711372</v>
+        <v>0.1137181767269389</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2448591035222365</v>
+        <v>0.347281232600631</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2593936174066264</v>
+        <v>0.5390005906724301</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="n">
-        <v>-0.1060698871132638</v>
-      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>-0.1060698871132638</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>0.4957472790711372</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.57</v>
-      </c>
+        <v>0.4609994093275699</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>34.70230953497961</v>
+        <v>32.26995865292989</v>
       </c>
       <c r="Z34" t="n">
-        <v>34.70230953497961</v>
+        <v>32.26995865292989</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>vRwVZeHf</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.98958333334</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2948,165 +3388,125 @@
       <c r="F35" t="n">
         <v>1671</v>
       </c>
-      <c r="G35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.5746381507885073</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.225750702095485</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.1996111471160078</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.05468215994531778</v>
-      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.2064575634094828</v>
+        <v>0.3377610251048948</v>
       </c>
       <c r="P35" t="n">
-        <v>0.4346844708020633</v>
+        <v>0.2629343508692568</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3588579657884538</v>
+        <v>0.3993046240258485</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S35" t="n">
-        <v>0.2089337687065784</v>
-      </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.2089337687065784</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
-        <v>0.4346844708020633</v>
-      </c>
-      <c r="W35" t="n">
-        <v>4.2</v>
-      </c>
+        <v>0.6006953759741516</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>30.42791295614444</v>
+        <v>42.04867631819061</v>
       </c>
       <c r="Z35" t="n">
-        <v>30.42791295614444</v>
+        <v>42.04867631819061</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>IHxZYFW0</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>philadelphia union</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>charlotte</t>
-        </is>
-      </c>
       <c r="E36" t="n">
         <v>167</v>
       </c>
       <c r="F36" t="n">
         <v>1671</v>
       </c>
-      <c r="G36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.4194683346364347</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.2550820953870211</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.3254495699765442</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.05954230092161117</v>
-      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1470755222311179</v>
+        <v>0.2102050138660907</v>
       </c>
       <c r="P36" t="n">
-        <v>0.3804223516987789</v>
+        <v>0.4460485145786615</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.4725021260701033</v>
+        <v>0.3437464715552478</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="n">
-        <v>0.1470525560935591</v>
-      </c>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" t="n">
-        <v>2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.1470525560935591</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
-        <v>0.4725021260701033</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.5539514854213385</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>33.07514882490723</v>
+        <v>38.7766039794937</v>
       </c>
       <c r="Z36" t="n">
-        <v>33.07514882490723</v>
+        <v>38.7766039794937</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -3115,7 +3515,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3124,86 +3524,66 @@
       <c r="F37" t="n">
         <v>1671</v>
       </c>
-      <c r="G37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4</v>
-      </c>
-      <c r="I37" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.54584017471928</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.2360758755660886</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.2180839497146315</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.05898156429801493</v>
-      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
         <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.3723226691402557</v>
+        <v>0.2039683792691152</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1948158673714422</v>
+        <v>0.2195417309854106</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4328614634883022</v>
+        <v>0.5764898897454743</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
       </c>
-      <c r="S37" t="n">
-        <v>0.2147775137736708</v>
-      </c>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="n">
-        <v>2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.2147775137736708</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
-        <v>0.4328614634883022</v>
-      </c>
-      <c r="W37" t="n">
-        <v>4.33</v>
-      </c>
+        <v>0.4235101102545257</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>30.30030244418116</v>
+        <v>29.6457077178168</v>
       </c>
       <c r="Z37" t="n">
-        <v>30.30030244418116</v>
+        <v>29.6457077178168</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3212,86 +3592,66 @@
       <c r="F38" t="n">
         <v>1671</v>
       </c>
-      <c r="G38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="H38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.3619297617627173</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.2719643638388418</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.3661058743984409</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.05055780721179959</v>
-      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>0.3328004140349778</v>
+        <v>0.165730761755151</v>
       </c>
       <c r="P38" t="n">
-        <v>0.426784241468339</v>
+        <v>0.3643945447399982</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.2404153444966831</v>
+        <v>0.4698746935048509</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
-        <v>0.1548198776294972</v>
-      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.1548198776294972</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
-        <v>0.426784241468339</v>
-      </c>
-      <c r="W38" t="n">
-        <v>3.5</v>
-      </c>
+        <v>0.530125306495149</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>29.87489690278373</v>
+        <v>37.10877145466043</v>
       </c>
       <c r="Z38" t="n">
-        <v>29.87489690278373</v>
+        <v>37.10877145466043</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>OU7ZWg1D</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45477.0625</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3300,86 +3660,66 @@
       <c r="F39" t="n">
         <v>1671</v>
       </c>
-      <c r="G39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.5180518051805181</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.2257225722572257</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.2562256225622562</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.05481359579720224</v>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
         <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0.2032595674696957</v>
+        <v>0.1804427270102636</v>
       </c>
       <c r="P39" t="n">
-        <v>0.2226757413052</v>
+        <v>0.3316364199201491</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.5740646912251044</v>
+        <v>0.4879208530695873</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
-      <c r="S39" t="n">
-        <v>0.3178390686628482</v>
-      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="n">
-        <v>2</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.3178390686628482</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
-        <v>0.5740646912251044</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3.7</v>
-      </c>
+        <v>0.5120791469304127</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>40.18452838575731</v>
+        <v>35.84554028512889</v>
       </c>
       <c r="Z39" t="n">
-        <v>40.18452838575731</v>
+        <v>35.84554028512889</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>xYeHewvE</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45478.02083333334</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3388,86 +3728,66 @@
       <c r="F40" t="n">
         <v>1671</v>
       </c>
-      <c r="G40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H40" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="I40" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.7239382239382238</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.1505791505791506</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.1254826254826255</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.06256410256410261</v>
-      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.3349990233680442</v>
+        <v>0.1555948135238605</v>
       </c>
       <c r="P40" t="n">
-        <v>0.3841275358129648</v>
+        <v>0.460780950832072</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.280873440818991</v>
+        <v>0.3836242356440675</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="n">
-        <v>0.2335483852338142</v>
-      </c>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0.2335483852338142</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
-        <v>0.3841275358129648</v>
-      </c>
-      <c r="W40" t="n">
-        <v>6.25</v>
-      </c>
+        <v>0.539219049167928</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>26.88892750690754</v>
+        <v>37.74533344175496</v>
       </c>
       <c r="Z40" t="n">
-        <v>26.88892750690754</v>
+        <v>37.74533344175496</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>jy0LfcgK</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45478.0625</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3476,155 +3796,1067 @@
       <c r="F41" t="n">
         <v>1671</v>
       </c>
-      <c r="G41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.439632042928325</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.2554618627826753</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.3049060942889996</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.05796719450132803</v>
-      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3153639087876114</v>
+        <v>0.2464572160737567</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2454734549405155</v>
+        <v>0.4197114665611633</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.33383131736508</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="n">
-        <v>0.1342565419828735</v>
-      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
-        <v>2</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0.1342565419828735</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="n">
-        <v>0.4391626362718731</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3.1</v>
-      </c>
+        <v>0.5802885334388367</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>30.74138453903112</v>
+        <v>40.62019734071857</v>
       </c>
       <c r="Z41" t="n">
-        <v>30.74138453903112</v>
+        <v>40.62019734071857</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YakQgH8Q</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45478.10416666666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.1912627821864503</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.5240250406309664</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.2847121771825833</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>0.4759749593690336</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>33.31824715583235</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>33.31824715583235</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>167</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.1339057857071087</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.3791454438510249</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.4869487704418664</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="n">
+        <v>0.5130512295581335</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y43" t="n">
+        <v>35.91358606906935</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>35.91358606906935</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>167</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.6970129084589971</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.1478901277561028</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.1550969637849001</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="n">
+        <v>0.3029870915410029</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y44" t="n">
+        <v>21.2090964078702</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>21.2090964078702</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>167</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.1032657155921802</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.3638537276127817</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.5328805567950382</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="n">
+        <v>0.4671194432049618</v>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y45" t="n">
+        <v>32.69836102434733</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>32.69836102434733</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>167</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.2186122003093852</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.4397178547663033</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.3416699449243116</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="n">
+        <v>0.5602821452336968</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y46" t="n">
+        <v>39.21975016635878</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>39.21975016635878</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>167</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.1753271859574902</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.3795316382043792</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.4451411758381306</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="n">
+        <v>0.5548588241618694</v>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y47" t="n">
+        <v>38.84011769133085</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>38.84011769133085</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45480.02083333334</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>167</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.3635616090733832</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.3758222204173031</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.2606161705093137</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="n">
+        <v>0.6241777795826969</v>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y48" t="n">
+        <v>43.69244457078879</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>43.69244457078879</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45480.0625</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>167</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>2</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.2170576406952672</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.215256431144031</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.5676859281607018</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="n">
+        <v>0.4323140718392982</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y49" t="n">
+        <v>30.26198502875087</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>30.26198502875087</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45480.10416666666</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>seattle sounders</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>167</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.1862907893755237</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.3809950351800475</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.4327141754444288</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="n">
+        <v>0.5672858245555712</v>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y50" t="n">
+        <v>39.71000771888998</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>39.71000771888998</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>167</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.1172133659454251</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.3491915500948359</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.533595083959739</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="n">
+        <v>0.466404916040261</v>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y51" t="n">
+        <v>32.64834412281827</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>32.64834412281827</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>fc dallas</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>167</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H42" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.6038755619308649</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.2312401542027946</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.1648842838663405</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.05475815766188674</v>
-      </c>
-      <c r="N42" t="n">
+      <c r="E52" t="n">
+        <v>167</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
         <v>2</v>
       </c>
-      <c r="O42" t="n">
-        <v>0.2068043869608158</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.242857704879984</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.5503379081592003</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.3854536242928598</v>
-      </c>
-      <c r="T42" t="n">
+      <c r="O52" t="n">
+        <v>0.2519730838065383</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.1717278774908062</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.5762990387026554</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="n">
+        <v>0.4237009612973446</v>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y52" t="n">
+        <v>29.65906729081412</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>29.65906729081412</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>45481.0625</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>167</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.1053620075900685</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.584721392714579</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.3099165996953525</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="n">
+        <v>0.415278607285421</v>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y53" t="n">
+        <v>29.06950250997947</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>29.06950250997947</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>167</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.4173085263408691</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.4131424591513406</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.1695490145077903</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="n">
+        <v>0.5826914736591309</v>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y54" t="n">
+        <v>40.78840315613916</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>40.78840315613916</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>167</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
         <v>2</v>
       </c>
-      <c r="U42" t="n">
-        <v>0.3854536242928598</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.5503379081592003</v>
-      </c>
-      <c r="W42" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y42" t="n">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>38.52365357114402</v>
+      <c r="O55" t="n">
+        <v>0.1942455617650128</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.3935222465769074</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.4122321916580799</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="n">
+        <v>0.5877678083419201</v>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y55" t="n">
+        <v>41.14374658393441</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>41.14374658393441</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>45481.83333333334</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>167</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.2753350332114494</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.3677670757637634</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.3568978910247871</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="n">
+        <v>0.6322329242362366</v>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y56" t="n">
+        <v>44.25630469653656</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>44.25630469653656</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -1794,20 +1794,20 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>W0zNyInr</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45471.97916666666</v>
+        <v>45476.9375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1816,86 +1816,66 @@
       <c r="F16" t="n">
         <v>1671</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.483021608861449</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.2478663519157435</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.2691120392228073</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.06169269327164084</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1642468697849789</v>
+        <v>0.2910801910715639</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3239081110463583</v>
+        <v>0.3187300557940925</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5118450191686629</v>
+        <v>0.3901897531343437</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
-        <v>0.2427329799458556</v>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.2427329799458556</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5118450191686629</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.5</v>
-      </c>
+        <v>0.6098102468656563</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>35.8291513418064</v>
+        <v>42.68671728059594</v>
       </c>
       <c r="Z16" t="n">
-        <v>35.8291513418064</v>
+        <v>42.68671728059594</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1904,86 +1884,66 @@
       <c r="F17" t="n">
         <v>1671</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.542180339508165</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.2344929968372814</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.2233266636545537</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.06612992017616293</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5495201590542395</v>
+        <v>0.11859282169494</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2376684911701525</v>
+        <v>0.2891652246559143</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2128113497756081</v>
+        <v>0.5922419536491457</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
-        <v>0.007339819546074433</v>
-      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.007339819546074433</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5495201590542395</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.73</v>
-      </c>
+        <v>0.4077580463508543</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>38.46641113379676</v>
+        <v>28.5430632445598</v>
       </c>
       <c r="Z17" t="n">
-        <v>38.46641113379676</v>
+        <v>28.5430632445598</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1992,86 +1952,66 @@
       <c r="F18" t="n">
         <v>1671</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.3236831523924407</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.268194611982308</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.4081222356252514</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.06532448061683449</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1112666056438713</v>
+        <v>0.1300286073032101</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4673436835784407</v>
+        <v>0.2959344201278853</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4213897107776879</v>
+        <v>0.5740369725689046</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
-        <v>0.1991490715961327</v>
-      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.1991490715961327</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4673436835784407</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.5</v>
-      </c>
+        <v>0.4259630274310954</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>32.71405785049085</v>
+        <v>29.81741192017668</v>
       </c>
       <c r="Z18" t="n">
-        <v>32.71405785049085</v>
+        <v>29.81741192017668</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2080,86 +2020,66 @@
       <c r="F19" t="n">
         <v>1671</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.3223762376237624</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.2526732673267326</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.4249504950495049</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.06964331102262133</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2885538219241844</v>
+        <v>0.3021367112651189</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4315579098143414</v>
+        <v>0.3118254466460983</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2798882682614742</v>
+        <v>0.3860378420887828</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>0.1788846424876088</v>
-      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.1788846424876088</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4315579098143414</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3.7</v>
-      </c>
+        <v>0.6139621579112171</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>30.2090536870039</v>
+        <v>42.9773510537852</v>
       </c>
       <c r="Z19" t="n">
-        <v>30.2090536870039</v>
+        <v>42.9773510537852</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2168,86 +2088,66 @@
       <c r="F20" t="n">
         <v>1671</v>
       </c>
-      <c r="G20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5546995377503853</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.2357473035439137</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.2095531587057011</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.06045751633986929</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2696524984710746</v>
+        <v>0.1137181767269389</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4044565330362194</v>
+        <v>0.347281232600631</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.325890968492706</v>
+        <v>0.5390005906724301</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
-        <v>0.1687092294923057</v>
-      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.1687092294923057</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4044565330362194</v>
-      </c>
-      <c r="W20" t="n">
-        <v>4</v>
-      </c>
+        <v>0.4609994093275699</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>28.31195731253536</v>
+        <v>32.26995865292989</v>
       </c>
       <c r="Z20" t="n">
-        <v>28.31195731253536</v>
+        <v>32.26995865292989</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>vRwVZeHf</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45476.98958333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2256,86 +2156,66 @@
       <c r="F21" t="n">
         <v>1671</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.3567060741948635</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.2680391357521402</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.3752547900529964</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.06594242259641492</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
         <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1056844427493848</v>
+        <v>0.3377610251048948</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4070576290052907</v>
+        <v>0.2629343508692568</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4872579282453244</v>
+        <v>0.3993046240258485</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="n">
-        <v>0.112003138192328</v>
-      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.112003138192328</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4872579282453244</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.6006953759741516</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>34.10805497717271</v>
+        <v>42.04867631819061</v>
       </c>
       <c r="Z21" t="n">
-        <v>34.10805497717271</v>
+        <v>42.04867631819061</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>IHxZYFW0</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2344,86 +2224,66 @@
       <c r="F22" t="n">
         <v>1671</v>
       </c>
-      <c r="G22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.5220012055455093</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.2610006027727547</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.216998191681736</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.0642802155504234</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2019387812030422</v>
+        <v>0.2102050138660907</v>
       </c>
       <c r="P22" t="n">
-        <v>0.289818025706767</v>
+        <v>0.4460485145786615</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.5082431930901908</v>
+        <v>0.3437464715552478</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
-        <v>0.2912450014084549</v>
-      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.2912450014084549</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.5082431930901908</v>
-      </c>
-      <c r="W22" t="n">
-        <v>4.33</v>
-      </c>
+        <v>0.5539514854213385</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>35.57702351631336</v>
+        <v>38.7766039794937</v>
       </c>
       <c r="Z22" t="n">
-        <v>35.57702351631336</v>
+        <v>38.7766039794937</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2432,86 +2292,66 @@
       <c r="F23" t="n">
         <v>1671</v>
       </c>
-      <c r="G23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.3958218801539307</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.2770753161077515</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.3271028037383177</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.06150793650793651</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
         <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0761032136620981</v>
+        <v>0.2039683792691152</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3219959001578103</v>
+        <v>0.2195417309854106</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6019008861800916</v>
+        <v>0.5764898897454743</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="n">
-        <v>0.2747980824417739</v>
-      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.2747980824417739</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.6019008861800916</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.88</v>
-      </c>
+        <v>0.4235101102545257</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>42.13306203260642</v>
+        <v>29.6457077178168</v>
       </c>
       <c r="Z23" t="n">
-        <v>42.13306203260642</v>
+        <v>29.6457077178168</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45473.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2520,86 +2360,66 @@
       <c r="F24" t="n">
         <v>1671</v>
       </c>
-      <c r="G24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.5228187919463088</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.2476510067114094</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.2295302013422819</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.06261588931678785</v>
-      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
         <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3408279566753958</v>
+        <v>0.165730761755151</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1450477685978707</v>
+        <v>0.3643945447399982</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5141242747267334</v>
+        <v>0.4698746935048509</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
-        <v>0.2845940733844515</v>
-      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.2845940733844515</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.5141242747267334</v>
-      </c>
-      <c r="W24" t="n">
-        <v>4.1</v>
-      </c>
+        <v>0.530125306495149</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>35.98869923087134</v>
+        <v>37.10877145466043</v>
       </c>
       <c r="Z24" t="n">
-        <v>35.98869923087134</v>
+        <v>37.10877145466043</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>OU7ZWg1D</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45477.0625</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2608,174 +2428,134 @@
       <c r="F25" t="n">
         <v>1671</v>
       </c>
-      <c r="G25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.6272727272727273</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.2090909090909091</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.1636363636363637</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.06280193236714959</v>
-      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4548433740951673</v>
+        <v>0.1804427270102636</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3177878431154366</v>
+        <v>0.3316364199201491</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.227368782789396</v>
+        <v>0.4879208530695873</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
       </c>
-      <c r="S25" t="n">
-        <v>-0.17242935317756</v>
-      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.17242935317756</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.4548433740951673</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0.5120791469304127</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>31.83903618666172</v>
+        <v>35.84554028512889</v>
       </c>
       <c r="Z25" t="n">
-        <v>31.83903618666172</v>
+        <v>35.84554028512889</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>xYeHewvE</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45478.02083333334</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>portland timbers</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>minnesota united</t>
-        </is>
-      </c>
       <c r="E26" t="n">
         <v>167</v>
       </c>
       <c r="F26" t="n">
         <v>1671</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.4931506849315068</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.2465753424657534</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.2602739726027397</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.06725146198830423</v>
-      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4638753279776394</v>
+        <v>0.1555948135238605</v>
       </c>
       <c r="P26" t="n">
-        <v>0.359396816040525</v>
+        <v>0.460780950832072</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1767278559818356</v>
+        <v>0.3836242356440675</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="S26" t="n">
-        <v>-0.02927535695386735</v>
-      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-0.02927535695386735</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.4638753279776394</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.9</v>
-      </c>
+        <v>0.539219049167928</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>32.47127295843476</v>
+        <v>37.74533344175496</v>
       </c>
       <c r="Z26" t="n">
-        <v>32.47127295843476</v>
+        <v>37.74533344175496</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>jy0LfcgK</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45478.0625</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2784,86 +2564,66 @@
       <c r="F27" t="n">
         <v>1671</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.3692307692307692</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.2615384615384615</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.3692307692307692</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.06209150326797408</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2337930636330741</v>
+        <v>0.2464572160737567</v>
       </c>
       <c r="P27" t="n">
-        <v>0.2864780022701863</v>
+        <v>0.4197114665611633</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4797289340967397</v>
+        <v>0.33383131736508</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="S27" t="n">
-        <v>0.1104981648659705</v>
-      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.1104981648659705</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.4797289340967397</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.55</v>
-      </c>
+        <v>0.5802885334388367</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>33.58102538677178</v>
+        <v>40.62019734071857</v>
       </c>
       <c r="Z27" t="n">
-        <v>33.58102538677178</v>
+        <v>40.62019734071857</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>YakQgH8Q</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45478.10416666666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2872,165 +2632,125 @@
       <c r="F28" t="n">
         <v>1671</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.5835764902042518</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.236348478532722</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.1800750312630263</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.05776014109347427</v>
-      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0.2292248832373925</v>
+        <v>0.1912627821864503</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3239337003004357</v>
+        <v>0.5240250406309664</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4468414164621718</v>
+        <v>0.2847121771825833</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="n">
-        <v>0.2667663851991455</v>
-      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0.2667663851991455</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.4468414164621718</v>
-      </c>
-      <c r="W28" t="n">
-        <v>5.25</v>
-      </c>
+        <v>0.4759749593690336</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>31.27889915235203</v>
+        <v>33.31824715583235</v>
       </c>
       <c r="Z28" t="n">
-        <v>31.27889915235203</v>
+        <v>33.31824715583235</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>xlCTyDNL</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45473.10416666666</v>
+        <v>45479.97916666666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>vancouver whitecaps</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
       <c r="E29" t="n">
         <v>167</v>
       </c>
       <c r="F29" t="n">
         <v>1671</v>
       </c>
-      <c r="G29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.5152153240048907</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.2548227143051216</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.2299619616899878</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.06062079672635434</v>
-      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1096026689551528</v>
+        <v>0.1339057857071087</v>
       </c>
       <c r="P29" t="n">
-        <v>0.6508783927570068</v>
+        <v>0.3791454438510249</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2395189382878405</v>
+        <v>0.4869487704418664</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="S29" t="n">
-        <v>0.3960556784518852</v>
-      </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.3960556784518852</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.6508783927570068</v>
-      </c>
-      <c r="W29" t="n">
-        <v>3.7</v>
-      </c>
+        <v>0.5130512295581335</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>45.56148749299047</v>
+        <v>35.91358606906935</v>
       </c>
       <c r="Z29" t="n">
-        <v>45.56148749299047</v>
+        <v>35.91358606906935</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>W0zNyInr</t>
+          <t>rRCPxg8F</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45476.9375</v>
+        <v>45479.97916666666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3039,7 +2759,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3056,27 +2776,27 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2910801910715639</v>
+        <v>0.6970129084589971</v>
       </c>
       <c r="P30" t="n">
-        <v>0.3187300557940925</v>
+        <v>0.1478901277561028</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3901897531343437</v>
+        <v>0.1550969637849001</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>0.6098102468656563</v>
+        <v>0.3029870915410029</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
@@ -3085,24 +2805,24 @@
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>42.68671728059594</v>
+        <v>21.2090964078702</v>
       </c>
       <c r="Z30" t="n">
-        <v>42.68671728059594</v>
+        <v>21.2090964078702</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>QJcftbvR</t>
+          <t>z9yhkyHs</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45479.97916666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3127,13 +2847,13 @@
         <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>0.11859282169494</v>
+        <v>0.1032657155921802</v>
       </c>
       <c r="P31" t="n">
-        <v>0.2891652246559143</v>
+        <v>0.3638537276127817</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.5922419536491457</v>
+        <v>0.5328805567950382</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3144,7 +2864,7 @@
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>0.4077580463508543</v>
+        <v>0.4671194432049618</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
@@ -3153,29 +2873,29 @@
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>28.5430632445598</v>
+        <v>32.69836102434733</v>
       </c>
       <c r="Z31" t="n">
-        <v>28.5430632445598</v>
+        <v>32.69836102434733</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>p4vRzx2l</t>
+          <t>4rtdleWm</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45479.97916666666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>dc united</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3192,27 +2912,27 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1300286073032101</v>
+        <v>0.2186122003093852</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2959344201278853</v>
+        <v>0.4397178547663033</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.5740369725689046</v>
+        <v>0.3416699449243116</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="n">
-        <v>-2</v>
+        <v>-100</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>0.4259630274310954</v>
+        <v>0.5602821452336968</v>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
@@ -3221,29 +2941,29 @@
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>29.81741192017668</v>
+        <v>39.21975016635878</v>
       </c>
       <c r="Z32" t="n">
-        <v>29.81741192017668</v>
+        <v>39.21975016635878</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>88KCueOd</t>
+          <t>rZv0mFof</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45479.97916666666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3263,13 +2983,13 @@
         <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>0.3021367112651189</v>
+        <v>0.1753271859574902</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3118254466460983</v>
+        <v>0.3795316382043792</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3860378420887828</v>
+        <v>0.4451411758381306</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3280,7 +3000,7 @@
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
-        <v>0.6139621579112171</v>
+        <v>0.5548588241618694</v>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
@@ -3289,29 +3009,29 @@
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>42.9773510537852</v>
+        <v>38.84011769133085</v>
       </c>
       <c r="Z33" t="n">
-        <v>42.9773510537852</v>
+        <v>38.84011769133085</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>naJGvFw3</t>
+          <t>QcU4nZ00</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45480.02083333334</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3328,27 +3048,27 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1137181767269389</v>
+        <v>0.3635616090733832</v>
       </c>
       <c r="P34" t="n">
-        <v>0.347281232600631</v>
+        <v>0.3758222204173031</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.5390005906724301</v>
+        <v>0.2606161705093137</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
-        <v>-2</v>
+        <v>-100</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>0.4609994093275699</v>
+        <v>0.6241777795826969</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
@@ -3357,24 +3077,24 @@
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>32.26995865292989</v>
+        <v>43.69244457078879</v>
       </c>
       <c r="Z34" t="n">
-        <v>32.26995865292989</v>
+        <v>43.69244457078879</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>vRwVZeHf</t>
+          <t>xYX8ogG6</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45476.98958333334</v>
+        <v>45480.0625</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3399,13 +3119,13 @@
         <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.3377610251048948</v>
+        <v>0.2170576406952672</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2629343508692568</v>
+        <v>0.215256431144031</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3993046240258485</v>
+        <v>0.5676859281607018</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3416,7 +3136,7 @@
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
-        <v>0.6006953759741516</v>
+        <v>0.4323140718392982</v>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
@@ -3425,29 +3145,29 @@
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>42.04867631819061</v>
+        <v>30.26198502875087</v>
       </c>
       <c r="Z35" t="n">
-        <v>42.04867631819061</v>
+        <v>30.26198502875087</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>IHxZYFW0</t>
+          <t>WfXCpDVC</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45480.10416666666</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3464,27 +3184,27 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>0.2102050138660907</v>
+        <v>0.1862907893755237</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4460485145786615</v>
+        <v>0.3809950351800475</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.3437464715552478</v>
+        <v>0.4327141754444288</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
-        <v>0.5539514854213385</v>
+        <v>0.5672858245555712</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
@@ -3493,29 +3213,29 @@
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>38.7766039794937</v>
+        <v>39.71000771888998</v>
       </c>
       <c r="Z36" t="n">
-        <v>38.7766039794937</v>
+        <v>39.71000771888998</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>UN8LwZh9</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45481.02083333334</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3535,13 +3255,13 @@
         <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2039683792691152</v>
+        <v>0.1172133659454251</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2195417309854106</v>
+        <v>0.3491915500948359</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.5764898897454743</v>
+        <v>0.533595083959739</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3552,7 +3272,7 @@
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
-        <v>0.4235101102545257</v>
+        <v>0.466404916040261</v>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
@@ -3561,29 +3281,29 @@
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>29.6457077178168</v>
+        <v>32.64834412281827</v>
       </c>
       <c r="Z37" t="n">
-        <v>29.6457077178168</v>
+        <v>32.64834412281827</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>pv9VXZo7</t>
+          <t>n3Fa8GNJ</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45481.02083333334</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3603,13 +3323,13 @@
         <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>0.165730761755151</v>
+        <v>0.2519730838065383</v>
       </c>
       <c r="P38" t="n">
-        <v>0.3643945447399982</v>
+        <v>0.1717278774908062</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4698746935048509</v>
+        <v>0.5762990387026554</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3620,7 +3340,7 @@
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
-        <v>0.530125306495149</v>
+        <v>0.4237009612973446</v>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
@@ -3629,29 +3349,29 @@
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>37.10877145466043</v>
+        <v>29.65906729081412</v>
       </c>
       <c r="Z38" t="n">
-        <v>37.10877145466043</v>
+        <v>29.65906729081412</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>OU7ZWg1D</t>
+          <t>rZ0V2fos</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45477.0625</v>
+        <v>45481.0625</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3668,27 +3388,27 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1804427270102636</v>
+        <v>0.1053620075900685</v>
       </c>
       <c r="P39" t="n">
-        <v>0.3316364199201491</v>
+        <v>0.584721392714579</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4879208530695873</v>
+        <v>0.3099165996953525</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="n">
-        <v>-2</v>
+        <v>-100</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
-        <v>0.5120791469304127</v>
+        <v>0.415278607285421</v>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
@@ -3697,29 +3417,29 @@
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>35.84554028512889</v>
+        <v>29.06950250997947</v>
       </c>
       <c r="Z39" t="n">
-        <v>35.84554028512889</v>
+        <v>29.06950250997947</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xYeHewvE</t>
+          <t>dx5Z1E0m</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45478.02083333334</v>
+        <v>45481.10416666666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3736,27 +3456,27 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1555948135238605</v>
+        <v>0.4173085263408691</v>
       </c>
       <c r="P40" t="n">
-        <v>0.460780950832072</v>
+        <v>0.4131424591513406</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.3836242356440675</v>
+        <v>0.1695490145077903</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
-        <v>0.539219049167928</v>
+        <v>0.5826914736591309</v>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
@@ -3765,29 +3485,29 @@
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>37.74533344175496</v>
+        <v>40.78840315613916</v>
       </c>
       <c r="Z40" t="n">
-        <v>37.74533344175496</v>
+        <v>40.78840315613916</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>jy0LfcgK</t>
+          <t>v1fv1YFg</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45478.0625</v>
+        <v>45481.10416666666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3804,27 +3524,27 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>0.2464572160737567</v>
+        <v>0.1942455617650128</v>
       </c>
       <c r="P41" t="n">
-        <v>0.4197114665611633</v>
+        <v>0.3935222465769074</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.33383131736508</v>
+        <v>0.4122321916580799</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="n">
-        <v>0.5802885334388367</v>
+        <v>0.5877678083419201</v>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
@@ -3833,29 +3553,29 @@
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>40.62019734071857</v>
+        <v>41.14374658393441</v>
       </c>
       <c r="Z41" t="n">
-        <v>40.62019734071857</v>
+        <v>41.14374658393441</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>YakQgH8Q</t>
+          <t>QgE37zwQ</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45478.10416666666</v>
+        <v>45481.83333333334</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3875,13 +3595,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.1912627821864503</v>
+        <v>0.2753350332114494</v>
       </c>
       <c r="P42" t="n">
-        <v>0.5240250406309664</v>
+        <v>0.3677670757637634</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.2847121771825833</v>
+        <v>0.3568978910247871</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -3892,7 +3612,7 @@
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="n">
-        <v>0.4759749593690336</v>
+        <v>0.6322329242362366</v>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
@@ -3901,29 +3621,29 @@
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>33.31824715583235</v>
+        <v>44.25630469653656</v>
       </c>
       <c r="Z42" t="n">
-        <v>33.31824715583235</v>
+        <v>44.25630469653656</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>xlCTyDNL</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45471.85416666666</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -3932,61 +3652,81 @@
       <c r="F43" t="n">
         <v>1671</v>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5066666666666666</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.2466666666666667</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.2466666666666667</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.06685633001422464</v>
+      </c>
       <c r="N43" t="n">
         <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1339057857071087</v>
+        <v>0.1642468697849789</v>
       </c>
       <c r="P43" t="n">
-        <v>0.3791454438510249</v>
+        <v>0.3239081110463583</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.4869487704418664</v>
+        <v>0.5118450191686629</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>0.2651783525019962</v>
+      </c>
       <c r="T43" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U43" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.2651783525019962</v>
+      </c>
       <c r="V43" t="n">
-        <v>0.5130512295581335</v>
-      </c>
-      <c r="W43" t="inlineStr"/>
+        <v>0.5118450191686629</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3.8</v>
+      </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>35.91358606906935</v>
+        <v>35.8291513418064</v>
       </c>
       <c r="Z43" t="n">
-        <v>35.91358606906935</v>
+        <v>35.8291513418064</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>rRCPxg8F</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4000,66 +3740,86 @@
       <c r="F44" t="n">
         <v>1671</v>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.5393258426966292</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.2359550561797753</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.2247191011235955</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.05952380952380953</v>
+      </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6970129084589971</v>
+        <v>0.5526446645642641</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1478901277561028</v>
+        <v>0.2389922603916535</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.1550969637849001</v>
+        <v>0.2083630750440825</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>0.01331882186763489</v>
+      </c>
       <c r="T44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.01331882186763489</v>
+      </c>
       <c r="V44" t="n">
-        <v>0.3029870915410029</v>
-      </c>
-      <c r="W44" t="inlineStr"/>
+        <v>0.5526446645642641</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.75</v>
+      </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y44" t="n">
-        <v>21.2090964078702</v>
+        <v>38.68512651949849</v>
       </c>
       <c r="Z44" t="n">
-        <v>21.2090964078702</v>
+        <v>38.68512651949849</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>z9yhkyHs</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4068,66 +3828,86 @@
       <c r="F45" t="n">
         <v>1671</v>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.369093490164267</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.2689109714053944</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.3619955384303387</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.06248653307476837</v>
+      </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1032657155921802</v>
+        <v>0.1112666056438713</v>
       </c>
       <c r="P45" t="n">
-        <v>0.3638537276127817</v>
+        <v>0.4673436835784407</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.5328805567950382</v>
+        <v>0.4213897107776879</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
       </c>
-      <c r="S45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>0.1984327121730463</v>
+      </c>
       <c r="T45" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U45" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.1984327121730463</v>
+      </c>
       <c r="V45" t="n">
-        <v>0.4671194432049618</v>
-      </c>
-      <c r="W45" t="inlineStr"/>
+        <v>0.4673436835784407</v>
+      </c>
+      <c r="W45" t="n">
+        <v>3.5</v>
+      </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y45" t="n">
-        <v>32.69836102434733</v>
+        <v>32.71405785049085</v>
       </c>
       <c r="Z45" t="n">
-        <v>32.69836102434733</v>
+        <v>32.71405785049085</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>4rtdleWm</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -4136,66 +3916,86 @@
       <c r="F46" t="n">
         <v>1671</v>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.3129548762736535</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.2503639010189229</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.4366812227074235</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.06511627906976747</v>
+      </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0.2186122003093852</v>
+        <v>0.2885538219241844</v>
       </c>
       <c r="P46" t="n">
-        <v>0.4397178547663033</v>
+        <v>0.4315579098143414</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.3416699449243116</v>
+        <v>0.2798882682614742</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>0.1811940087954185</v>
+      </c>
       <c r="T46" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.1811940087954185</v>
+      </c>
       <c r="V46" t="n">
-        <v>0.5602821452336968</v>
-      </c>
-      <c r="W46" t="inlineStr"/>
+        <v>0.4315579098143414</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.75</v>
+      </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>39.21975016635878</v>
+        <v>30.2090536870039</v>
       </c>
       <c r="Z46" t="n">
-        <v>39.21975016635878</v>
+        <v>30.2090536870039</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>rZv0mFof</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -4204,66 +4004,86 @@
       <c r="F47" t="n">
         <v>1671</v>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.6386964914272737</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.2100601794027478</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1512433291699784</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.0578978978978979</v>
+      </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0.1753271859574902</v>
+        <v>0.2696524984710746</v>
       </c>
       <c r="P47" t="n">
-        <v>0.3795316382043792</v>
+        <v>0.4044565330362194</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.4451411758381306</v>
+        <v>0.325890968492706</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
       </c>
-      <c r="S47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>0.1943963536334716</v>
+      </c>
       <c r="T47" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U47" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.1943963536334716</v>
+      </c>
       <c r="V47" t="n">
-        <v>0.5548588241618694</v>
-      </c>
-      <c r="W47" t="inlineStr"/>
+        <v>0.4044565330362194</v>
+      </c>
+      <c r="W47" t="n">
+        <v>4.5</v>
+      </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y47" t="n">
-        <v>38.84011769133085</v>
+        <v>28.31195731253536</v>
       </c>
       <c r="Z47" t="n">
-        <v>38.84011769133085</v>
+        <v>28.31195731253536</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>QcU4nZ00</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45480.02083333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -4272,66 +4092,86 @@
       <c r="F48" t="n">
         <v>1671</v>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.375767498976668</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.2762996316004912</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.3479328694228407</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.06448801742919397</v>
+      </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>0.3635616090733832</v>
+        <v>0.1041119879087057</v>
       </c>
       <c r="P48" t="n">
-        <v>0.3758222204173031</v>
+        <v>0.4088091982217832</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.2606161705093137</v>
+        <v>0.4870788138695111</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
       </c>
-      <c r="S48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>0.1391459444466704</v>
+      </c>
       <c r="T48" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U48" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.1391459444466704</v>
+      </c>
       <c r="V48" t="n">
-        <v>0.6241777795826969</v>
-      </c>
-      <c r="W48" t="inlineStr"/>
+        <v>0.4870788138695111</v>
+      </c>
+      <c r="W48" t="n">
+        <v>2.7</v>
+      </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y48" t="n">
-        <v>43.69244457078879</v>
+        <v>34.09551697086578</v>
       </c>
       <c r="Z48" t="n">
-        <v>43.69244457078879</v>
+        <v>34.09551697086578</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>xYX8ogG6</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45480.0625</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -4340,66 +4180,86 @@
       <c r="F49" t="n">
         <v>1671</v>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.2592592592592593</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2074074074074074</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.0714285714285714</v>
+      </c>
       <c r="N49" t="n">
         <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>0.2170576406952672</v>
+        <v>0.2019387812030422</v>
       </c>
       <c r="P49" t="n">
-        <v>0.215256431144031</v>
+        <v>0.289818025706767</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.5676859281607018</v>
+        <v>0.5082431930901908</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
       </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>0.3008357856827835</v>
+      </c>
       <c r="T49" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U49" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.3008357856827835</v>
+      </c>
       <c r="V49" t="n">
-        <v>0.4323140718392982</v>
-      </c>
-      <c r="W49" t="inlineStr"/>
+        <v>0.5082431930901908</v>
+      </c>
+      <c r="W49" t="n">
+        <v>4.5</v>
+      </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y49" t="n">
-        <v>30.26198502875087</v>
+        <v>35.57702351631336</v>
       </c>
       <c r="Z49" t="n">
-        <v>30.26198502875087</v>
+        <v>35.57702351631336</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>WfXCpDVC</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45480.10416666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -4408,66 +4268,86 @@
       <c r="F50" t="n">
         <v>1671</v>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.495575221238938</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.2690265486725664</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2353982300884956</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.06203007518796988</v>
+      </c>
       <c r="N50" t="n">
         <v>2</v>
       </c>
       <c r="O50" t="n">
-        <v>0.1862907893755237</v>
+        <v>0.0761032136620981</v>
       </c>
       <c r="P50" t="n">
-        <v>0.3809950351800475</v>
+        <v>0.3219959001578103</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.4327141754444288</v>
+        <v>0.6019008861800916</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>0.366502656091596</v>
+      </c>
       <c r="T50" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U50" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.366502656091596</v>
+      </c>
       <c r="V50" t="n">
-        <v>0.5672858245555712</v>
-      </c>
-      <c r="W50" t="inlineStr"/>
+        <v>0.6019008861800916</v>
+      </c>
+      <c r="W50" t="n">
+        <v>4</v>
+      </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>39.71000771888998</v>
+        <v>42.13306203260642</v>
       </c>
       <c r="Z50" t="n">
-        <v>39.71000771888998</v>
+        <v>42.13306203260642</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45481.02083333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -4476,66 +4356,86 @@
       <c r="F51" t="n">
         <v>1671</v>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.5256916996047432</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.2490118577075099</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.225296442687747</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.05680868838763575</v>
+      </c>
       <c r="N51" t="n">
         <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1172133659454251</v>
+        <v>0.3408279566753958</v>
       </c>
       <c r="P51" t="n">
-        <v>0.3491915500948359</v>
+        <v>0.1450477685978707</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.533595083959739</v>
+        <v>0.5141242747267334</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
       </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>0.2888278320389864</v>
+      </c>
       <c r="T51" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U51" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.2888278320389864</v>
+      </c>
       <c r="V51" t="n">
-        <v>0.466404916040261</v>
-      </c>
-      <c r="W51" t="inlineStr"/>
+        <v>0.5141242747267334</v>
+      </c>
+      <c r="W51" t="n">
+        <v>4.2</v>
+      </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>32.64834412281827</v>
+        <v>35.98869923087134</v>
       </c>
       <c r="Z51" t="n">
-        <v>32.64834412281827</v>
+        <v>35.98869923087134</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>n3Fa8GNJ</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45481.02083333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -4544,66 +4444,86 @@
       <c r="F52" t="n">
         <v>1671</v>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.6272727272727273</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.2090909090909091</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.1636363636363637</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.06280193236714959</v>
+      </c>
       <c r="N52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.2519730838065383</v>
+        <v>0.4548433740951673</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1717278774908062</v>
+        <v>0.3177878431154366</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.5762990387026554</v>
+        <v>0.227368782789396</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
-      <c r="S52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>-0.17242935317756</v>
+      </c>
       <c r="T52" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>-0.17242935317756</v>
+      </c>
       <c r="V52" t="n">
-        <v>0.4237009612973446</v>
-      </c>
-      <c r="W52" t="inlineStr"/>
+        <v>0.4548433740951673</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.5</v>
+      </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>29.65906729081412</v>
+        <v>31.83903618666172</v>
       </c>
       <c r="Z52" t="n">
-        <v>29.65906729081412</v>
+        <v>31.83903618666172</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>rZ0V2fos</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45481.0625</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -4612,134 +4532,174 @@
       <c r="F53" t="n">
         <v>1671</v>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.4931506849315068</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.2465753424657534</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.2602739726027397</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.06725146198830423</v>
+      </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.1053620075900685</v>
+        <v>0.4638753279776394</v>
       </c>
       <c r="P53" t="n">
-        <v>0.584721392714579</v>
+        <v>0.359396816040525</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.3099165996953525</v>
+        <v>0.1767278559818356</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
       </c>
-      <c r="S53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>-0.02927535695386735</v>
+      </c>
       <c r="T53" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>-0.02927535695386735</v>
+      </c>
       <c r="V53" t="n">
-        <v>0.415278607285421</v>
-      </c>
-      <c r="W53" t="inlineStr"/>
+        <v>0.4638753279776394</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.9</v>
+      </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>29.06950250997947</v>
+        <v>32.47127295843476</v>
       </c>
       <c r="Z53" t="n">
-        <v>29.06950250997947</v>
+        <v>32.47127295843476</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>dx5Z1E0m</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45481.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>los angeles galaxy</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>minnesota united</t>
-        </is>
-      </c>
       <c r="E54" t="n">
         <v>167</v>
       </c>
       <c r="F54" t="n">
         <v>1671</v>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.2615384615384615</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.06209150326797408</v>
+      </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
-        <v>0.4173085263408691</v>
+        <v>0.2337930636330741</v>
       </c>
       <c r="P54" t="n">
-        <v>0.4131424591513406</v>
+        <v>0.2864780022701863</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.1695490145077903</v>
+        <v>0.4797289340967397</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
       </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>0.1104981648659705</v>
+      </c>
       <c r="T54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U54" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.1104981648659705</v>
+      </c>
       <c r="V54" t="n">
-        <v>0.5826914736591309</v>
-      </c>
-      <c r="W54" t="inlineStr"/>
+        <v>0.4797289340967397</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.55</v>
+      </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>40.78840315613916</v>
+        <v>33.58102538677178</v>
       </c>
       <c r="Z54" t="n">
-        <v>40.78840315613916</v>
+        <v>33.58102538677178</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>v1fv1YFg</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45481.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -4748,66 +4708,86 @@
       <c r="F55" t="n">
         <v>1671</v>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.5835764902042518</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.236348478532722</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1800750312630263</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.05776014109347427</v>
+      </c>
       <c r="N55" t="n">
         <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>0.1942455617650128</v>
+        <v>0.2292248832373925</v>
       </c>
       <c r="P55" t="n">
-        <v>0.3935222465769074</v>
+        <v>0.3239337003004357</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.4122321916580799</v>
+        <v>0.4468414164621718</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
       </c>
-      <c r="S55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>0.2667663851991455</v>
+      </c>
       <c r="T55" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U55" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.2667663851991455</v>
+      </c>
       <c r="V55" t="n">
-        <v>0.5877678083419201</v>
-      </c>
-      <c r="W55" t="inlineStr"/>
+        <v>0.4468414164621718</v>
+      </c>
+      <c r="W55" t="n">
+        <v>5.25</v>
+      </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>41.14374658393441</v>
+        <v>31.27889915235203</v>
       </c>
       <c r="Z55" t="n">
-        <v>41.14374658393441</v>
+        <v>31.27889915235203</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>QgE37zwQ</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45481.83333333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -4816,47 +4796,67 @@
       <c r="F56" t="n">
         <v>1671</v>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.5221774193548387</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.2540322580645161</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.2237903225806452</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.06392106392106389</v>
+      </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0.2753350332114494</v>
+        <v>0.1096026689551528</v>
       </c>
       <c r="P56" t="n">
-        <v>0.3677670757637634</v>
+        <v>0.6508783927570068</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.3568978910247871</v>
+        <v>0.2395189382878405</v>
       </c>
       <c r="R56" t="n">
         <v>1</v>
       </c>
-      <c r="S56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>0.3968461346924906</v>
+      </c>
       <c r="T56" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.3968461346924906</v>
+      </c>
       <c r="V56" t="n">
-        <v>0.6322329242362366</v>
-      </c>
-      <c r="W56" t="inlineStr"/>
+        <v>0.6508783927570068</v>
+      </c>
+      <c r="W56" t="n">
+        <v>3.7</v>
+      </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y56" t="n">
-        <v>44.25630469653656</v>
+        <v>45.56148749299047</v>
       </c>
       <c r="Z56" t="n">
-        <v>44.25630469653656</v>
+        <v>45.56148749299047</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z56"/>
+  <dimension ref="A1:AB60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,16 @@
           <t>stake_to_bet</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -646,6 +656,8 @@
       <c r="Z2" t="n">
         <v>37.52960884546724</v>
       </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -734,6 +746,8 @@
       <c r="Z3" t="n">
         <v>31.71115255219031</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -822,6 +836,8 @@
       <c r="Z4" t="n">
         <v>33.32974830833433</v>
       </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -910,6 +926,8 @@
       <c r="Z5" t="n">
         <v>30.02064457154486</v>
       </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -998,6 +1016,8 @@
       <c r="Z6" t="n">
         <v>33.8459538614815</v>
       </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1086,6 +1106,8 @@
       <c r="Z7" t="n">
         <v>34.70230953497961</v>
       </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1174,6 +1196,8 @@
       <c r="Z8" t="n">
         <v>30.42791295614444</v>
       </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1262,6 +1286,8 @@
       <c r="Z9" t="n">
         <v>33.07514882490723</v>
       </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1350,6 +1376,8 @@
       <c r="Z10" t="n">
         <v>30.30030244418116</v>
       </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1438,6 +1466,8 @@
       <c r="Z11" t="n">
         <v>29.87489690278373</v>
       </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1526,6 +1556,8 @@
       <c r="Z12" t="n">
         <v>40.18452838575731</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1614,6 +1646,8 @@
       <c r="Z13" t="n">
         <v>26.88892750690754</v>
       </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1702,6 +1736,8 @@
       <c r="Z14" t="n">
         <v>30.74138453903112</v>
       </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1790,24 +1826,26 @@
       <c r="Z15" t="n">
         <v>38.52365357114402</v>
       </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>W0zNyInr</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45476.9375</v>
+        <v>45471.85416666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1816,66 +1854,96 @@
       <c r="F16" t="n">
         <v>1671</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5066666666666666</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2466666666666667</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2466666666666667</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.06685633001422464</v>
+      </c>
       <c r="N16" t="n">
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2910801910715639</v>
+        <v>0.1585296251078339</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3187300557940925</v>
+        <v>0.3603816340318831</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3901897531343437</v>
+        <v>0.4810887408602829</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0.2344220741936162</v>
+      </c>
       <c r="T16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2344220741936162</v>
+      </c>
       <c r="V16" t="n">
-        <v>0.6098102468656563</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
+        <v>0.4810887408602829</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.8</v>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>42.68671728059594</v>
+        <v>19.05443704301414</v>
       </c>
       <c r="Z16" t="n">
-        <v>42.68671728059594</v>
+        <v>19.05443704301414</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>QJcftbvR</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1884,66 +1952,96 @@
       <c r="F17" t="n">
         <v>1671</v>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5393258426966292</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2359550561797753</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2247191011235955</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.05952380952380953</v>
+      </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.11859282169494</v>
+        <v>0.600582874090608</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2891652246559143</v>
+        <v>0.2593121032056201</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5922419536491457</v>
+        <v>0.1401050227037719</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>0.06125703139397876</v>
+      </c>
       <c r="T17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.06125703139397876</v>
+      </c>
       <c r="V17" t="n">
-        <v>0.4077580463508543</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
+        <v>0.600582874090608</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.75</v>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>28.5430632445598</v>
+        <v>25.0291437045304</v>
       </c>
       <c r="Z17" t="n">
-        <v>28.5430632445598</v>
+        <v>25.0291437045304</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>p4vRzx2l</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1952,66 +2050,96 @@
       <c r="F18" t="n">
         <v>1671</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.369093490164267</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2689109714053944</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3619955384303387</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.06248653307476837</v>
+      </c>
       <c r="N18" t="n">
         <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1300286073032101</v>
+        <v>0.1011077281055308</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2959344201278853</v>
+        <v>0.2294654363350203</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5740369725689046</v>
+        <v>0.6694268355594488</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0.3074312971291102</v>
+      </c>
       <c r="T18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.3074312971291102</v>
+      </c>
       <c r="V18" t="n">
-        <v>0.4259630274310954</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
+        <v>0.6694268355594488</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.6</v>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>29.81741192017668</v>
+        <v>28.47134177797244</v>
       </c>
       <c r="Z18" t="n">
-        <v>29.81741192017668</v>
+        <v>28.47134177797244</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>88KCueOd</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2020,66 +2148,96 @@
       <c r="F19" t="n">
         <v>1671</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3129548762736535</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2503639010189229</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4366812227074235</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.06511627906976747</v>
+      </c>
       <c r="N19" t="n">
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3021367112651189</v>
+        <v>0.3174985794909022</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3118254466460983</v>
+        <v>0.2631537432633123</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3860378420887828</v>
+        <v>0.4193476772457856</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>-0.01733354546163796</v>
+      </c>
       <c r="T19" t="n">
         <v>-2</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>0.01733354546163796</v>
+      </c>
       <c r="V19" t="n">
-        <v>0.6139621579112171</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
+        <v>0.5806523227542144</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.666666666666667</v>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>42.9773510537852</v>
+        <v>24.03261613771072</v>
       </c>
       <c r="Z19" t="n">
-        <v>42.9773510537852</v>
+        <v>24.03261613771072</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>naJGvFw3</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45476.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2088,66 +2246,96 @@
       <c r="F20" t="n">
         <v>1671</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.05555555555555558</v>
+      </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1137181767269389</v>
+        <v>0.5113280515068027</v>
       </c>
       <c r="P20" t="n">
-        <v>0.347281232600631</v>
+        <v>0.2294201897299064</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5390005906724301</v>
+        <v>0.2592517587632908</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>-0.1202508958616183</v>
+      </c>
       <c r="T20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.1202508958616183</v>
+      </c>
       <c r="V20" t="n">
-        <v>0.4609994093275699</v>
-      </c>
-      <c r="W20" t="inlineStr"/>
+        <v>0.4886719484931973</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.571428571428571</v>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>32.26995865292989</v>
+        <v>19.43359742465987</v>
       </c>
       <c r="Z20" t="n">
-        <v>32.26995865292989</v>
+        <v>19.43359742465987</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>vRwVZeHf</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45476.98958333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2156,66 +2344,96 @@
       <c r="F21" t="n">
         <v>1671</v>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.375767498976668</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2762996316004912</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3479328694228407</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.06448801742919397</v>
+      </c>
       <c r="N21" t="n">
         <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3377610251048948</v>
+        <v>0.1461905207264745</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2629343508692568</v>
+        <v>0.2006163205883511</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3993046240258485</v>
+        <v>0.6531931586851744</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0.3052602892623336</v>
+      </c>
       <c r="T21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.3052602892623336</v>
+      </c>
       <c r="V21" t="n">
-        <v>0.6006953759741516</v>
-      </c>
-      <c r="W21" t="inlineStr"/>
+        <v>0.6531931586851744</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.7</v>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>42.04867631819061</v>
+        <v>27.65965793425872</v>
       </c>
       <c r="Z21" t="n">
-        <v>42.04867631819061</v>
+        <v>27.65965793425872</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>IHxZYFW0</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2224,66 +2442,96 @@
       <c r="F22" t="n">
         <v>1671</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2592592592592593</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2074074074074074</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0714285714285714</v>
+      </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2102050138660907</v>
+        <v>0.2770150961145689</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4460485145786615</v>
+        <v>0.3381121763154563</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3437464715552478</v>
+        <v>0.3848727275699747</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0.1774653201625673</v>
+      </c>
       <c r="T22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.1774653201625673</v>
+      </c>
       <c r="V22" t="n">
-        <v>0.5539514854213385</v>
-      </c>
-      <c r="W22" t="inlineStr"/>
+        <v>0.3848727275699747</v>
+      </c>
+      <c r="W22" t="n">
+        <v>4.5</v>
+      </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>38.7766039794937</v>
+        <v>14.24363637849873</v>
       </c>
       <c r="Z22" t="n">
-        <v>38.7766039794937</v>
+        <v>14.24363637849873</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>UN8LwZh9</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2292,66 +2540,96 @@
       <c r="F23" t="n">
         <v>1671</v>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4983388704318937</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2491694352159468</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2524916943521595</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.05614035087719293</v>
+      </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2039683792691152</v>
+        <v>0.1822897025916111</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2195417309854106</v>
+        <v>0.4115121503485941</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5764898897454743</v>
+        <v>0.4061981470597947</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0.1623427151326473</v>
+      </c>
       <c r="T23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1623427151326473</v>
+      </c>
       <c r="V23" t="n">
-        <v>0.4235101102545257</v>
-      </c>
-      <c r="W23" t="inlineStr"/>
+        <v>0.4115121503485941</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.8</v>
+      </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>29.6457077178168</v>
+        <v>15.57560751742971</v>
       </c>
       <c r="Z23" t="n">
-        <v>29.6457077178168</v>
+        <v>15.57560751742971</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>pv9VXZo7</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45477.02083333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2360,66 +2638,96 @@
       <c r="F24" t="n">
         <v>1671</v>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5228187919463088</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2476510067114094</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2295302013422819</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.06261588931678785</v>
+      </c>
       <c r="N24" t="n">
         <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>0.165730761755151</v>
+        <v>0.2562809039497406</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3643945447399982</v>
+        <v>0.343238534749213</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4698746935048509</v>
+        <v>0.4004805613010465</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>0.1709503599587646</v>
+      </c>
       <c r="T24" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U24" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1709503599587646</v>
+      </c>
       <c r="V24" t="n">
-        <v>0.530125306495149</v>
-      </c>
-      <c r="W24" t="inlineStr"/>
+        <v>0.4004805613010465</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4.1</v>
+      </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>37.10877145466043</v>
+        <v>15.02402806505232</v>
       </c>
       <c r="Z24" t="n">
-        <v>37.10877145466043</v>
+        <v>15.02402806505232</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>OU7ZWg1D</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45477.0625</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2428,66 +2736,96 @@
       <c r="F25" t="n">
         <v>1671</v>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.6272727272727273</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2090909090909091</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1636363636363637</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.06280193236714959</v>
+      </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1804427270102636</v>
+        <v>0.6842793279755205</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3316364199201491</v>
+        <v>0.2583691465609907</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4879208530695873</v>
+        <v>0.05735152546348866</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0.05700660070279318</v>
+      </c>
       <c r="T25" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.05700660070279318</v>
+      </c>
       <c r="V25" t="n">
-        <v>0.5120791469304127</v>
-      </c>
-      <c r="W25" t="inlineStr"/>
+        <v>0.6842793279755205</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>35.84554028512889</v>
+        <v>29.21396639877602</v>
       </c>
       <c r="Z25" t="n">
-        <v>35.84554028512889</v>
+        <v>29.21396639877602</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>xYeHewvE</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45478.02083333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2496,66 +2834,96 @@
       <c r="F26" t="n">
         <v>1671</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5082095387021109</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2410737555381809</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2507167057597081</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.06361746361746357</v>
+      </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1555948135238605</v>
+        <v>0.6556394530658596</v>
       </c>
       <c r="P26" t="n">
-        <v>0.460780950832072</v>
+        <v>0.1749962637134689</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.3836242356440675</v>
+        <v>0.1693642832206717</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>0.1474299143637486</v>
+      </c>
       <c r="T26" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.1474299143637486</v>
+      </c>
       <c r="V26" t="n">
-        <v>0.539219049167928</v>
-      </c>
-      <c r="W26" t="inlineStr"/>
+        <v>0.6556394530658596</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.85</v>
+      </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>37.74533344175496</v>
+        <v>27.78197265329298</v>
       </c>
       <c r="Z26" t="n">
-        <v>37.74533344175496</v>
+        <v>27.78197265329298</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>jy0LfcgK</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45478.0625</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2564,66 +2932,96 @@
       <c r="F27" t="n">
         <v>1671</v>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3646038628301144</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2562081198265668</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.379188017343319</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.05488565488565467</v>
+      </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2464572160737567</v>
+        <v>0.2392310608947727</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4197114665611633</v>
+        <v>0.3227469299461854</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.33383131736508</v>
+        <v>0.4380220091590419</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0.05883399181572296</v>
+      </c>
       <c r="T27" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U27" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.05883399181572296</v>
+      </c>
       <c r="V27" t="n">
-        <v>0.5802885334388367</v>
-      </c>
-      <c r="W27" t="inlineStr"/>
+        <v>0.4380220091590419</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.5</v>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>40.62019734071857</v>
+        <v>16.9011004579521</v>
       </c>
       <c r="Z27" t="n">
-        <v>40.62019734071857</v>
+        <v>16.9011004579521</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>YakQgH8Q</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45478.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2632,66 +3030,96 @@
       <c r="F28" t="n">
         <v>1671</v>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.5835764902042518</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.236348478532722</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1800750312630263</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.05776014109347427</v>
+      </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1912627821864503</v>
+        <v>0.1104422495607779</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5240250406309664</v>
+        <v>0.3755765015243285</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2847121771825833</v>
+        <v>0.5139812489148935</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0.3339062176518672</v>
+      </c>
       <c r="T28" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U28" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.3339062176518672</v>
+      </c>
       <c r="V28" t="n">
-        <v>0.4759749593690336</v>
-      </c>
-      <c r="W28" t="inlineStr"/>
+        <v>0.5139812489148935</v>
+      </c>
+      <c r="W28" t="n">
+        <v>5.25</v>
+      </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>33.31824715583235</v>
+        <v>20.69906244574468</v>
       </c>
       <c r="Z28" t="n">
-        <v>33.31824715583235</v>
+        <v>20.69906244574468</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>xlCTyDNL</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2700,57 +3128,87 @@
       <c r="F29" t="n">
         <v>1671</v>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5221774193548387</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.2540322580645161</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2237903225806452</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.06392106392106389</v>
+      </c>
       <c r="N29" t="n">
         <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1339057857071087</v>
+        <v>0.3511615882647987</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3791454438510249</v>
+        <v>0.2676215560887525</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4869487704418664</v>
+        <v>0.3812168556464487</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0.1574265330658036</v>
+      </c>
       <c r="T29" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U29" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.1574265330658036</v>
+      </c>
       <c r="V29" t="n">
-        <v>0.5130512295581335</v>
-      </c>
-      <c r="W29" t="inlineStr"/>
+        <v>0.3812168556464487</v>
+      </c>
+      <c r="W29" t="n">
+        <v>4.2</v>
+      </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>35.91358606906935</v>
+        <v>14.06084278232244</v>
       </c>
       <c r="Z29" t="n">
-        <v>35.91358606906935</v>
+        <v>14.06084278232244</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>rRCPxg8F</t>
+          <t>W0zNyInr</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45476.8125</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2759,7 +3217,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2768,61 +3226,91 @@
       <c r="F30" t="n">
         <v>1671</v>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5636978579481398</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.2536640360766629</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1826381059751973</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.09506172839506166</v>
+      </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0.6970129084589971</v>
+        <v>0.2986195152733523</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1478901277561028</v>
+        <v>0.2383247333879759</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1550969637849001</v>
+        <v>0.4630557513386717</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>0.2804176453634744</v>
+      </c>
       <c r="T30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U30" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.2804176453634744</v>
+      </c>
       <c r="V30" t="n">
-        <v>0.3029870915410029</v>
-      </c>
-      <c r="W30" t="inlineStr"/>
+        <v>0.4630557513386717</v>
+      </c>
+      <c r="W30" t="n">
+        <v>5</v>
+      </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>21.2090964078702</v>
+        <v>18.15278756693358</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.2090964078702</v>
+        <v>18.15278756693358</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>z9yhkyHs</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2836,66 +3324,96 @@
       <c r="F31" t="n">
         <v>1671</v>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4343286698684485</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.2806431405303822</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2850281896011694</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.09638278388278376</v>
+      </c>
       <c r="N31" t="n">
         <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1032657155921802</v>
+        <v>0.1836536507829496</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3638537276127817</v>
+        <v>0.3266724605478561</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.5328805567950382</v>
+        <v>0.4896738886691943</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>0.2046456990680249</v>
+      </c>
       <c r="T31" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U31" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.2046456990680249</v>
+      </c>
       <c r="V31" t="n">
-        <v>0.4671194432049618</v>
-      </c>
-      <c r="W31" t="inlineStr"/>
+        <v>0.4896738886691943</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.2</v>
+      </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>32.69836102434733</v>
+        <v>19.48369443345971</v>
       </c>
       <c r="Z31" t="n">
-        <v>32.69836102434733</v>
+        <v>19.48369443345971</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>4rtdleWm</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2904,66 +3422,96 @@
       <c r="F32" t="n">
         <v>1671</v>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.3521126760563379</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2816901408450704</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3661971830985915</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.09230769230769242</v>
+      </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0.2186122003093852</v>
+        <v>0.1553928911572484</v>
       </c>
       <c r="P32" t="n">
-        <v>0.4397178547663033</v>
+        <v>0.3170210187805046</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.3416699449243116</v>
+        <v>0.527586090062247</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>0.1613889069636555</v>
+      </c>
       <c r="T32" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.1613889069636555</v>
+      </c>
       <c r="V32" t="n">
-        <v>0.5602821452336968</v>
-      </c>
-      <c r="W32" t="inlineStr"/>
+        <v>0.527586090062247</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.5</v>
+      </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>39.21975016635878</v>
+        <v>21.37930450311235</v>
       </c>
       <c r="Z32" t="n">
-        <v>39.21975016635878</v>
+        <v>21.37930450311235</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>rZv0mFof</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45479.97916666666</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2972,66 +3520,96 @@
       <c r="F33" t="n">
         <v>1671</v>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.5811960717106538</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.2433274220228604</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.1754765062664858</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.09591703413359465</v>
+      </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1753271859574902</v>
+        <v>0.303257120057161</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3795316382043792</v>
+        <v>0.4890266717119621</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4451411758381306</v>
+        <v>0.2077162082308768</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>0.2456992496891018</v>
+      </c>
       <c r="T33" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.2456992496891018</v>
+      </c>
       <c r="V33" t="n">
-        <v>0.5548588241618694</v>
-      </c>
-      <c r="W33" t="inlineStr"/>
+        <v>0.4890266717119621</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.75</v>
+      </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>38.84011769133085</v>
+        <v>19.45133358559811</v>
       </c>
       <c r="Z33" t="n">
-        <v>38.84011769133085</v>
+        <v>19.45133358559811</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>QcU4nZ00</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45480.02083333334</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3040,61 +3618,91 @@
       <c r="F34" t="n">
         <v>1671</v>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.0969643383436487</v>
+      </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>0.3635616090733832</v>
+        <v>0.09331688082328962</v>
       </c>
       <c r="P34" t="n">
-        <v>0.3758222204173031</v>
+        <v>0.2367728396021617</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2606161705093137</v>
+        <v>0.6699102795745489</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>0.3555631543730443</v>
+      </c>
       <c r="T34" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U34" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.3555631543730443</v>
+      </c>
       <c r="V34" t="n">
-        <v>0.6241777795826969</v>
-      </c>
-      <c r="W34" t="inlineStr"/>
+        <v>0.6699102795745489</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.9</v>
+      </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>43.69244457078879</v>
+        <v>28.49551397872744</v>
       </c>
       <c r="Z34" t="n">
-        <v>43.69244457078879</v>
+        <v>28.49551397872744</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>xYX8ogG6</t>
+          <t>vRwVZeHf</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45480.0625</v>
+        <v>45476.86458333334</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3108,66 +3716,96 @@
       <c r="F35" t="n">
         <v>1671</v>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.0969643383436487</v>
+      </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.2170576406952672</v>
+        <v>0.3927384873205019</v>
       </c>
       <c r="P35" t="n">
-        <v>0.215256431144031</v>
+        <v>0.2829980502106852</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5676859281607018</v>
+        <v>0.3242634624688129</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>-0.01242002960588179</v>
+      </c>
       <c r="T35" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.01242002960588179</v>
+      </c>
       <c r="V35" t="n">
-        <v>0.4323140718392982</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
+        <v>0.6072615126794981</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.532520325203252</v>
+      </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>30.26198502875087</v>
+        <v>25.3630756339749</v>
       </c>
       <c r="Z35" t="n">
-        <v>30.26198502875087</v>
+        <v>25.3630756339749</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>WfXCpDVC</t>
+          <t>IHxZYFW0</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45480.10416666666</v>
+        <v>45476.89583333334</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3176,66 +3814,96 @@
       <c r="F36" t="n">
         <v>1671</v>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.0969643383436487</v>
+      </c>
       <c r="N36" t="n">
         <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1862907893755237</v>
+        <v>0.332706312209954</v>
       </c>
       <c r="P36" t="n">
-        <v>0.3809950351800475</v>
+        <v>0.2913184969117958</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.4327141754444288</v>
+        <v>0.3759751908782502</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>0.06162806567674561</v>
+      </c>
       <c r="T36" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U36" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.06162806567674561</v>
+      </c>
       <c r="V36" t="n">
-        <v>0.5672858245555712</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
+        <v>0.3759751908782502</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.9</v>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>39.71000771888998</v>
+        <v>13.79875954391251</v>
       </c>
       <c r="Z36" t="n">
-        <v>39.71000771888998</v>
+        <v>13.79875954391251</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45481.02083333334</v>
+        <v>45476.89583333334</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3244,66 +3912,96 @@
       <c r="F37" t="n">
         <v>1671</v>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.0969643383436487</v>
+      </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1172133659454251</v>
+        <v>0.2399367110755938</v>
       </c>
       <c r="P37" t="n">
-        <v>0.3491915500948359</v>
+        <v>0.4607248436047824</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.533595083959739</v>
+        <v>0.2993384453196239</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
       </c>
-      <c r="S37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>0.1802304857326706</v>
+      </c>
       <c r="T37" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.1802304857326706</v>
+      </c>
       <c r="V37" t="n">
-        <v>0.466404916040261</v>
-      </c>
-      <c r="W37" t="inlineStr"/>
+        <v>0.4607248436047824</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.25</v>
+      </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>32.64834412281827</v>
+        <v>18.03624218023912</v>
       </c>
       <c r="Z37" t="n">
-        <v>32.64834412281827</v>
+        <v>18.03624218023912</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>n3Fa8GNJ</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45481.02083333334</v>
+        <v>45476.89583333334</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3312,66 +4010,96 @@
       <c r="F38" t="n">
         <v>1671</v>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.5639990501068629</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.2436475896461648</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1923533602469722</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.09447693307342431</v>
+      </c>
       <c r="N38" t="n">
         <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2519730838065383</v>
+        <v>0.3015832438805195</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1717278774908062</v>
+        <v>0.3189591270404248</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.5762990387026554</v>
+        <v>0.3794576290790557</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>0.1871042688320835</v>
+      </c>
       <c r="T38" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.1871042688320835</v>
+      </c>
       <c r="V38" t="n">
-        <v>0.4237009612973446</v>
-      </c>
-      <c r="W38" t="inlineStr"/>
+        <v>0.3794576290790557</v>
+      </c>
+      <c r="W38" t="n">
+        <v>4.75</v>
+      </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>29.65906729081412</v>
+        <v>13.97288145395278</v>
       </c>
       <c r="Z38" t="n">
-        <v>29.65906729081412</v>
+        <v>13.97288145395278</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>rZ0V2fos</t>
+          <t>OU7ZWg1D</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45481.0625</v>
+        <v>45476.9375</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3380,66 +4108,96 @@
       <c r="F39" t="n">
         <v>1671</v>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5280322219860701</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.2609987840102575</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2109689940036723</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.09469585001230074</v>
+      </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1053620075900685</v>
+        <v>0.3384884511422985</v>
       </c>
       <c r="P39" t="n">
-        <v>0.584721392714579</v>
+        <v>0.3447227435307231</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.3099165996953525</v>
+        <v>0.3167888053269785</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0.08372395952046557</v>
+      </c>
       <c r="T39" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.08372395952046557</v>
+      </c>
       <c r="V39" t="n">
-        <v>0.415278607285421</v>
-      </c>
-      <c r="W39" t="inlineStr"/>
+        <v>0.3447227435307231</v>
+      </c>
+      <c r="W39" t="n">
+        <v>3.5</v>
+      </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>29.06950250997947</v>
+        <v>12.23613717653615</v>
       </c>
       <c r="Z39" t="n">
-        <v>29.06950250997947</v>
+        <v>12.23613717653615</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>dx5Z1E0m</t>
+          <t>xYeHewvE</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45481.10416666666</v>
+        <v>45477.89583333334</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3448,66 +4206,96 @@
       <c r="F40" t="n">
         <v>1671</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.3803786574870912</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.2685025817555938</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.3511187607573149</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.09539969834087492</v>
+      </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>0.4173085263408691</v>
+        <v>0.1165722926010396</v>
       </c>
       <c r="P40" t="n">
-        <v>0.4131424591513406</v>
+        <v>0.2643952151519466</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1695490145077903</v>
+        <v>0.6190324922470138</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>0.2679137314896989</v>
+      </c>
       <c r="T40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U40" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.2679137314896989</v>
+      </c>
       <c r="V40" t="n">
-        <v>0.5826914736591309</v>
-      </c>
-      <c r="W40" t="inlineStr"/>
+        <v>0.6190324922470138</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.6</v>
+      </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>40.78840315613916</v>
+        <v>25.95162461235069</v>
       </c>
       <c r="Z40" t="n">
-        <v>40.78840315613916</v>
+        <v>25.95162461235069</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>v1fv1YFg</t>
+          <t>jy0LfcgK</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45481.10416666666</v>
+        <v>45477.9375</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3516,66 +4304,96 @@
       <c r="F41" t="n">
         <v>1671</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5636978579481398</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.2536640360766629</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1826381059751973</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.09506172839506166</v>
+      </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1942455617650128</v>
+        <v>0.3553081675807302</v>
       </c>
       <c r="P41" t="n">
-        <v>0.3935222465769074</v>
+        <v>0.3166251980902031</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4122321916580799</v>
+        <v>0.3280666343290666</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>-0.2083896903674095</v>
+      </c>
       <c r="T41" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U41" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.2083896903674095</v>
+      </c>
       <c r="V41" t="n">
-        <v>0.5877678083419201</v>
-      </c>
-      <c r="W41" t="inlineStr"/>
+        <v>0.6446918324192698</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2.093023255813954</v>
+      </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>41.14374658393441</v>
+        <v>27.23459162096349</v>
       </c>
       <c r="Z41" t="n">
-        <v>41.14374658393441</v>
+        <v>27.23459162096349</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>QgE37zwQ</t>
+          <t>YakQgH8Q</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45481.83333333334</v>
+        <v>45477.97916666666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3584,66 +4402,96 @@
       <c r="F42" t="n">
         <v>1671</v>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.3803786574870912</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.2685025817555938</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.3511187607573149</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.09539969834087492</v>
+      </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2753350332114494</v>
+        <v>0.1577702476860585</v>
       </c>
       <c r="P42" t="n">
-        <v>0.3677670757637634</v>
+        <v>0.3783477455351054</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.3568978910247871</v>
+        <v>0.4638820067788361</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
-      <c r="S42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>0.1127632460215212</v>
+      </c>
       <c r="T42" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U42" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.1127632460215212</v>
+      </c>
       <c r="V42" t="n">
-        <v>0.6322329242362366</v>
-      </c>
-      <c r="W42" t="inlineStr"/>
+        <v>0.4638820067788361</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.6</v>
+      </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>44.25630469653656</v>
+        <v>18.19410033894181</v>
       </c>
       <c r="Z42" t="n">
-        <v>44.25630469653656</v>
+        <v>18.19410033894181</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>xlCTyDNL</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45471.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -3652,81 +4500,71 @@
       <c r="F43" t="n">
         <v>1671</v>
       </c>
-      <c r="G43" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="H43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.5066666666666666</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.2466666666666667</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.2466666666666667</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.06685633001422464</v>
-      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1642468697849789</v>
+        <v>0.2198767360298228</v>
       </c>
       <c r="P43" t="n">
-        <v>0.3239081110463583</v>
+        <v>0.3762799186433601</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5118450191686629</v>
+        <v>0.4038433453268171</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="n">
-        <v>0.2651783525019962</v>
-      </c>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="n">
-        <v>2</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0.2651783525019962</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
-        <v>0.5118450191686629</v>
-      </c>
-      <c r="W43" t="n">
-        <v>3.8</v>
-      </c>
+        <v>0.5961566546731829</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>35.8291513418064</v>
+        <v>24.80783273365915</v>
       </c>
       <c r="Z43" t="n">
-        <v>35.8291513418064</v>
+        <v>24.80783273365915</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>rRCPxg8F</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3740,86 +4578,76 @@
       <c r="F44" t="n">
         <v>1671</v>
       </c>
-      <c r="G44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H44" t="n">
-        <v>4</v>
-      </c>
-      <c r="I44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.5393258426966292</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.2359550561797753</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.2247191011235955</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.05952380952380953</v>
-      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.5526446645642641</v>
+        <v>0.6517450933228697</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2389922603916535</v>
+        <v>0.2462058230352516</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.2083630750440825</v>
+        <v>0.1020490836418788</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="S44" t="n">
-        <v>0.01331882186763489</v>
-      </c>
+      <c r="S44" t="inlineStr"/>
       <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0.01331882186763489</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="n">
-        <v>0.5526446645642641</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.75</v>
-      </c>
+        <v>0.3482549066771303</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y44" t="n">
-        <v>38.68512651949849</v>
+        <v>12.41274533385652</v>
       </c>
       <c r="Z44" t="n">
-        <v>38.68512651949849</v>
+        <v>12.41274533385652</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>z9yhkyHs</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -3828,86 +4656,76 @@
       <c r="F45" t="n">
         <v>1671</v>
       </c>
-      <c r="G45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.369093490164267</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.2689109714053944</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.3619955384303387</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.06248653307476837</v>
-      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1112666056438713</v>
+        <v>0.2340252767550797</v>
       </c>
       <c r="P45" t="n">
-        <v>0.4673436835784407</v>
+        <v>0.4533277151477706</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.4213897107776879</v>
+        <v>0.3126470080971495</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
       </c>
-      <c r="S45" t="n">
-        <v>0.1984327121730463</v>
-      </c>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.1984327121730463</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="n">
-        <v>0.4673436835784407</v>
-      </c>
-      <c r="W45" t="n">
-        <v>3.5</v>
-      </c>
+        <v>0.5466722848522294</v>
+      </c>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y45" t="n">
-        <v>32.71405785049085</v>
+        <v>22.33361424261147</v>
       </c>
       <c r="Z45" t="n">
-        <v>32.71405785049085</v>
+        <v>22.33361424261147</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>4rtdleWm</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -3916,86 +4734,76 @@
       <c r="F46" t="n">
         <v>1671</v>
       </c>
-      <c r="G46" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.3129548762736535</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.2503639010189229</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.4366812227074235</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.06511627906976747</v>
-      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.2885538219241844</v>
+        <v>0.4879230264703818</v>
       </c>
       <c r="P46" t="n">
-        <v>0.4315579098143414</v>
+        <v>0.2880531314804122</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.2798882682614742</v>
+        <v>0.224023842049206</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
       </c>
-      <c r="S46" t="n">
-        <v>0.1811940087954185</v>
-      </c>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0.1811940087954185</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="n">
-        <v>0.4315579098143414</v>
-      </c>
-      <c r="W46" t="n">
-        <v>3.75</v>
-      </c>
+        <v>0.5120769735296182</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>30.2090536870039</v>
+        <v>20.60384867648091</v>
       </c>
       <c r="Z46" t="n">
-        <v>30.2090536870039</v>
+        <v>20.60384867648091</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>rZv0mFof</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>new york red bulls</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>dc united</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -4004,86 +4812,76 @@
       <c r="F47" t="n">
         <v>1671</v>
       </c>
-      <c r="G47" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H47" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I47" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.6386964914272737</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.2100601794027478</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.1512433291699784</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.0578978978978979</v>
-      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2696524984710746</v>
+        <v>0.3248000313835386</v>
       </c>
       <c r="P47" t="n">
-        <v>0.4044565330362194</v>
+        <v>0.4291690095653991</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.325890968492706</v>
+        <v>0.2460309590510623</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
       </c>
-      <c r="S47" t="n">
-        <v>0.1943963536334716</v>
-      </c>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.1943963536334716</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="n">
-        <v>0.4044565330362194</v>
-      </c>
-      <c r="W47" t="n">
-        <v>4.5</v>
-      </c>
+        <v>0.5708309904346009</v>
+      </c>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y47" t="n">
-        <v>28.31195731253536</v>
+        <v>23.54154952173005</v>
       </c>
       <c r="Z47" t="n">
-        <v>28.31195731253536</v>
+        <v>23.54154952173005</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>QcU4nZ00</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45479.89583333334</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -4092,86 +4890,76 @@
       <c r="F48" t="n">
         <v>1671</v>
       </c>
-      <c r="G48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.375767498976668</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.2762996316004912</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.3479328694228407</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.06448801742919397</v>
-      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
         <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>0.1041119879087057</v>
+        <v>0.2992059919222956</v>
       </c>
       <c r="P48" t="n">
-        <v>0.4088091982217832</v>
+        <v>0.2498873569671831</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4870788138695111</v>
+        <v>0.4509066511105214</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
       </c>
-      <c r="S48" t="n">
-        <v>0.1391459444466704</v>
-      </c>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
-        <v>2</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0.1391459444466704</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="n">
-        <v>0.4870788138695111</v>
-      </c>
-      <c r="W48" t="n">
-        <v>2.7</v>
-      </c>
+        <v>0.5490933488894787</v>
+      </c>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y48" t="n">
-        <v>34.09551697086578</v>
+        <v>22.45466744447393</v>
       </c>
       <c r="Z48" t="n">
-        <v>34.09551697086578</v>
+        <v>22.45466744447393</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>xYX8ogG6</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45479.9375</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -4180,86 +4968,76 @@
       <c r="F49" t="n">
         <v>1671</v>
       </c>
-      <c r="G49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.2592592592592593</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.2074074074074074</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.0714285714285714</v>
-      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0.2019387812030422</v>
+        <v>0.3212718705413699</v>
       </c>
       <c r="P49" t="n">
-        <v>0.289818025706767</v>
+        <v>0.390346703945361</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.5082431930901908</v>
+        <v>0.2883814255132691</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
       </c>
-      <c r="S49" t="n">
-        <v>0.3008357856827835</v>
-      </c>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="n">
-        <v>2</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0.3008357856827835</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="n">
-        <v>0.5082431930901908</v>
-      </c>
-      <c r="W49" t="n">
-        <v>4.5</v>
-      </c>
+        <v>0.609653296054639</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y49" t="n">
-        <v>35.57702351631336</v>
+        <v>25.48266480273195</v>
       </c>
       <c r="Z49" t="n">
-        <v>35.57702351631336</v>
+        <v>25.48266480273195</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>WfXCpDVC</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45479.97916666666</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -4268,86 +5046,76 @@
       <c r="F50" t="n">
         <v>1671</v>
       </c>
-      <c r="G50" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I50" t="n">
-        <v>4</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.495575221238938</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.2690265486725664</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.2353982300884956</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.06203007518796988</v>
-      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0761032136620981</v>
+        <v>0.225668000183265</v>
       </c>
       <c r="P50" t="n">
-        <v>0.3219959001578103</v>
+        <v>0.4145494309309021</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.6019008861800916</v>
+        <v>0.3597825688858328</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
       </c>
-      <c r="S50" t="n">
-        <v>0.366502656091596</v>
-      </c>
+      <c r="S50" t="inlineStr"/>
       <c r="T50" t="n">
-        <v>2</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0.366502656091596</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="n">
-        <v>0.6019008861800916</v>
-      </c>
-      <c r="W50" t="n">
-        <v>4</v>
-      </c>
+        <v>0.5854505690690979</v>
+      </c>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>42.13306203260642</v>
+        <v>24.27252845345489</v>
       </c>
       <c r="Z50" t="n">
-        <v>42.13306203260642</v>
+        <v>24.27252845345489</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45480.89583333334</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -4356,86 +5124,76 @@
       <c r="F51" t="n">
         <v>1671</v>
       </c>
-      <c r="G51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.5256916996047432</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.2490118577075099</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.225296442687747</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.05680868838763575</v>
-      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
         <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0.3408279566753958</v>
+        <v>0.1112410798441106</v>
       </c>
       <c r="P51" t="n">
-        <v>0.1450477685978707</v>
+        <v>0.266165823801843</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.5141242747267334</v>
+        <v>0.6225930963540462</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
       </c>
-      <c r="S51" t="n">
-        <v>0.2888278320389864</v>
-      </c>
+      <c r="S51" t="inlineStr"/>
       <c r="T51" t="n">
-        <v>2</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.2888278320389864</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="n">
-        <v>0.5141242747267334</v>
-      </c>
-      <c r="W51" t="n">
-        <v>4.2</v>
-      </c>
+        <v>0.3774069036459538</v>
+      </c>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>35.98869923087134</v>
+        <v>13.87034518229769</v>
       </c>
       <c r="Z51" t="n">
-        <v>35.98869923087134</v>
+        <v>13.87034518229769</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>QgE37zwQ</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45480.89583333334</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -4444,86 +5202,76 @@
       <c r="F52" t="n">
         <v>1671</v>
       </c>
-      <c r="G52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I52" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.6272727272727273</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.2090909090909091</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0.1636363636363637</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0.06280193236714959</v>
-      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>0.4548433740951673</v>
+        <v>0.2392316636670534</v>
       </c>
       <c r="P52" t="n">
-        <v>0.3177878431154366</v>
+        <v>0.3479242645368</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.227368782789396</v>
+        <v>0.4128440717961466</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
-      <c r="S52" t="n">
-        <v>-0.17242935317756</v>
-      </c>
+      <c r="S52" t="inlineStr"/>
       <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
-        <v>-0.17242935317756</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="n">
-        <v>0.4548433740951673</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0.5871559282038534</v>
+      </c>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>31.83903618666172</v>
+        <v>24.35779641019267</v>
       </c>
       <c r="Z52" t="n">
-        <v>31.83903618666172</v>
+        <v>24.35779641019267</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>n3Fa8GNJ</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45480.89583333334</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -4532,86 +5280,76 @@
       <c r="F53" t="n">
         <v>1671</v>
       </c>
-      <c r="G53" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H53" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.4931506849315068</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.2465753424657534</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.2602739726027397</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0.06725146198830423</v>
-      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>0.4638753279776394</v>
+        <v>0.2027394013853659</v>
       </c>
       <c r="P53" t="n">
-        <v>0.359396816040525</v>
+        <v>0.3507673632106973</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.1767278559818356</v>
+        <v>0.4464932354039368</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
       </c>
-      <c r="S53" t="n">
-        <v>-0.02927535695386735</v>
-      </c>
+      <c r="S53" t="inlineStr"/>
       <c r="T53" t="n">
-        <v>1</v>
-      </c>
-      <c r="U53" t="n">
-        <v>-0.02927535695386735</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="n">
-        <v>0.4638753279776394</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.9</v>
-      </c>
+        <v>0.5535067645960632</v>
+      </c>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>32.47127295843476</v>
+        <v>22.67533822980316</v>
       </c>
       <c r="Z53" t="n">
-        <v>32.47127295843476</v>
+        <v>22.67533822980316</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>rZ0V2fos</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45480.9375</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -4620,86 +5358,76 @@
       <c r="F54" t="n">
         <v>1671</v>
       </c>
-      <c r="G54" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H54" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.3692307692307692</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.2615384615384615</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0.3692307692307692</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.06209150326797408</v>
-      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
         <v>2</v>
       </c>
       <c r="O54" t="n">
-        <v>0.2337930636330741</v>
+        <v>0.1832356348957332</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2864780022701863</v>
+        <v>0.2403955547468579</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.4797289340967397</v>
+        <v>0.5763688103574088</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
       </c>
-      <c r="S54" t="n">
-        <v>0.1104981648659705</v>
-      </c>
+      <c r="S54" t="inlineStr"/>
       <c r="T54" t="n">
-        <v>2</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0.1104981648659705</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="n">
-        <v>0.4797289340967397</v>
-      </c>
-      <c r="W54" t="n">
-        <v>2.55</v>
-      </c>
+        <v>0.4236311896425912</v>
+      </c>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>33.58102538677178</v>
+        <v>16.18155948212956</v>
       </c>
       <c r="Z54" t="n">
-        <v>33.58102538677178</v>
+        <v>16.18155948212956</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>dx5Z1E0m</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45480.97916666666</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -4708,86 +5436,76 @@
       <c r="F55" t="n">
         <v>1671</v>
       </c>
-      <c r="G55" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H55" t="n">
-        <v>4</v>
-      </c>
-      <c r="I55" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.5835764902042518</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.236348478532722</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.1800750312630263</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.05776014109347427</v>
-      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0.2292248832373925</v>
+        <v>0.4443843597147053</v>
       </c>
       <c r="P55" t="n">
-        <v>0.3239337003004357</v>
+        <v>0.3332789578993695</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.4468414164621718</v>
+        <v>0.2223366823859252</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
       </c>
-      <c r="S55" t="n">
-        <v>0.2667663851991455</v>
-      </c>
+      <c r="S55" t="inlineStr"/>
       <c r="T55" t="n">
-        <v>2</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0.2667663851991455</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="n">
-        <v>0.4468414164621718</v>
-      </c>
-      <c r="W55" t="n">
-        <v>5.25</v>
-      </c>
+        <v>0.5556156402852948</v>
+      </c>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>31.27889915235203</v>
+        <v>22.78078201426474</v>
       </c>
       <c r="Z55" t="n">
-        <v>31.27889915235203</v>
+        <v>22.78078201426474</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>v1fv1YFg</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45480.97916666666</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -4796,67 +5514,327 @@
       <c r="F56" t="n">
         <v>1671</v>
       </c>
-      <c r="G56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H56" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.5221774193548387</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0.2540322580645161</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0.2237903225806452</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.06392106392106389</v>
-      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.1096026689551528</v>
+        <v>0.3771408747564578</v>
       </c>
       <c r="P56" t="n">
-        <v>0.6508783927570068</v>
+        <v>0.2843206683708714</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.2395189382878405</v>
+        <v>0.3385384568726707</v>
       </c>
       <c r="R56" t="n">
         <v>1</v>
       </c>
-      <c r="S56" t="n">
-        <v>0.3968461346924906</v>
-      </c>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.3968461346924906</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="n">
-        <v>0.6508783927570068</v>
-      </c>
-      <c r="W56" t="n">
-        <v>3.7</v>
-      </c>
+        <v>0.6228591252435423</v>
+      </c>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y56" t="n">
-        <v>45.56148749299047</v>
+        <v>26.14295626217711</v>
       </c>
       <c r="Z56" t="n">
-        <v>45.56148749299047</v>
+        <v>26.14295626217711</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>45482.83333333334</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>indy eleven</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>167</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sacramento republic</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>167</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>45483.91666666666</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>167</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.1866426214177104</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.333167626535192</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.4801897520470976</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="n">
+        <v>0.5198102479529023</v>
+      </c>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y59" t="n">
+        <v>20.99051239764512</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>20.99051239764512</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>new mexico</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>167</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -1855,55 +1855,55 @@
         <v>1671</v>
       </c>
       <c r="G16" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5066666666666666</v>
+        <v>0.510925955038516</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2466666666666667</v>
+        <v>0.2397421789026883</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2466666666666667</v>
+        <v>0.2493318660587958</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06685633001422464</v>
+        <v>0.06952501050861692</v>
       </c>
       <c r="N16" t="n">
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1585296251078339</v>
+        <v>0.1600414027325715</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3603816340318831</v>
+        <v>0.3548428194046342</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4810887408602829</v>
+        <v>0.4851157778627943</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2344220741936162</v>
+        <v>0.2357839118039984</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2344220741936162</v>
+        <v>0.2357839118039984</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4810887408602829</v>
+        <v>0.4851157778627943</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>19.05443704301414</v>
+        <v>2.425578889313971</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.05443704301414</v>
+        <v>2.425578889313971</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -1977,28 +1977,28 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.600582874090608</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2593121032056201</v>
+        <v>0.2825583427564414</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1401050227037719</v>
+        <v>0.1038652110113047</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0.06125703139397876</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0.06125703139397876</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="V17" t="n">
-        <v>0.600582874090608</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="W17" t="n">
         <v>1.75</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>25.0291437045304</v>
+        <v>3.067882231161269</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.0291437045304</v>
+        <v>3.067882231161269</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2075,28 +2075,28 @@
         <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1011077281055308</v>
+        <v>0.0706619627663416</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2294654363350203</v>
+        <v>0.2511722045198468</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6694268355594488</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3074312971291102</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3074312971291102</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6694268355594488</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="W18" t="n">
         <v>2.6</v>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>28.47134177797244</v>
+        <v>3.390829163569058</v>
       </c>
       <c r="Z18" t="n">
-        <v>28.47134177797244</v>
+        <v>3.390829163569058</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2170,45 +2170,45 @@
         <v>0.06511627906976747</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3174985794909022</v>
+        <v>0.1964722326397506</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2631537432633123</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4193476772457856</v>
+        <v>0.3909365342429724</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.01733354546163796</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="T19" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01733354546163796</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5806523227542144</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="W19" t="n">
-        <v>1.666666666666667</v>
+        <v>3.75</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>24.03261613771072</v>
+        <v>2.062956165586385</v>
       </c>
       <c r="Z19" t="n">
-        <v>24.03261613771072</v>
+        <v>2.062956165586385</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2271,28 +2271,28 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5113280515068027</v>
+        <v>0.4489400143010975</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2294201897299064</v>
+        <v>0.3040135939367658</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2592517587632908</v>
+        <v>0.2470463917621368</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1202508958616183</v>
+        <v>-0.1826389330673235</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1202508958616183</v>
+        <v>0.1826389330673235</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4886719484931973</v>
+        <v>0.5510599856989025</v>
       </c>
       <c r="W20" t="n">
         <v>2.571428571428571</v>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>19.43359742465987</v>
+        <v>2.755299928494512</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.43359742465987</v>
+        <v>2.755299928494512</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2345,55 +2345,55 @@
         <v>1671</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="J21" t="n">
-        <v>0.375767498976668</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2762996316004912</v>
+        <v>0.2689109714053944</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3479328694228407</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="M21" t="n">
-        <v>0.06448801742919397</v>
+        <v>0.06248653307476837</v>
       </c>
       <c r="N21" t="n">
         <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1461905207264745</v>
+        <v>0.1285853626482153</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2006163205883511</v>
+        <v>0.2521890736131565</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.6531931586851744</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3052602892623336</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3052602892623336</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6531931586851744</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>27.65965793425872</v>
+        <v>3.096127818693141</v>
       </c>
       <c r="Z21" t="n">
-        <v>27.65965793425872</v>
+        <v>3.096127818693141</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2467,28 +2467,28 @@
         <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2770150961145689</v>
+        <v>0.2868517150384613</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3381121763154563</v>
+        <v>0.3390256513186948</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3848727275699747</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1774653201625673</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="T22" t="n">
         <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1774653201625673</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3848727275699747</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="W22" t="n">
         <v>4.5</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>14.24363637849873</v>
+        <v>1.870613168214219</v>
       </c>
       <c r="Z22" t="n">
-        <v>14.24363637849873</v>
+        <v>1.870613168214219</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2541,55 +2541,55 @@
         <v>1671</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4983388704318937</v>
+        <v>0.4953320415712524</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2491694352159468</v>
+        <v>0.2489695261581821</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2524916943521595</v>
+        <v>0.2556984322705654</v>
       </c>
       <c r="M23" t="n">
-        <v>0.05614035087719293</v>
+        <v>0.05698837443119609</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1822897025916111</v>
+        <v>0.07899396123747764</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4115121503485941</v>
+        <v>0.2628148092904548</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4061981470597947</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1623427151326473</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1623427151326473</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4115121503485941</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="W23" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>15.57560751742971</v>
+        <v>3.290956147360338</v>
       </c>
       <c r="Z23" t="n">
-        <v>15.57560751742971</v>
+        <v>3.290956147360338</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2645,49 +2645,49 @@
         <v>3.8</v>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5228187919463088</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2476510067114094</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2295302013422819</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="M24" t="n">
-        <v>0.06261588931678785</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="N24" t="n">
         <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2562809039497406</v>
+        <v>0.2519603951479352</v>
       </c>
       <c r="P24" t="n">
-        <v>0.343238534749213</v>
+        <v>0.3332635017594314</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4004805613010465</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1709503599587646</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1709503599587646</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4004805613010465</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="W24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>15.02402806505232</v>
+        <v>2.073880515463168</v>
       </c>
       <c r="Z24" t="n">
-        <v>15.02402806505232</v>
+        <v>2.073880515463168</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2761,28 +2761,28 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6842793279755205</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2583691465609907</v>
+        <v>0.2779189034356739</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.05735152546348866</v>
+        <v>0.07194914847262197</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.05700660070279318</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0.05700660070279318</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6842793279755205</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="W25" t="n">
         <v>1.5</v>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>29.21396639877602</v>
+        <v>3.25065974045852</v>
       </c>
       <c r="Z25" t="n">
-        <v>29.21396639877602</v>
+        <v>3.25065974045852</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -2859,28 +2859,28 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6556394530658596</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1749962637134689</v>
+        <v>0.1566867042163429</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1693642832206717</v>
+        <v>0.1544764098783133</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1474299143637486</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1474299143637486</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6556394530658596</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="W26" t="n">
         <v>1.85</v>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>27.78197265329298</v>
+        <v>3.44418442952672</v>
       </c>
       <c r="Z26" t="n">
-        <v>27.78197265329298</v>
+        <v>3.44418442952672</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -2957,28 +2957,28 @@
         <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2392310608947727</v>
+        <v>0.2111363599934632</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3227469299461854</v>
+        <v>0.2528128853098374</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4380220091590419</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.05883399181572296</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0.05883399181572296</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="V27" t="n">
-        <v>0.4380220091590419</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="W27" t="n">
         <v>2.5</v>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>16.9011004579521</v>
+        <v>2.680253773483497</v>
       </c>
       <c r="Z27" t="n">
-        <v>16.9011004579521</v>
+        <v>2.680253773483497</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3055,28 +3055,28 @@
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1104422495607779</v>
+        <v>0.1101391702825879</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3755765015243285</v>
+        <v>0.3923018476563575</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.5139812489148935</v>
+        <v>0.4975589820610545</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.3339062176518672</v>
+        <v>0.3174839507980283</v>
       </c>
       <c r="T28" t="n">
         <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0.3339062176518672</v>
+        <v>0.3174839507980283</v>
       </c>
       <c r="V28" t="n">
-        <v>0.5139812489148935</v>
+        <v>0.4975589820610545</v>
       </c>
       <c r="W28" t="n">
         <v>5.25</v>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>20.69906244574468</v>
+        <v>2.487794910305273</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.69906244574468</v>
+        <v>2.487794910305273</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3153,28 +3153,28 @@
         <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>0.3511615882647987</v>
+        <v>0.3419055891466642</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2676215560887525</v>
+        <v>0.2647645273290432</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.3812168556464487</v>
+        <v>0.3933298835242927</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1574265330658036</v>
+        <v>0.1695395609436476</v>
       </c>
       <c r="T29" t="n">
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1574265330658036</v>
+        <v>0.1695395609436476</v>
       </c>
       <c r="V29" t="n">
-        <v>0.3812168556464487</v>
+        <v>0.3933298835242927</v>
       </c>
       <c r="W29" t="n">
         <v>4.2</v>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>14.06084278232244</v>
+        <v>1.966649417621464</v>
       </c>
       <c r="Z29" t="n">
-        <v>14.06084278232244</v>
+        <v>1.966649417621464</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3251,28 +3251,28 @@
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2986195152733523</v>
+        <v>0.2968325553819417</v>
       </c>
       <c r="P30" t="n">
-        <v>0.2383247333879759</v>
+        <v>0.2265005769057136</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.4630557513386717</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2804176453634744</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2804176453634744</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="V30" t="n">
-        <v>0.4630557513386717</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="W30" t="n">
         <v>5</v>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>18.15278756693358</v>
+        <v>2.383334338561724</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.15278756693358</v>
+        <v>2.383334338561724</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3349,28 +3349,28 @@
         <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1836536507829496</v>
+        <v>0.1839455355924454</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3266724605478561</v>
+        <v>0.3280930314040816</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4896738886691943</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.2046456990680249</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="T31" t="n">
         <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>0.2046456990680249</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="V31" t="n">
-        <v>0.4896738886691943</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="W31" t="n">
         <v>3.2</v>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>19.48369443345971</v>
+        <v>2.439807165017365</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.48369443345971</v>
+        <v>2.439807165017365</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3447,28 +3447,28 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1553928911572484</v>
+        <v>0.1546325039321441</v>
       </c>
       <c r="P32" t="n">
-        <v>0.3170210187805046</v>
+        <v>0.3258389601561393</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.527586090062247</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.1613889069636555</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="T32" t="n">
         <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1613889069636555</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="V32" t="n">
-        <v>0.527586090062247</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="W32" t="n">
         <v>2.5</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>21.37930450311235</v>
+        <v>2.597642679558583</v>
       </c>
       <c r="Z32" t="n">
-        <v>21.37930450311235</v>
+        <v>2.597642679558583</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3521,55 +3521,55 @@
         <v>1671</v>
       </c>
       <c r="G33" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="H33" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5811960717106538</v>
+        <v>0.6359043646830759</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2433274220228604</v>
+        <v>0.211478587792986</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1754765062664858</v>
+        <v>0.1526170475239382</v>
       </c>
       <c r="M33" t="n">
-        <v>0.09591703413359465</v>
+        <v>0.09205799332820108</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.303257120057161</v>
+        <v>0.2962823561221066</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4890266717119621</v>
+        <v>0.4856871051415895</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2077162082308768</v>
+        <v>0.2180305387363038</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2456992496891018</v>
+        <v>0.2742085173486035</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2456992496891018</v>
+        <v>0.2742085173486035</v>
       </c>
       <c r="V33" t="n">
-        <v>0.4890266717119621</v>
+        <v>0.4856871051415895</v>
       </c>
       <c r="W33" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>19.45133358559811</v>
+        <v>2.428435525707947</v>
       </c>
       <c r="Z33" t="n">
-        <v>19.45133358559811</v>
+        <v>2.428435525707947</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3643,28 +3643,28 @@
         <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>0.09331688082328962</v>
+        <v>0.09582627098066902</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2367728396021617</v>
+        <v>0.2336393823796127</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.6699102795745489</v>
+        <v>0.6705343466397182</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.3555631543730443</v>
+        <v>0.3561872214382136</v>
       </c>
       <c r="T34" t="n">
         <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>0.3555631543730443</v>
+        <v>0.3561872214382136</v>
       </c>
       <c r="V34" t="n">
-        <v>0.6699102795745489</v>
+        <v>0.6705343466397182</v>
       </c>
       <c r="W34" t="n">
         <v>2.9</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>28.49551397872744</v>
+        <v>3.352671733198591</v>
       </c>
       <c r="Z34" t="n">
-        <v>28.49551397872744</v>
+        <v>3.352671733198591</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3741,28 +3741,28 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.3927384873205019</v>
+        <v>0.4043701639172806</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2829980502106852</v>
+        <v>0.2780547405980152</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3242634624688129</v>
+        <v>0.3175750954847041</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.01242002960588179</v>
+        <v>-0.0007883530091030155</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>0.01242002960588179</v>
+        <v>0.0007883530091030155</v>
       </c>
       <c r="V35" t="n">
-        <v>0.6072615126794981</v>
+        <v>0.5956298360827194</v>
       </c>
       <c r="W35" t="n">
         <v>1.532520325203252</v>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>25.3630756339749</v>
+        <v>2.978149180413597</v>
       </c>
       <c r="Z35" t="n">
-        <v>25.3630756339749</v>
+        <v>2.978149180413597</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -3839,28 +3839,28 @@
         <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>0.332706312209954</v>
+        <v>0.3439326658646624</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2913184969117958</v>
+        <v>0.2927412809917307</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.3759751908782502</v>
+        <v>0.3633260531436069</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.06162806567674561</v>
+        <v>0.04897892794210235</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>0.06162806567674561</v>
+        <v>0.04897892794210235</v>
       </c>
       <c r="V36" t="n">
-        <v>0.3759751908782502</v>
+        <v>0.3633260531436069</v>
       </c>
       <c r="W36" t="n">
         <v>2.9</v>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>13.79875954391251</v>
+        <v>1.816630265718035</v>
       </c>
       <c r="Z36" t="n">
-        <v>13.79875954391251</v>
+        <v>1.816630265718035</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -3937,28 +3937,28 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2399367110755938</v>
+        <v>0.2448931430703108</v>
       </c>
       <c r="P37" t="n">
-        <v>0.4607248436047824</v>
+        <v>0.4556050920427626</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2993384453196239</v>
+        <v>0.2995017648869266</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.1802304857326706</v>
+        <v>0.1751107341706508</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0.1802304857326706</v>
+        <v>0.1751107341706508</v>
       </c>
       <c r="V37" t="n">
-        <v>0.4607248436047824</v>
+        <v>0.4556050920427626</v>
       </c>
       <c r="W37" t="n">
         <v>3.25</v>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>18.03624218023912</v>
+        <v>2.278025460213813</v>
       </c>
       <c r="Z37" t="n">
-        <v>18.03624218023912</v>
+        <v>2.278025460213813</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4035,28 +4035,28 @@
         <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>0.3015832438805195</v>
+        <v>0.2985644244914996</v>
       </c>
       <c r="P38" t="n">
-        <v>0.3189591270404248</v>
+        <v>0.3169153134554451</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.3794576290790557</v>
+        <v>0.3845202620530553</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.1871042688320835</v>
+        <v>0.1921669018060831</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1871042688320835</v>
+        <v>0.1921669018060831</v>
       </c>
       <c r="V38" t="n">
-        <v>0.3794576290790557</v>
+        <v>0.3845202620530553</v>
       </c>
       <c r="W38" t="n">
         <v>4.75</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>13.97288145395278</v>
+        <v>1.922601310265276</v>
       </c>
       <c r="Z38" t="n">
-        <v>13.97288145395278</v>
+        <v>1.922601310265276</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4130,45 +4130,45 @@
         <v>0.09469585001230074</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.3384884511422985</v>
+        <v>0.3422502016557549</v>
       </c>
       <c r="P39" t="n">
-        <v>0.3447227435307231</v>
+        <v>0.3415599378636597</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.3167888053269785</v>
+        <v>0.3161898604805853</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0.08372395952046557</v>
+        <v>-0.1857820203303152</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U39" t="n">
-        <v>0.08372395952046557</v>
+        <v>0.1857820203303152</v>
       </c>
       <c r="V39" t="n">
-        <v>0.3447227435307231</v>
+        <v>0.6577497983442451</v>
       </c>
       <c r="W39" t="n">
-        <v>3.5</v>
+        <v>1.935504469987229</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>12.23613717653615</v>
+        <v>3.288748991721225</v>
       </c>
       <c r="Z39" t="n">
-        <v>12.23613717653615</v>
+        <v>3.288748991721225</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4207,55 +4207,55 @@
         <v>1671</v>
       </c>
       <c r="G40" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H40" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3803786574870912</v>
+        <v>0.4329004329004328</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2685025817555938</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3511187607573149</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="M40" t="n">
-        <v>0.09539969834087492</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1165722926010396</v>
+        <v>0.1161871972015239</v>
       </c>
       <c r="P40" t="n">
-        <v>0.2643952151519466</v>
+        <v>0.2590926084503565</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.6190324922470138</v>
+        <v>0.6247201943481197</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.2679137314896989</v>
+        <v>0.300044869672795</v>
       </c>
       <c r="T40" t="n">
         <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0.2679137314896989</v>
+        <v>0.300044869672795</v>
       </c>
       <c r="V40" t="n">
-        <v>0.6190324922470138</v>
+        <v>0.6247201943481197</v>
       </c>
       <c r="W40" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>25.95162461235069</v>
+        <v>3.123600971740598</v>
       </c>
       <c r="Z40" t="n">
-        <v>25.95162461235069</v>
+        <v>3.123600971740598</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4305,55 +4305,55 @@
         <v>1671</v>
       </c>
       <c r="G41" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="H41" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5636978579481398</v>
+        <v>0.5949500412764382</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2536640360766629</v>
+        <v>0.2395456745139343</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1826381059751973</v>
+        <v>0.1655042842096274</v>
       </c>
       <c r="M41" t="n">
-        <v>0.09506172839506166</v>
+        <v>0.0985708477968541</v>
       </c>
       <c r="N41" t="n">
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3553081675807302</v>
+        <v>0.3708726163433075</v>
       </c>
       <c r="P41" t="n">
-        <v>0.3166251980902031</v>
+        <v>0.3150255188123561</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.3280666343290666</v>
+        <v>0.3141018648443366</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.2083896903674095</v>
+        <v>-0.2240774249331308</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>0.2083896903674095</v>
+        <v>0.2240774249331308</v>
       </c>
       <c r="V41" t="n">
-        <v>0.6446918324192698</v>
+        <v>0.6291273836566925</v>
       </c>
       <c r="W41" t="n">
-        <v>2.093023255813954</v>
+        <v>2.247311827956989</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>27.23459162096349</v>
+        <v>3.145636918283463</v>
       </c>
       <c r="Z41" t="n">
-        <v>27.23459162096349</v>
+        <v>3.145636918283463</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4403,55 +4403,55 @@
         <v>1671</v>
       </c>
       <c r="G42" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="H42" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3803786574870912</v>
+        <v>0.41797976447172</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2685025817555938</v>
+        <v>0.2627301376679383</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3511187607573149</v>
+        <v>0.3192900978603417</v>
       </c>
       <c r="M42" t="n">
-        <v>0.09539969834087492</v>
+        <v>0.08748196248196249</v>
       </c>
       <c r="N42" t="n">
         <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>0.1577702476860585</v>
+        <v>0.1630457610990916</v>
       </c>
       <c r="P42" t="n">
-        <v>0.3783477455351054</v>
+        <v>0.3785328609147655</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.4638820067788361</v>
+        <v>0.4584213779861428</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.1127632460215212</v>
+        <v>0.1391312801258011</v>
       </c>
       <c r="T42" t="n">
         <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0.1127632460215212</v>
+        <v>0.1391312801258011</v>
       </c>
       <c r="V42" t="n">
-        <v>0.4638820067788361</v>
+        <v>0.4584213779861428</v>
       </c>
       <c r="W42" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>18.19410033894181</v>
+        <v>2.292106889930714</v>
       </c>
       <c r="Z42" t="n">
-        <v>18.19410033894181</v>
+        <v>2.292106889930714</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4511,13 +4511,13 @@
         <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>0.2198767360298228</v>
+        <v>0.223759155178852</v>
       </c>
       <c r="P43" t="n">
-        <v>0.3762799186433601</v>
+        <v>0.3735870219714469</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.4038433453268171</v>
+        <v>0.4026538228497012</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
-        <v>0.5961566546731829</v>
+        <v>0.5973461771502988</v>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>24.80783273365915</v>
+        <v>2.986730885751494</v>
       </c>
       <c r="Z43" t="n">
-        <v>24.80783273365915</v>
+        <v>2.986730885751494</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4589,13 +4589,13 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6517450933228697</v>
+        <v>0.6553996133903959</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2462058230352516</v>
+        <v>0.2410638081451136</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.1020490836418788</v>
+        <v>0.1035365784644905</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="n">
-        <v>0.3482549066771303</v>
+        <v>0.3446003866096041</v>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Y44" t="n">
-        <v>12.41274533385652</v>
+        <v>1.723001933048021</v>
       </c>
       <c r="Z44" t="n">
-        <v>12.41274533385652</v>
+        <v>1.723001933048021</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4667,13 +4667,13 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0.2340252767550797</v>
+        <v>0.2360330562038147</v>
       </c>
       <c r="P45" t="n">
-        <v>0.4533277151477706</v>
+        <v>0.4495899136506157</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.3126470080971495</v>
+        <v>0.3143770301455694</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="n">
-        <v>0.5466722848522294</v>
+        <v>0.5504100863493844</v>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Y45" t="n">
-        <v>22.33361424261147</v>
+        <v>2.752050431746922</v>
       </c>
       <c r="Z45" t="n">
-        <v>22.33361424261147</v>
+        <v>2.752050431746922</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -4745,13 +4745,13 @@
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.4879230264703818</v>
+        <v>0.4795172639227532</v>
       </c>
       <c r="P46" t="n">
-        <v>0.2880531314804122</v>
+        <v>0.2875773278385532</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.224023842049206</v>
+        <v>0.2329054082386934</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="n">
-        <v>0.5120769735296182</v>
+        <v>0.5204827360772468</v>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>20.60384867648091</v>
+        <v>2.602413680386234</v>
       </c>
       <c r="Z46" t="n">
-        <v>20.60384867648091</v>
+        <v>2.602413680386234</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0.3248000313835386</v>
+        <v>0.3186060955835326</v>
       </c>
       <c r="P47" t="n">
-        <v>0.4291690095653991</v>
+        <v>0.4299583669421621</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.2460309590510623</v>
+        <v>0.2514355374743054</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="n">
-        <v>0.5708309904346009</v>
+        <v>0.5700416330578379</v>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="Y47" t="n">
-        <v>23.54154952173005</v>
+        <v>2.85020816528919</v>
       </c>
       <c r="Z47" t="n">
-        <v>23.54154952173005</v>
+        <v>2.85020816528919</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -4901,13 +4901,13 @@
         <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>0.2992059919222956</v>
+        <v>0.3070182371591425</v>
       </c>
       <c r="P48" t="n">
-        <v>0.2498873569671831</v>
+        <v>0.2545542891632127</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4509066511105214</v>
+        <v>0.4384274736776448</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="n">
-        <v>0.5490933488894787</v>
+        <v>0.5615725263223552</v>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Y48" t="n">
-        <v>22.45466744447393</v>
+        <v>2.807862631611776</v>
       </c>
       <c r="Z48" t="n">
-        <v>22.45466744447393</v>
+        <v>2.807862631611776</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -4979,13 +4979,13 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0.3212718705413699</v>
+        <v>0.3237649678672507</v>
       </c>
       <c r="P49" t="n">
-        <v>0.390346703945361</v>
+        <v>0.3903995195351682</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.2883814255132691</v>
+        <v>0.2858355125975812</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="n">
-        <v>0.609653296054639</v>
+        <v>0.6096004804648318</v>
       </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Y49" t="n">
-        <v>25.48266480273195</v>
+        <v>3.048002402324159</v>
       </c>
       <c r="Z49" t="n">
-        <v>25.48266480273195</v>
+        <v>3.048002402324159</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.225668000183265</v>
+        <v>0.2238260684664798</v>
       </c>
       <c r="P50" t="n">
-        <v>0.4145494309309021</v>
+        <v>0.4161708195251439</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.3597825688858328</v>
+        <v>0.3600031120083761</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="n">
-        <v>0.5854505690690979</v>
+        <v>0.5838291804748561</v>
       </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
@@ -5083,10 +5083,10 @@
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>24.27252845345489</v>
+        <v>2.919145902374281</v>
       </c>
       <c r="Z50" t="n">
-        <v>24.27252845345489</v>
+        <v>2.919145902374281</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5135,13 +5135,13 @@
         <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1112410798441106</v>
+        <v>0.1120165223774064</v>
       </c>
       <c r="P51" t="n">
-        <v>0.266165823801843</v>
+        <v>0.2698353424998143</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.6225930963540462</v>
+        <v>0.6181481351227792</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="n">
-        <v>0.3774069036459538</v>
+        <v>0.3818518648772208</v>
       </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>13.87034518229769</v>
+        <v>1.909259324386104</v>
       </c>
       <c r="Z51" t="n">
-        <v>13.87034518229769</v>
+        <v>1.909259324386104</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5213,13 +5213,13 @@
         <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>0.2392316636670534</v>
+        <v>0.2405801587546016</v>
       </c>
       <c r="P52" t="n">
-        <v>0.3479242645368</v>
+        <v>0.3523714869042734</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.4128440717961466</v>
+        <v>0.407048354341125</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="n">
-        <v>0.5871559282038534</v>
+        <v>0.592951645658875</v>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>24.35779641019267</v>
+        <v>2.964758228294375</v>
       </c>
       <c r="Z52" t="n">
-        <v>24.35779641019267</v>
+        <v>2.964758228294375</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5291,13 +5291,13 @@
         <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>0.2027394013853659</v>
+        <v>0.198872053428177</v>
       </c>
       <c r="P53" t="n">
-        <v>0.3507673632106973</v>
+        <v>0.3501070220679228</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.4464932354039368</v>
+        <v>0.4510209245039001</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="n">
-        <v>0.5535067645960632</v>
+        <v>0.5489790754960999</v>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>22.67533822980316</v>
+        <v>2.7448953774805</v>
       </c>
       <c r="Z53" t="n">
-        <v>22.67533822980316</v>
+        <v>2.7448953774805</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         <v>2</v>
       </c>
       <c r="O54" t="n">
-        <v>0.1832356348957332</v>
+        <v>0.188470341582974</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2403955547468579</v>
+        <v>0.2394887306904805</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.5763688103574088</v>
+        <v>0.5720409277265455</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="n">
-        <v>0.4236311896425912</v>
+        <v>0.4279590722734545</v>
       </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>16.18155948212956</v>
+        <v>2.139795361367272</v>
       </c>
       <c r="Z54" t="n">
-        <v>16.18155948212956</v>
+        <v>2.139795361367272</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5447,13 +5447,13 @@
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0.4443843597147053</v>
+        <v>0.4414859472229207</v>
       </c>
       <c r="P55" t="n">
-        <v>0.3332789578993695</v>
+        <v>0.3348306941728106</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2223366823859252</v>
+        <v>0.2236833586042686</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="n">
-        <v>0.5556156402852948</v>
+        <v>0.5585140527770793</v>
       </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>22.78078201426474</v>
+        <v>2.792570263885397</v>
       </c>
       <c r="Z55" t="n">
-        <v>22.78078201426474</v>
+        <v>2.792570263885397</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5525,13 +5525,13 @@
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.3771408747564578</v>
+        <v>0.3763245744414552</v>
       </c>
       <c r="P56" t="n">
-        <v>0.2843206683708714</v>
+        <v>0.2845306901402596</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.3385384568726707</v>
+        <v>0.3391447354182852</v>
       </c>
       <c r="R56" t="n">
         <v>1</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="n">
-        <v>0.6228591252435423</v>
+        <v>0.6236754255585448</v>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Y56" t="n">
-        <v>26.14295626217711</v>
+        <v>3.118377127792724</v>
       </c>
       <c r="Z56" t="n">
-        <v>26.14295626217711</v>
+        <v>3.118377127792724</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -5731,13 +5731,13 @@
         <v>2</v>
       </c>
       <c r="O59" t="n">
-        <v>0.1866426214177104</v>
+        <v>0.182855882324076</v>
       </c>
       <c r="P59" t="n">
-        <v>0.333167626535192</v>
+        <v>0.332272585414535</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.4801897520470976</v>
+        <v>0.4848715322613889</v>
       </c>
       <c r="R59" t="n">
         <v>1</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="n">
-        <v>0.5198102479529023</v>
+        <v>0.5151284677386111</v>
       </c>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Y59" t="n">
-        <v>20.99051239764512</v>
+        <v>2.575642338693056</v>
       </c>
       <c r="Z59" t="n">
-        <v>20.99051239764512</v>
+        <v>2.575642338693056</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>

--- a/p6_deployment/data/historial_predicciones.xlsx
+++ b/p6_deployment/data/historial_predicciones.xlsx
@@ -5887,28 +5887,28 @@
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.5478121359331051</v>
+        <v>0.5472927597399772</v>
       </c>
       <c r="P61" t="n">
-        <v>0.3193946784018565</v>
+        <v>0.3174877309452435</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.1327931856650388</v>
+        <v>0.1352195093147789</v>
       </c>
       <c r="R61" t="n">
         <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.07394357007552477</v>
+        <v>-0.07446294626865269</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>-0.07394357007552477</v>
+        <v>-0.07446294626865269</v>
       </c>
       <c r="V61" t="n">
-        <v>0.5478121359331051</v>
+        <v>0.5472927597399772</v>
       </c>
       <c r="W61" t="n">
         <v>1.53</v>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Y61" t="n">
-        <v>3.889293414211416</v>
+        <v>6.884337015187532</v>
       </c>
       <c r="Z61" t="n">
-        <v>3.889293414211416</v>
+        <v>6.884337015187532</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -5985,28 +5985,28 @@
         <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>0.2075059145687156</v>
+        <v>0.2100382114772122</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2996237109575965</v>
+        <v>0.2980519455785725</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.4928703744736879</v>
+        <v>0.4919098429442151</v>
       </c>
       <c r="R62" t="n">
         <v>1</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.1952030200217249</v>
+        <v>-0.1961635515511977</v>
       </c>
       <c r="T62" t="n">
         <v>2</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.1952030200217249</v>
+        <v>-0.1961635515511977</v>
       </c>
       <c r="V62" t="n">
-        <v>0.4928703744736879</v>
+        <v>0.4919098429442151</v>
       </c>
       <c r="W62" t="n">
         <v>1.36</v>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Y62" t="n">
-        <v>3.499224233569205</v>
+        <v>6.187681235770201</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.499224233569205</v>
+        <v>6.187681235770201</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -6083,28 +6083,28 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.4467977924840937</v>
+        <v>0.4465517429240594</v>
       </c>
       <c r="P63" t="n">
-        <v>0.3094895004568461</v>
+        <v>0.3099576327625041</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.2437127070590602</v>
+        <v>0.2434906243134364</v>
       </c>
       <c r="R63" t="n">
         <v>1</v>
       </c>
       <c r="S63" t="n">
-        <v>-0.3365738390178907</v>
+        <v>-0.336819888577925</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>-0.3365738390178907</v>
+        <v>-0.336819888577925</v>
       </c>
       <c r="V63" t="n">
-        <v>0.4467977924840937</v>
+        <v>0.4465517429240594</v>
       </c>
       <c r="W63" t="n">
         <v>1.22</v>
@@ -6115,10 +6115,10 @@
         </is>
       </c>
       <c r="Y63" t="n">
-        <v>3.172123430293599</v>
+        <v>5.617126553015594</v>
       </c>
       <c r="Z63" t="n">
-        <v>3.172123430293599</v>
+        <v>5.617126553015594</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -6181,28 +6181,28 @@
         <v>2</v>
       </c>
       <c r="O64" t="n">
-        <v>0.2278268765141783</v>
+        <v>0.2312737815347075</v>
       </c>
       <c r="P64" t="n">
-        <v>0.3619384246905776</v>
+        <v>0.364304302167788</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.4102346987952438</v>
+        <v>0.4044219162975047</v>
       </c>
       <c r="R64" t="n">
         <v>1</v>
       </c>
       <c r="S64" t="n">
-        <v>0.07939031083750286</v>
+        <v>0.07357752833976383</v>
       </c>
       <c r="T64" t="n">
         <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>0.07939031083750286</v>
+        <v>0.07357752833976383</v>
       </c>
       <c r="V64" t="n">
-        <v>0.4102346987952438</v>
+        <v>0.4044219162975047</v>
       </c>
       <c r="W64" t="n">
         <v>2.88</v>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Y64" t="n">
-        <v>2.91253699516467</v>
+        <v>5.087179975563296</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.91253699516467</v>
+        <v>5.087179975563296</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -6279,28 +6279,28 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.4854916296044625</v>
+        <v>0.4860935572145377</v>
       </c>
       <c r="P65" t="n">
-        <v>0.3445222740792314</v>
+        <v>0.346874166327044</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.1699860963163061</v>
+        <v>0.1670322764584181</v>
       </c>
       <c r="R65" t="n">
         <v>1</v>
       </c>
       <c r="S65" t="n">
-        <v>-0.2238268683093066</v>
+        <v>-0.2232249406992314</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>-0.2238268683093066</v>
+        <v>-0.2232249406992314</v>
       </c>
       <c r="V65" t="n">
-        <v>0.4854916296044625</v>
+        <v>0.4860935572145377</v>
       </c>
       <c r="W65" t="n">
         <v>1.33</v>
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="Y65" t="n">
-        <v>3.446837471862763</v>
+        <v>6.114518800442628</v>
       </c>
       <c r="Z65" t="n">
-        <v>3.446837471862763</v>
+        <v>6.114518800442628</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Y66" t="n">
-        <v>2.605577891638621</v>
+        <v>4.616442401246155</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.605577891638621</v>
+        <v>4.616442401246155</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -6475,28 +6475,28 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0.3805482879075007</v>
+        <v>0.3743799427639963</v>
       </c>
       <c r="P67" t="n">
-        <v>0.396365754989814</v>
+        <v>0.3946336719648086</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.2230859571026854</v>
+        <v>0.2309863852711951</v>
       </c>
       <c r="R67" t="n">
         <v>1</v>
       </c>
       <c r="S67" t="n">
-        <v>0.1255324216564806</v>
+        <v>0.1238003386314753</v>
       </c>
       <c r="T67" t="n">
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>0.1255324216564806</v>
+        <v>0.1238003386314753</v>
       </c>
       <c r="V67" t="n">
-        <v>0.396365754989814</v>
+        <v>0.3946336719648086</v>
       </c>
       <c r="W67" t="n">
         <v>3.5</v>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="Y67" t="n">
-        <v>2.81407186767594</v>
+        <v>4.964054698325397</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.81407186767594</v>
+        <v>4.964054698325397</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -6549,52 +6549,52 @@
         <v>481</v>
       </c>
       <c r="G68" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="H68" t="n">
         <v>3.4</v>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.3938223938223938</v>
       </c>
       <c r="K68" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.277992277992278</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="M68" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.05800653594771243</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0.3106801764048837</v>
+        <v>0.3144227816646827</v>
       </c>
       <c r="P68" t="n">
-        <v>0.384110555074948</v>
+        <v>0.3842052001281865</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.3052092685201684</v>
+        <v>0.3013720182071305</v>
       </c>
       <c r="R68" t="n">
         <v>1</v>
       </c>
       <c r="S68" t="n">
-        <v>0.1064901584743814</v>
+        <v>0.1062129221359085</v>
       </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>0.1064901584743814</v>
+        <v>0.1062129221359085</v>
       </c>
       <c r="V68" t="n">
-        <v>0.384110555074948</v>
+        <v>0.3842052001281865</v>
       </c>
       <c r="W68" t="n">
         <v>3.4</v>
@@ -6605,10 +6605,10 @@
         </is>
       </c>
       <c r="Y68" t="n">
-        <v>2.72706381292092</v>
+        <v>4.832876067877577</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.72706381292092</v>
+        <v>4.832876067877577</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -6671,28 +6671,28 @@
         <v>2</v>
       </c>
       <c r="O69" t="n">
-        <v>0.2820386913923193</v>
+        <v>0.2820683392247597</v>
       </c>
       <c r="P69" t="n">
-        <v>0.3396646854508487</v>
+        <v>0.3380256032651838</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.3782966231568318</v>
+        <v>0.3799060575100564</v>
       </c>
       <c r="R69" t="n">
         <v>1</v>
       </c>
       <c r="S69" t="n">
-        <v>-0.1305811565363245</v>
+        <v>-0.1289717221830999</v>
       </c>
       <c r="T69" t="n">
         <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>-0.1305811565363245</v>
+        <v>-0.1289717221830999</v>
       </c>
       <c r="V69" t="n">
-        <v>0.3782966231568318</v>
+        <v>0.3799060575100564</v>
       </c>
       <c r="W69" t="n">
         <v>1.85</v>
@@ -6703,10 +6703,10 @@
         </is>
       </c>
       <c r="Y69" t="n">
-        <v>2.685786729708283</v>
+        <v>4.778797613279301</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.685786729708283</v>
+        <v>4.778797613279301</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="Y70" t="n">
-        <v>3.686010949050913</v>
+        <v>6.53070372267968</v>
       </c>
       <c r="Z70" t="n">
-        <v>3.686010949050913</v>
+        <v>6.53070372267968</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -6849,49 +6849,49 @@
         <v>4.75</v>
       </c>
       <c r="I71" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="J71" t="n">
-        <v>0.2061603080154008</v>
+        <v>0.2077442718852288</v>
       </c>
       <c r="K71" t="n">
-        <v>0.1953097654882744</v>
+        <v>0.1968103628386378</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5985299264963249</v>
+        <v>0.5954453652761335</v>
       </c>
       <c r="M71" t="n">
-        <v>0.07790982833427651</v>
+        <v>0.06969121317093152</v>
       </c>
       <c r="N71" t="n">
         <v>2</v>
       </c>
       <c r="O71" t="n">
-        <v>0.3028390567587279</v>
+        <v>0.2992414176127644</v>
       </c>
       <c r="P71" t="n">
-        <v>0.3365992230389832</v>
+        <v>0.3364340154000717</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.3605617202022888</v>
+        <v>0.3643245669871641</v>
       </c>
       <c r="R71" t="n">
         <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>-0.2379682062940361</v>
+        <v>-0.2311207982889693</v>
       </c>
       <c r="T71" t="n">
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>-0.2379682062940361</v>
+        <v>-0.2311207982889693</v>
       </c>
       <c r="V71" t="n">
-        <v>0.3605617202022888</v>
+        <v>0.3643245669871641</v>
       </c>
       <c r="W71" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Y71" t="n">
-        <v>2.55987451137947</v>
+        <v>4.582799712613659</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.55987451137947</v>
+        <v>4.582799712613659</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -7391,10 +7391,10 @@
         </is>
       </c>
       <c r="Y77" t="n">
-        <v>3.434307874051561</v>
+        <v>6.084747855583996</v>
       </c>
       <c r="Z77" t="n">
-        <v>3.434307874051561</v>
+        <v>6.084747855583996</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="Y94" t="n">
-        <v>2.766953864951772</v>
+        <v>4.902360887174315</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.766953864951772</v>
+        <v>4.902360887174315</v>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="Y104" t="n">
-        <v>3.254462363758577</v>
+        <v>5.766105898245254</v>
       </c>
       <c r="Z104" t="n">
-        <v>3.254462363758577</v>
+        <v>5.766105898245254</v>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Y106" t="n">
-        <v>4.271171166281338</v>
+        <v>7.567463532092283</v>
       </c>
       <c r="Z106" t="n">
-        <v>4.271171166281338</v>
+        <v>7.567463532092283</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
@@ -9803,28 +9803,28 @@
         <v>2</v>
       </c>
       <c r="O107" t="n">
-        <v>0.1729686475272086</v>
+        <v>0.1664549248772655</v>
       </c>
       <c r="P107" t="n">
-        <v>0.1505997669895271</v>
+        <v>0.1487827602374613</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.6764315854832647</v>
+        <v>0.6847623148852729</v>
       </c>
       <c r="R107" t="n">
         <v>1</v>
       </c>
       <c r="S107" t="n">
-        <v>0.09637039221452426</v>
+        <v>0.1047011216165326</v>
       </c>
       <c r="T107" t="n">
         <v>2</v>
       </c>
       <c r="U107" t="n">
-        <v>0.09637039221452426</v>
+        <v>0.1047011216165326</v>
       </c>
       <c r="V107" t="n">
-        <v>0.6764315854832647</v>
+        <v>0.6847623148852729</v>
       </c>
       <c r="W107" t="n">
         <v>1.62</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="Y107" t="n">
-        <v>20.29294756449794</v>
+        <v>12.13230199941425</v>
       </c>
       <c r="Z107" t="n">
-        <v>20.29294756449794</v>
+        <v>12.13230199941425</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
@@ -9901,28 +9901,28 @@
         <v>2</v>
       </c>
       <c r="O108" t="n">
-        <v>0.2317616976083876</v>
+        <v>0.2371626881820494</v>
       </c>
       <c r="P108" t="n">
-        <v>0.1873067975146034</v>
+        <v>0.1955269582216931</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.580931504877009</v>
+        <v>0.5673103535962573</v>
       </c>
       <c r="R108" t="n">
         <v>1</v>
       </c>
       <c r="S108" t="n">
-        <v>0.1506355547212458</v>
+        <v>0.1370144034404941</v>
       </c>
       <c r="T108" t="n">
         <v>2</v>
       </c>
       <c r="U108" t="n">
-        <v>0.1506355547212458</v>
+        <v>0.1370144034404941</v>
       </c>
       <c r="V108" t="n">
-        <v>0.580931504877009</v>
+        <v>0.5673103535962573</v>
       </c>
       <c r="W108" t="n">
         <v>2.2</v>
@@ -9933,10 +9933,10 @@
         </is>
       </c>
       <c r="Y108" t="n">
-        <v>17.42794514631027</v>
+        <v>10.05134246965305</v>
       </c>
       <c r="Z108" t="n">
-        <v>17.42794514631027</v>
+        <v>10.05134246965305</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
@@ -9999,28 +9999,28 @@
         <v>2</v>
       </c>
       <c r="O109" t="n">
-        <v>0.3533679002749218</v>
+        <v>0.354926915744822</v>
       </c>
       <c r="P109" t="n">
-        <v>0.2489795619064891</v>
+        <v>0.2495066794755585</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.3976525378185889</v>
+        <v>0.3955664047796192</v>
       </c>
       <c r="R109" t="n">
         <v>1</v>
       </c>
       <c r="S109" t="n">
-        <v>0.0411338380632586</v>
+        <v>0.03904770502428889</v>
       </c>
       <c r="T109" t="n">
         <v>2</v>
       </c>
       <c r="U109" t="n">
-        <v>0.0411338380632586</v>
+        <v>0.03904770502428889</v>
       </c>
       <c r="V109" t="n">
-        <v>0.3976525378185889</v>
+        <v>0.3955664047796192</v>
       </c>
       <c r="W109" t="n">
         <v>2.63</v>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="Y109" t="n">
-        <v>11.92957613455767</v>
+        <v>7.008462614378747</v>
       </c>
       <c r="Z109" t="n">
-        <v>11.92957613455767</v>
+        <v>7.008462614378747</v>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
@@ -10097,28 +10097,28 @@
         <v>2</v>
       </c>
       <c r="O110" t="n">
-        <v>0.1295641630952608</v>
+        <v>0.1427096599821709</v>
       </c>
       <c r="P110" t="n">
-        <v>0.1728765496975989</v>
+        <v>0.1812842175949421</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.6975592872071401</v>
+        <v>0.676006122422887</v>
       </c>
       <c r="R110" t="n">
         <v>1</v>
       </c>
       <c r="S110" t="n">
-        <v>0.04369317407792372</v>
+        <v>0.02214000929367066</v>
       </c>
       <c r="T110" t="n">
         <v>2</v>
       </c>
       <c r="U110" t="n">
-        <v>0.04369317407792372</v>
+        <v>0.02214000929367066</v>
       </c>
       <c r="V110" t="n">
-        <v>0.6975592872071401</v>
+        <v>0.676006122422887</v>
       </c>
       <c r="W110" t="n">
         <v>1.45</v>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Y110" t="n">
-        <v>20.9267786162142</v>
+        <v>11.97716383101715</v>
       </c>
       <c r="Z110" t="n">
-        <v>20.9267786162142</v>
+        <v>11.97716383101715</v>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
@@ -10195,28 +10195,28 @@
         <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0.5670563869178281</v>
+        <v>0.5735556639085384</v>
       </c>
       <c r="P111" t="n">
-        <v>0.2753010456706311</v>
+        <v>0.275418703280472</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.1576425674115408</v>
+        <v>0.1510256328109897</v>
       </c>
       <c r="R111" t="n">
         <v>1</v>
       </c>
       <c r="S111" t="n">
-        <v>-0.06270139854930001</v>
+        <v>-0.05620212155858972</v>
       </c>
       <c r="T111" t="n">
         <v>1</v>
       </c>
       <c r="U111" t="n">
-        <v>-0.06270139854930001</v>
+        <v>-0.05620212155858972</v>
       </c>
       <c r="V111" t="n">
-        <v>0.5670563869178281</v>
+        <v>0.5735556639085384</v>
       </c>
       <c r="W111" t="n">
         <v>1.5</v>
@@ -10227,10 +10227,10 @@
         </is>
       </c>
       <c r="Y111" t="n">
-        <v>17.01169160753484</v>
+        <v>10.16199398937248</v>
       </c>
       <c r="Z111" t="n">
-        <v>17.01169160753484</v>
+        <v>10.16199398937248</v>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
@@ -10293,28 +10293,28 @@
         <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0.4567094682001097</v>
+        <v>0.4547109040248056</v>
       </c>
       <c r="P112" t="n">
-        <v>0.2582212984756653</v>
+        <v>0.260593877861823</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.2850692333242246</v>
+        <v>0.2846952181133715</v>
       </c>
       <c r="R112" t="n">
         <v>1</v>
       </c>
       <c r="S112" t="n">
-        <v>-0.003613961660740239</v>
+        <v>-0.005612525836044324</v>
       </c>
       <c r="T112" t="n">
         <v>1</v>
       </c>
       <c r="U112" t="n">
-        <v>-0.003613961660740239</v>
+        <v>-0.005612525836044324</v>
       </c>
       <c r="V112" t="n">
-        <v>0.4567094682001097</v>
+        <v>0.4547109040248056</v>
       </c>
       <c r="W112" t="n">
         <v>2.05</v>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Y112" t="n">
-        <v>13.70128404600329</v>
+        <v>8.056357498265502</v>
       </c>
       <c r="Z112" t="n">
-        <v>13.70128404600329</v>
+        <v>8.056357498265502</v>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
@@ -10391,28 +10391,28 @@
         <v>2</v>
       </c>
       <c r="O113" t="n">
-        <v>0.3661568152418682</v>
+        <v>0.3483132254346947</v>
       </c>
       <c r="P113" t="n">
-        <v>0.2318042695397813</v>
+        <v>0.2281432612817216</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.4020389152183506</v>
+        <v>0.4235435132835836</v>
       </c>
       <c r="R113" t="n">
         <v>1</v>
       </c>
       <c r="S113" t="n">
-        <v>-0.07145285809060742</v>
+        <v>-0.04994826002537434</v>
       </c>
       <c r="T113" t="n">
         <v>2</v>
       </c>
       <c r="U113" t="n">
-        <v>-0.07145285809060742</v>
+        <v>-0.04994826002537434</v>
       </c>
       <c r="V113" t="n">
-        <v>0.4020389152183506</v>
+        <v>0.4235435132835836</v>
       </c>
       <c r="W113" t="n">
         <v>2</v>
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="Y113" t="n">
-        <v>12.06116745655052</v>
+        <v>7.504148083719076</v>
       </c>
       <c r="Z113" t="n">
-        <v>12.06116745655052</v>
+        <v>7.504148083719076</v>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
@@ -10486,34 +10486,34 @@
         <v>0.05106209150326801</v>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>0.3787959845619371</v>
+        <v>0.3836468384032026</v>
       </c>
       <c r="P114" t="n">
-        <v>0.2353448661406139</v>
+        <v>0.2369855400499945</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.3858591492974488</v>
+        <v>0.3793676215468028</v>
       </c>
       <c r="R114" t="n">
         <v>1</v>
       </c>
       <c r="S114" t="n">
-        <v>0.08854084381746435</v>
+        <v>-0.03920586272388638</v>
       </c>
       <c r="T114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U114" t="n">
-        <v>0.08854084381746435</v>
+        <v>-0.03920586272388638</v>
       </c>
       <c r="V114" t="n">
-        <v>0.3858591492974488</v>
+        <v>0.3836468384032026</v>
       </c>
       <c r="W114" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
@@ -10521,10 +10521,10 @@
         </is>
       </c>
       <c r="Y114" t="n">
-        <v>11.57577447892346</v>
+        <v>6.79727725000165</v>
       </c>
       <c r="Z114" t="n">
-        <v>11.57577447892346</v>
+        <v>6.79727725000165</v>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
@@ -10587,28 +10587,28 @@
         <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>0.4324341330827636</v>
+        <v>0.4366857274476634</v>
       </c>
       <c r="P115" t="n">
-        <v>0.28390046926644</v>
+        <v>0.2827917961495244</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.2836653976507963</v>
+        <v>0.2805224764028122</v>
       </c>
       <c r="R115" t="n">
         <v>1</v>
       </c>
       <c r="S115" t="n">
-        <v>-0.02788929677808633</v>
+        <v>-0.02363770241318652</v>
       </c>
       <c r="T115" t="n">
         <v>1</v>
       </c>
       <c r="U115" t="n">
-        <v>-0.02788929677808633</v>
+        <v>-0.02363770241318652</v>
       </c>
       <c r="V115" t="n">
-        <v>0.4324341330827636</v>
+        <v>0.4366857274476634</v>
       </c>
       <c r="W115" t="n">
         <v>2.05</v>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Y115" t="n">
-        <v>12.97302399248291</v>
+        <v>7.736995756135612</v>
       </c>
       <c r="Z115" t="n">
-        <v>12.97302399248291</v>
+        <v>7.736995756135612</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
@@ -10735,13 +10735,13 @@
         <v>2</v>
       </c>
       <c r="O117" t="n">
-        <v>0.09632788562397251</v>
+        <v>0.0971796147990323</v>
       </c>
       <c r="P117" t="n">
-        <v>0.1182393982592243</v>
+        <v>0.1193467756926307</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.7854327161168032</v>
+        <v>0.7834736095083371</v>
       </c>
       <c r="R117" t="n">
         <v>1</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="n">
-        <v>0.2145672838831968</v>
+        <v>0.2165263904916629</v>
       </c>
       <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr">
@@ -10761,10 +10761,10 @@
         </is>
       </c>
       <c r="Y117" t="n">
-        <v>0.8110177206963003</v>
+        <v>1.450043520282718</v>
       </c>
       <c r="Z117" t="n">
-        <v>0.8110177206963003</v>
+        <v>1.450043520282718</v>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
@@ -11325,13 +11325,13 @@
         <v>2</v>
       </c>
       <c r="O126" t="n">
-        <v>0.06117359204943089</v>
+        <v>0.05890705866981628</v>
       </c>
       <c r="P126" t="n">
-        <v>0.08600848854088683</v>
+        <v>0.0850825161689492</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.8528179194096823</v>
+        <v>0.8560104251612345</v>
       </c>
       <c r="R126" t="n">
         <v>1</v>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="n">
-        <v>0.1471820805903177</v>
+        <v>0.1439895748387655</v>
       </c>
       <c r="W126" t="inlineStr"/>
       <c r="X126" t="inlineStr">
@@ -11351,10 +11351,10 @@
         </is>
       </c>
       <c r="Y126" t="n">
-        <v>0.5563162909433954</v>
+        <v>0.9642757610705874</v>
       </c>
       <c r="Z126" t="n">
-        <v>0.5563162909433954</v>
+        <v>0.9642757610705874</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
@@ -11851,13 +11851,13 @@
         <v>2</v>
       </c>
       <c r="O134" t="n">
-        <v>0.1776197490202196</v>
+        <v>0.1794567954919975</v>
       </c>
       <c r="P134" t="n">
-        <v>0.1134975541628484</v>
+        <v>0.1125722033075784</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.7088826968169321</v>
+        <v>0.7079710012004241</v>
       </c>
       <c r="R134" t="n">
         <v>1</v>
@@ -11868,7 +11868,7 @@
       </c>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="n">
-        <v>0.2911173031830679</v>
+        <v>0.2920289987995759</v>
       </c>
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr">
@@ -11877,10 +11877,10 @@
         </is>
       </c>
       <c r="Y134" t="n">
-        <v>1.100360164000171</v>
+        <v>1.955672731081154</v>
       </c>
       <c r="Z134" t="n">
-        <v>1.100360164000171</v>
+        <v>1.955672731081154</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
@@ -12569,13 +12569,13 @@
         <v>2</v>
       </c>
       <c r="O145" t="n">
-        <v>0.03980787590673734</v>
+        <v>0.03866522508709244</v>
       </c>
       <c r="P145" t="n">
-        <v>0.07123388984010177</v>
+        <v>0.0701925108605358</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.8889582342531608</v>
+        <v>0.8911422640523718</v>
       </c>
       <c r="R145" t="n">
         <v>1</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="n">
-        <v>0.1110417657468392</v>
+        <v>0.1088577359476282</v>
       </c>
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
@@ -12595,10 +12595,10 @@
         </is>
       </c>
       <c r="Y145" t="n">
-        <v>0.4197137519209032</v>
+        <v>0.7290033066411972</v>
       </c>
       <c r="Z145" t="n">
-        <v>0.4197137519209032</v>
+        <v>0.7290033066411972</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
@@ -12637,55 +12637,55 @@
         <v>594</v>
       </c>
       <c r="G146" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H146" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I146" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J146" t="n">
-        <v>0.5185185185185186</v>
+        <v>0.4926019487549621</v>
       </c>
       <c r="K146" t="n">
-        <v>0.2592592592592593</v>
+        <v>0.2674124864669794</v>
       </c>
       <c r="L146" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2399855647780585</v>
       </c>
       <c r="M146" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.06844033159822627</v>
       </c>
       <c r="N146" t="n">
         <v>1</v>
       </c>
       <c r="O146" t="n">
-        <v>0.7990466275754536</v>
+        <v>0.7830864358157542</v>
       </c>
       <c r="P146" t="n">
-        <v>0.03928553527936484</v>
+        <v>0.04088231273115332</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.1616678371451817</v>
+        <v>0.1760312514530925</v>
       </c>
       <c r="R146" t="n">
         <v>1</v>
       </c>
       <c r="S146" t="n">
-        <v>0.280528109056935</v>
+        <v>0.2904844870607921</v>
       </c>
       <c r="T146" t="n">
         <v>1</v>
       </c>
       <c r="U146" t="n">
-        <v>0.280528109056935</v>
+        <v>0.2904844870607921</v>
       </c>
       <c r="V146" t="n">
-        <v>0.7990466275754536</v>
+        <v>0.7830864358157542</v>
       </c>
       <c r="W146" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
@@ -12693,10 +12693,10 @@
         </is>
       </c>
       <c r="Y146" t="n">
-        <v>3.020222668144887</v>
+        <v>5.24420792078758</v>
       </c>
       <c r="Z146" t="n">
-        <v>3.020222668144887</v>
+        <v>5.24420792078758</v>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
@@ -12735,52 +12735,52 @@
         <v>771</v>
       </c>
       <c r="G147" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="H147" t="n">
         <v>3.8</v>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J147" t="n">
-        <v>0.158004158004158</v>
+        <v>0.1649473486776882</v>
       </c>
       <c r="K147" t="n">
-        <v>0.2494802494802495</v>
+        <v>0.2495913828675545</v>
       </c>
       <c r="L147" t="n">
-        <v>0.5925155925155925</v>
+        <v>0.5854612684547574</v>
       </c>
       <c r="M147" t="n">
-        <v>0.05482456140350878</v>
+        <v>0.05435488883238682</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>0.2322024601791497</v>
+        <v>0.2287387667007373</v>
       </c>
       <c r="P147" t="n">
-        <v>0.5231222758917055</v>
+        <v>0.5359146990191095</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.2446752639291447</v>
+        <v>0.2353465342801532</v>
       </c>
       <c r="R147" t="n">
         <v>1</v>
       </c>
       <c r="S147" t="n">
-        <v>0.273642026411456</v>
+        <v>0.286323316151555</v>
       </c>
       <c r="T147" t="n">
         <v>0</v>
       </c>
       <c r="U147" t="n">
-        <v>0.273642026411456</v>
+        <v>0.286323316151555</v>
       </c>
       <c r="V147" t="n">
-        <v>0.5231222758917055</v>
+        <v>0.5359146990191095</v>
       </c>
       <c r="W147" t="n">
         <v>3.8</v>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Y147" t="n">
-        <v>3.530708773348613</v>
+        <v>6.408519536582851</v>
       </c>
       <c r="Z147" t="n">
-        <v>3.530708773348613</v>
+        <v>6.408519536582851</v>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
@@ -12857,28 +12857,28 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>0.2711379192563951</v>
+        <v>0.2725231151948335</v>
       </c>
       <c r="P148" t="n">
-        <v>0.3958014781491829</v>
+        <v>0.3956846156670256</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.3330606025944221</v>
+        <v>0.3317922691381407</v>
       </c>
       <c r="R148" t="n">
         <v>1</v>
       </c>
       <c r="S148" t="n">
-        <v>0.1009831338966516</v>
+        <v>0.1008662714144943</v>
       </c>
       <c r="T148" t="n">
         <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>0.1009831338966516</v>
+        <v>0.1008662714144943</v>
       </c>
       <c r="V148" t="n">
-        <v>0.3958014781491829</v>
+        <v>0.3956846156670256</v>
       </c>
       <c r="W148" t="n">
         <v>3.2</v>
@@ -12889,10 +12889,10 @@
         </is>
       </c>
       <c r="Y148" t="n">
-        <v>2.671382611309341</v>
+        <v>4.731634706920012</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.671382611309341</v>
+        <v>4.731634706920012</v>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
@@ -12955,28 +12955,28 @@
         <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>0.4372196027838811</v>
+        <v>0.4400086634656995</v>
       </c>
       <c r="P149" t="n">
-        <v>0.5004885127723747</v>
+        <v>0.4942897790766149</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.06229188444374419</v>
+        <v>0.06570155745768574</v>
       </c>
       <c r="R149" t="n">
         <v>1</v>
       </c>
       <c r="S149" t="n">
-        <v>0.2237053833631196</v>
+        <v>0.2175066496673598</v>
       </c>
       <c r="T149" t="n">
         <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>0.2237053833631196</v>
+        <v>0.2175066496673598</v>
       </c>
       <c r="V149" t="n">
-        <v>0.5004885127723747</v>
+        <v>0.4942897790766149</v>
       </c>
       <c r="W149" t="n">
         <v>3.4</v>
@@ -12987,10 +12987,10 @@
         </is>
       </c>
       <c r="Y149" t="n">
-        <v>3.377946733377945</v>
+        <v>5.910764738760704</v>
       </c>
       <c r="Z149" t="n">
-        <v>3.377946733377945</v>
+        <v>5.910764738760704</v>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
@@ -13053,28 +13053,28 @@
         <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>0.3446007529713776</v>
+        <v>0.3447548041594359</v>
       </c>
       <c r="P150" t="n">
-        <v>0.3526910107122487</v>
+        <v>0.3527536688143402</v>
       </c>
       <c r="Q150" t="n">
-        <v>0.3027082363163736</v>
+        <v>0.3024915270262238</v>
       </c>
       <c r="R150" t="n">
         <v>1</v>
       </c>
       <c r="S150" t="n">
-        <v>0.05857336365342514</v>
+        <v>0.05863602175551663</v>
       </c>
       <c r="T150" t="n">
         <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>0.05857336365342514</v>
+        <v>0.05863602175551663</v>
       </c>
       <c r="V150" t="n">
-        <v>0.3526910107122487</v>
+        <v>0.3527536688143402</v>
       </c>
       <c r="W150" t="n">
         <v>3.2</v>
@@ -13085,10 +13085,10 @@
         </is>
       </c>
       <c r="Y150" t="n">
-        <v>2.380417166675411</v>
+        <v>4.218262313639893</v>
       </c>
       <c r="Z150" t="n">
-        <v>2.380417166675411</v>
+        <v>4.218262313639893</v>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
@@ -13151,28 +13151,28 @@
         <v>1</v>
       </c>
       <c r="O151" t="n">
-        <v>0.4323588882589248</v>
+        <v>0.4272144406220799</v>
       </c>
       <c r="P151" t="n">
-        <v>0.3773943291766953</v>
+        <v>0.3766028498451762</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.19024678256438</v>
+        <v>0.1961827095327438</v>
       </c>
       <c r="R151" t="n">
         <v>1</v>
       </c>
       <c r="S151" t="n">
-        <v>-0.07893478087621114</v>
+        <v>-0.0840792285130561</v>
       </c>
       <c r="T151" t="n">
         <v>1</v>
       </c>
       <c r="U151" t="n">
-        <v>-0.07893478087621114</v>
+        <v>-0.0840792285130561</v>
       </c>
       <c r="V151" t="n">
-        <v>0.4323588882589248</v>
+        <v>0.4272144406220799</v>
       </c>
       <c r="W151" t="n">
         <v>1.85</v>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Y151" t="n">
-        <v>2.918119511177259</v>
+        <v>5.108671387532308</v>
       </c>
       <c r="Z151" t="n">
-        <v>2.918119511177259</v>
+        <v>5.108671387532308</v>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
@@ -13249,28 +13249,28 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>0.2317021112264667</v>
+        <v>0.2314049743946865</v>
       </c>
       <c r="P152" t="n">
-        <v>0.5192890211216494</v>
+        <v>0.5173633450324683</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.2490088676518839</v>
+        <v>0.2512316805728451</v>
       </c>
       <c r="R152" t="n">
         <v>1</v>
       </c>
       <c r="S152" t="n">
-        <v>0.2317692738862625</v>
+        <v>0.2298435977970813</v>
       </c>
       <c r="T152" t="n">
         <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>0.2317692738862625</v>
+        <v>0.2298435977970813</v>
       </c>
       <c r="V152" t="n">
-        <v>0.5192890211216494</v>
+        <v>0.5173633450324683</v>
       </c>
       <c r="W152" t="n">
         <v>3.3</v>
@@ -13281,10 +13281,10 @@
         </is>
       </c>
       <c r="Y152" t="n">
-        <v>3.504836989884513</v>
+        <v>6.186680660599315</v>
       </c>
       <c r="Z152" t="n">
-        <v>3.504836989884513</v>
+        <v>6.186680660599315</v>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
@@ -13347,28 +13347,28 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>0.2446428108738781</v>
+        <v>0.243982251206936</v>
       </c>
       <c r="P153" t="n">
-        <v>0.492293700379923</v>
+        <v>0.4947117110728264</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.2630634887461987</v>
+        <v>0.2613060377202377</v>
       </c>
       <c r="R153" t="n">
         <v>1</v>
       </c>
       <c r="S153" t="n">
-        <v>0.215697955699072</v>
+        <v>0.2181159663919753</v>
       </c>
       <c r="T153" t="n">
         <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>0.215697955699072</v>
+        <v>0.2181159663919753</v>
       </c>
       <c r="V153" t="n">
-        <v>0.492293700379923</v>
+        <v>0.4947117110728264</v>
       </c>
       <c r="W153" t="n">
         <v>3.4</v>
@@ -13379,10 +13379,10 @@
         </is>
       </c>
       <c r="Y153" t="n">
-        <v>3.322637492415771</v>
+        <v>5.915810242169697</v>
       </c>
       <c r="Z153" t="n">
-        <v>3.322637492415771</v>
+        <v>5.915810242169697</v>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
@@ -13442,34 +13442,34 @@
         <v>0.05900900900900896</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O154" t="n">
-        <v>0.4672142682244892</v>
+        <v>0.4688481526967667</v>
       </c>
       <c r="P154" t="n">
-        <v>0.4687109776100618</v>
+        <v>0.4645031770758087</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.06407475416544899</v>
+        <v>0.06664867022742459</v>
       </c>
       <c r="R154" t="n">
         <v>1</v>
       </c>
       <c r="S154" t="n">
-        <v>0.2326412200600831</v>
+        <v>-0.1691782190599326</v>
       </c>
       <c r="T154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U154" t="n">
-        <v>0.2326412200600831</v>
+        <v>-0.1691782190599326</v>
       </c>
       <c r="V154" t="n">
-        <v>0.4687109776100618</v>
+        <v>0.4688481526967667</v>
       </c>
       <c r="W154" t="n">
-        <v>4</v>
+        <v>1.48</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
@@ -13477,10 +13477,10 @@
         </is>
       </c>
       <c r="Y154" t="n">
-        <v>3.163470639807426</v>
+        <v>5.606531322517188</v>
       </c>
       <c r="Z154" t="n">
-        <v>3.163470639807426</v>
+        <v>5.606531322517188</v>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
@@ -13543,28 +13543,28 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>0.2653946255938225</v>
+        <v>0.2651006284586224</v>
       </c>
       <c r="P155" t="n">
-        <v>0.406166107039758</v>
+        <v>0.406726162603766</v>
       </c>
       <c r="Q155" t="n">
-        <v>0.3284392673664195</v>
+        <v>0.3281732089376114</v>
       </c>
       <c r="R155" t="n">
         <v>1</v>
       </c>
       <c r="S155" t="n">
-        <v>0.149916107039758</v>
+        <v>0.1504761626037661</v>
       </c>
       <c r="T155" t="n">
         <v>0</v>
       </c>
       <c r="U155" t="n">
-        <v>0.149916107039758</v>
+        <v>0.1504761626037661</v>
       </c>
       <c r="V155" t="n">
-        <v>0.406166107039758</v>
+        <v>0.406726162603766</v>
       </c>
       <c r="W155" t="n">
         <v>3.7</v>
@@ -13575,10 +13575,10 @@
         </is>
       </c>
       <c r="Y155" t="n">
-        <v>2.74133659308937</v>
+        <v>4.8636705876072</v>
       </c>
       <c r="Z155" t="n">
-        <v>2.74133659308937</v>
+        <v>4.8636705876072</v>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
@@ -13641,28 +13641,28 @@
         <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>0.4896822687582531</v>
+        <v>0.4889679156451812</v>
       </c>
       <c r="P156" t="n">
-        <v>0.4535486110547644</v>
+        <v>0.4566736230579956</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.05676912018698233</v>
+        <v>0.05435846129682308</v>
       </c>
       <c r="R156" t="n">
         <v>1</v>
       </c>
       <c r="S156" t="n">
-        <v>-0.2215552845845635</v>
+        <v>-0.2222696376976354</v>
       </c>
       <c r="T156" t="n">
         <v>1</v>
       </c>
       <c r="U156" t="n">
-        <v>-0.2215552845845635</v>
+        <v>-0.2222696376976354</v>
       </c>
       <c r="V156" t="n">
-        <v>0.4896822687582531</v>
+        <v>0.4889679156451812</v>
       </c>
       <c r="W156" t="n">
         <v>1.33</v>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Y156" t="n">
-        <v>3.305012158985048</v>
+        <v>5.847125383777921</v>
       </c>
       <c r="Z156" t="n">
-        <v>3.305012158985048</v>
+        <v>5.847125383777921</v>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
@@ -13714,13 +13714,27 @@
       <c r="F157" t="n">
         <v>773</v>
       </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
+      <c r="G157" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H157" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I157" t="n">
+        <v>4</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0.5010684547933092</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0.2696927271387518</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.229238818067939</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0.09056573449051752</v>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
@@ -13732,7 +13746,9 @@
       </c>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
+      <c r="W157" t="n">
+        <v>1.25557461406518</v>
+      </c>
       <c r="X157" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -13776,13 +13792,27 @@
       <c r="F158" t="n">
         <v>773</v>
       </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
+      <c r="G158" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I158" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.2216320651496475</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0.247988310735011</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0.5303796241153415</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0.08985084607100191</v>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
@@ -13794,7 +13824,9 @@
       </c>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
-      <c r="W158" t="inlineStr"/>
+      <c r="W158" t="n">
+        <v>1.220136286201022</v>
+      </c>
       <c r="X158" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -13816,20 +13848,20 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>45508.54166666666</v>
+        <v>45508.64583333334</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>juve stabia</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>avellino</t>
+          <t>padova</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -13838,13 +13870,27 @@
       <c r="F159" t="n">
         <v>773</v>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
+      <c r="G159" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H159" t="n">
+        <v>4</v>
+      </c>
+      <c r="I159" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.6227621063893677</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0.2288650740980926</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0.1483728195125398</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0.09234666313851303</v>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
@@ -13856,7 +13902,9 @@
       </c>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
-      <c r="W159" t="inlineStr"/>
+      <c r="W159" t="n">
+        <v>1.187159685863874</v>
+      </c>
       <c r="X159" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -13878,20 +13926,20 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>45508.64583333334</v>
+        <v>45508.65625</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>avellino</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>padova</t>
+          <t>juve stabia</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -13900,13 +13948,27 @@
       <c r="F160" t="n">
         <v>773</v>
       </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
+      <c r="G160" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.2902468687989416</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.2997631595792349</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.4099899716218234</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0.09375966319287654</v>
+      </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
@@ -13918,7 +13980,9 @@
       </c>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
-      <c r="W160" t="inlineStr"/>
+      <c r="W160" t="n">
+        <v>1.305669144981413</v>
+      </c>
       <c r="X160" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -13973,13 +14037,13 @@
         <v>1</v>
       </c>
       <c r="O161" t="n">
-        <v>0.4714480047822971</v>
+        <v>0.4694967552742121</v>
       </c>
       <c r="P161" t="n">
-        <v>0.4056032949254636</v>
+        <v>0.4042830898537844</v>
       </c>
       <c r="Q161" t="n">
-        <v>0.1229487002922391</v>
+        <v>0.1262201548720035</v>
       </c>
       <c r="R161" t="n">
         <v>1</v>
@@ -13990,7 +14054,7 @@
       </c>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="n">
-        <v>0.5285519952177029</v>
+        <v>0.5305032447257878</v>
       </c>
       <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr">
@@ -13999,10 +14063,10 @@
         </is>
       </c>
       <c r="Y161" t="n">
-        <v>3.567355573809254</v>
+        <v>6.343808845453178</v>
       </c>
       <c r="Z161" t="n">
-        <v>3.567355573809254</v>
+        <v>6.343808845453178</v>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
@@ -14051,13 +14115,13 @@
         <v>1</v>
       </c>
       <c r="O162" t="n">
-        <v>0.474807650426295</v>
+        <v>0.4727240812949189</v>
       </c>
       <c r="P162" t="n">
-        <v>0.4097372930966371</v>
+        <v>0.4071627836349588</v>
       </c>
       <c r="Q162" t="n">
-        <v>0.115455056477068</v>
+        <v>0.1201131350701222</v>
       </c>
       <c r="R162" t="n">
         <v>1</v>
@@ -14068,7 +14132,7 @@
       </c>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="n">
-        <v>0.525192349573705</v>
+        <v>0.5272759187050811</v>
       </c>
       <c r="W162" t="inlineStr"/>
       <c r="X162" t="inlineStr">
@@ -14077,10 +14141,10 @@
         </is>
       </c>
       <c r="Y162" t="n">
-        <v>3.544680320054506</v>
+        <v>6.305216170364257</v>
       </c>
       <c r="Z162" t="n">
-        <v>3.544680320054506</v>
+        <v>6.305216170364257</v>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
@@ -14129,13 +14193,13 @@
         <v>1</v>
       </c>
       <c r="O163" t="n">
-        <v>0.4744099064021176</v>
+        <v>0.4738402187299073</v>
       </c>
       <c r="P163" t="n">
-        <v>0.3974162014452964</v>
+        <v>0.3970833715775151</v>
       </c>
       <c r="Q163" t="n">
-        <v>0.128173892152586</v>
+        <v>0.1290764096925773</v>
       </c>
       <c r="R163" t="n">
         <v>1</v>
@@ -14146,7 +14210,7 @@
       </c>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="n">
-        <v>0.5255900935978823</v>
+        <v>0.5261597812700927</v>
       </c>
       <c r="W163" t="inlineStr"/>
       <c r="X163" t="inlineStr">
@@ -14155,10 +14219,10 @@
         </is>
       </c>
       <c r="Y163" t="n">
-        <v>3.547364813490225</v>
+        <v>6.291869291521921</v>
       </c>
       <c r="Z163" t="n">
-        <v>3.547364813490225</v>
+        <v>6.291869291521921</v>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
@@ -14207,13 +14271,13 @@
         <v>1</v>
       </c>
       <c r="O164" t="n">
-        <v>0.3961073401413146</v>
+        <v>0.3997746834822209</v>
       </c>
       <c r="P164" t="n">
-        <v>0.3802938556685332</v>
+        <v>0.3808697754406668</v>
       </c>
       <c r="Q164" t="n">
-        <v>0.223598804190152</v>
+        <v>0.2193555410771125</v>
       </c>
       <c r="R164" t="n">
         <v>1</v>
@@ -14224,7 +14288,7 @@
       </c>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="n">
-        <v>0.6038926598586853</v>
+        <v>0.6002253165177791</v>
       </c>
       <c r="W164" t="inlineStr"/>
       <c r="X164" t="inlineStr">
@@ -14233,10 +14297,10 @@
         </is>
       </c>
       <c r="Y164" t="n">
-        <v>4.075852263582984</v>
+        <v>7.177552088599557</v>
       </c>
       <c r="Z164" t="n">
-        <v>4.075852263582984</v>
+        <v>7.177552088599557</v>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
@@ -14285,13 +14349,13 @@
         <v>1</v>
       </c>
       <c r="O165" t="n">
-        <v>0.4357604694674418</v>
+        <v>0.4375459700908128</v>
       </c>
       <c r="P165" t="n">
-        <v>0.3721789459378736</v>
+        <v>0.3730150628421344</v>
       </c>
       <c r="Q165" t="n">
-        <v>0.1920605845946844</v>
+        <v>0.1894389670670526</v>
       </c>
       <c r="R165" t="n">
         <v>1</v>
@@ -14302,7 +14366,7 @@
       </c>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="n">
-        <v>0.5642395305325583</v>
+        <v>0.5624540299091871</v>
       </c>
       <c r="W165" t="inlineStr"/>
       <c r="X165" t="inlineStr">
@@ -14311,10 +14375,10 @@
         </is>
       </c>
       <c r="Y165" t="n">
-        <v>3.808221428394718</v>
+        <v>6.725879408980817</v>
       </c>
       <c r="Z165" t="n">
-        <v>3.808221428394718</v>
+        <v>6.725879408980817</v>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
@@ -14363,13 +14427,13 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>0.4748223715979583</v>
+        <v>0.4762256520660549</v>
       </c>
       <c r="P166" t="n">
-        <v>0.4821446094511964</v>
+        <v>0.4803533188099261</v>
       </c>
       <c r="Q166" t="n">
-        <v>0.04303301895084536</v>
+        <v>0.0434210291240188</v>
       </c>
       <c r="R166" t="n">
         <v>1</v>
@@ -14380,7 +14444,7 @@
       </c>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="n">
-        <v>0.5178553905488036</v>
+        <v>0.519646681190074</v>
       </c>
       <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr">
@@ -14389,10 +14453,10 @@
         </is>
       </c>
       <c r="Y166" t="n">
-        <v>3.495160988164534</v>
+        <v>6.213985014074568</v>
       </c>
       <c r="Z166" t="n">
-        <v>3.495160988164534</v>
+        <v>6.213985014074568</v>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
@@ -14441,13 +14505,13 @@
         <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>0.3378760736066398</v>
+        <v>0.3405749389402209</v>
       </c>
       <c r="P167" t="n">
-        <v>0.35690813030224</v>
+        <v>0.3558480852076204</v>
       </c>
       <c r="Q167" t="n">
-        <v>0.3052157960911198</v>
+        <v>0.3035769758521589</v>
       </c>
       <c r="R167" t="n">
         <v>1</v>
@@ -14458,7 +14522,7 @@
       </c>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="n">
-        <v>0.64309186969776</v>
+        <v>0.6441519147923795</v>
       </c>
       <c r="W167" t="inlineStr"/>
       <c r="X167" t="inlineStr">
@@ -14467,10 +14531,10 @@
         </is>
       </c>
       <c r="Y167" t="n">
-        <v>4.34041946032726</v>
+        <v>7.702830577384516</v>
       </c>
       <c r="Z167" t="n">
-        <v>4.34041946032726</v>
+        <v>7.702830577384516</v>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
@@ -14519,13 +14583,13 @@
         <v>1</v>
       </c>
       <c r="O168" t="n">
-        <v>0.406988013196621</v>
+        <v>0.403847330668933</v>
       </c>
       <c r="P168" t="n">
-        <v>0.3644240071799103</v>
+        <v>0.3641302640579551</v>
       </c>
       <c r="Q168" t="n">
-        <v>0.2285879796234687</v>
+        <v>0.232022405273112</v>
       </c>
       <c r="R168" t="n">
         <v>1</v>
@@ -14536,7 +14600,7 @@
       </c>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="n">
-        <v>0.593011986803379</v>
+        <v>0.596152669331067</v>
       </c>
       <c r="W168" t="inlineStr"/>
       <c r="X168" t="inlineStr">
@@ -14545,10 +14609,10 @@
         </is>
       </c>
       <c r="Y168" t="n">
-        <v>4.002415345319804</v>
+        <v>7.128850981670743</v>
       </c>
       <c r="Z168" t="n">
-        <v>4.002415345319804</v>
+        <v>7.128850981670743</v>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
@@ -14597,13 +14661,13 @@
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>0.3694937315310033</v>
+        <v>0.3742469639595186</v>
       </c>
       <c r="P169" t="n">
-        <v>0.3732029792473935</v>
+        <v>0.3749425523620097</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.2573032892216031</v>
+        <v>0.2508104836784718</v>
       </c>
       <c r="R169" t="n">
         <v>1</v>
@@ -14614,7 +14678,7 @@
       </c>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="n">
-        <v>0.6267970207526066</v>
+        <v>0.6250574476379902</v>
       </c>
       <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr">
@@ -14623,10 +14687,10 @@
         </is>
       </c>
       <c r="Y169" t="n">
-        <v>4.230440648905065</v>
+        <v>7.474497101882698</v>
       </c>
       <c r="Z169" t="n">
-        <v>4.230440648905065</v>
+        <v>7.474497101882698</v>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
@@ -14675,13 +14739,13 @@
         <v>1</v>
       </c>
       <c r="O170" t="n">
-        <v>0.4733371806917877</v>
+        <v>0.4739942378041332</v>
       </c>
       <c r="P170" t="n">
-        <v>0.4239851741582934</v>
+        <v>0.422798329895286</v>
       </c>
       <c r="Q170" t="n">
-        <v>0.1026776451499188</v>
+        <v>0.1032074323005807</v>
       </c>
       <c r="R170" t="n">
         <v>1</v>
@@ -14692,7 +14756,7 @@
       </c>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="n">
-        <v>0.5266628193082123</v>
+        <v>0.5260057621958667</v>
       </c>
       <c r="W170" t="inlineStr"/>
       <c r="X170" t="inlineStr">
@@ -14701,10 +14765,10 @@
         </is>
       </c>
       <c r="Y170" t="n">
-        <v>3.554604960299884</v>
+        <v>6.290027516612613</v>
       </c>
       <c r="Z170" t="n">
-        <v>3.554604960299884</v>
+        <v>6.290027516612613</v>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
@@ -14753,13 +14817,13 @@
         <v>1</v>
       </c>
       <c r="O171" t="n">
-        <v>0.4238880895081383</v>
+        <v>0.4214803559717588</v>
       </c>
       <c r="P171" t="n">
-        <v>0.3826738469226045</v>
+        <v>0.3823090013622199</v>
       </c>
       <c r="Q171" t="n">
-        <v>0.1934380635692574</v>
+        <v>0.196210642666021</v>
       </c>
       <c r="R171" t="n">
         <v>1</v>
@@ -14770,7 +14834,7 @@
       </c>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="n">
-        <v>0.5761119104918617</v>
+        <v>0.5785196440282412</v>
       </c>
       <c r="W171" t="inlineStr"/>
       <c r="X171" t="inlineStr">
@@ -14779,10 +14843,10 @@
         </is>
       </c>
       <c r="Y171" t="n">
-        <v>3.88835167330044</v>
+        <v>6.917993568449856</v>
       </c>
       <c r="Z171" t="n">
-        <v>3.88835167330044</v>
+        <v>6.917993568449856</v>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
@@ -14831,13 +14895,13 @@
         <v>1</v>
       </c>
       <c r="O172" t="n">
-        <v>0.4544331171342493</v>
+        <v>0.4455732802592645</v>
       </c>
       <c r="P172" t="n">
-        <v>0.3913317838444145</v>
+        <v>0.3852067815535028</v>
       </c>
       <c r="Q172" t="n">
-        <v>0.1542350990213361</v>
+        <v>0.1692199381872326</v>
       </c>
       <c r="R172" t="n">
         <v>1</v>
@@ -14848,7 +14912,7 @@
       </c>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="n">
-        <v>0.5455668828657507</v>
+        <v>0.5544267197407355</v>
       </c>
       <c r="W172" t="inlineStr"/>
       <c r="X172" t="inlineStr">
@@ -14857,10 +14921,10 @@
         </is>
       </c>
       <c r="Y172" t="n">
-        <v>3.682194141893745</v>
+        <v>6.629888061598689</v>
       </c>
       <c r="Z172" t="n">
-        <v>3.682194141893745</v>
+        <v>6.629888061598689</v>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
@@ -14923,28 +14987,28 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>0.3380679964157302</v>
+        <v>0.3388659580677731</v>
       </c>
       <c r="P173" t="n">
-        <v>0.3740222378372361</v>
+        <v>0.3746946149815555</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.2879097657470336</v>
+        <v>0.2864394269506713</v>
       </c>
       <c r="R173" t="n">
         <v>1</v>
       </c>
       <c r="S173" t="n">
-        <v>0.08333192751424695</v>
+        <v>0.08400430465856634</v>
       </c>
       <c r="T173" t="n">
         <v>0</v>
       </c>
       <c r="U173" t="n">
-        <v>0.08333192751424695</v>
+        <v>0.08400430465856634</v>
       </c>
       <c r="V173" t="n">
-        <v>0.3740222378372361</v>
+        <v>0.3746946149815555</v>
       </c>
       <c r="W173" t="n">
         <v>3.2</v>
@@ -14955,10 +15019,10 @@
         </is>
       </c>
       <c r="Y173" t="n">
-        <v>2.524388001463713</v>
+        <v>4.480634259065295</v>
       </c>
       <c r="Z173" t="n">
-        <v>2.524388001463713</v>
+        <v>4.480634259065295</v>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
@@ -15101,28 +15165,28 @@
         <v>1</v>
       </c>
       <c r="O175" t="n">
-        <v>0.3790586940833662</v>
+        <v>0.3771596572542751</v>
       </c>
       <c r="P175" t="n">
-        <v>0.3715543510497629</v>
+        <v>0.3703923812577244</v>
       </c>
       <c r="Q175" t="n">
-        <v>0.2493869548668708</v>
+        <v>0.2524479614880006</v>
       </c>
       <c r="R175" t="n">
         <v>1</v>
       </c>
       <c r="S175" t="n">
-        <v>0.00735858848674531</v>
+        <v>0.00545955165765416</v>
       </c>
       <c r="T175" t="n">
         <v>1</v>
       </c>
       <c r="U175" t="n">
-        <v>0.00735858848674531</v>
+        <v>0.00545955165765416</v>
       </c>
       <c r="V175" t="n">
-        <v>0.3790586940833662</v>
+        <v>0.3771596572542751</v>
       </c>
       <c r="W175" t="n">
         <v>2.5</v>
@@ -15133,10 +15197,10 @@
         </is>
       </c>
       <c r="Y175" t="n">
-        <v>2.55838055172261</v>
+        <v>4.510111471748842</v>
       </c>
       <c r="Z175" t="n">
-        <v>2.55838055172261</v>
+        <v>4.510111471748842</v>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
@@ -15199,28 +15263,28 @@
         <v>1</v>
       </c>
       <c r="O176" t="n">
-        <v>0.4583076869532984</v>
+        <v>0.451102352483415</v>
       </c>
       <c r="P176" t="n">
-        <v>0.3950426087473192</v>
+        <v>0.3894999314195416</v>
       </c>
       <c r="Q176" t="n">
-        <v>0.146649704299382</v>
+        <v>0.1593977160970436</v>
       </c>
       <c r="R176" t="n">
         <v>1</v>
       </c>
       <c r="S176" t="n">
-        <v>-0.04557375270795772</v>
+        <v>-0.05277908717784108</v>
       </c>
       <c r="T176" t="n">
         <v>1</v>
       </c>
       <c r="U176" t="n">
-        <v>-0.04557375270795772</v>
+        <v>-0.05277908717784108</v>
       </c>
       <c r="V176" t="n">
-        <v>0.4583076869532984</v>
+        <v>0.451102352483415</v>
       </c>
       <c r="W176" t="n">
         <v>1.85</v>
@@ -15231,10 +15295,10 @@
         </is>
       </c>
       <c r="Y176" t="n">
-        <v>3.09325571819867</v>
+        <v>5.394325336065033</v>
       </c>
       <c r="Z176" t="n">
-        <v>3.09325571819867</v>
+        <v>5.394325336065033</v>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
@@ -15297,28 +15361,28 @@
         <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>0.3614264383835507</v>
+        <v>0.3613841827993978</v>
       </c>
       <c r="P177" t="n">
-        <v>0.3743785460922382</v>
+        <v>0.3730405837229831</v>
       </c>
       <c r="Q177" t="n">
-        <v>0.2641950155242111</v>
+        <v>0.265575233477619</v>
       </c>
       <c r="R177" t="n">
         <v>1</v>
       </c>
       <c r="S177" t="n">
-        <v>0.0718963729883717</v>
+        <v>0.07055841061911661</v>
       </c>
       <c r="T177" t="n">
         <v>0</v>
       </c>
       <c r="U177" t="n">
-        <v>0.0718963729883717</v>
+        <v>0.07055841061911661</v>
       </c>
       <c r="V177" t="n">
-        <v>0.3743785460922382</v>
+        <v>0.3730405837229831</v>
       </c>
       <c r="W177" t="n">
         <v>3.1</v>
@@ -15329,10 +15393,10 @@
         </is>
       </c>
       <c r="Y177" t="n">
-        <v>2.526792832494484</v>
+        <v>4.460855194124398</v>
       </c>
       <c r="Z177" t="n">
-        <v>2.526792832494484</v>
+        <v>4.460855194124398</v>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
@@ -15395,28 +15459,28 @@
         <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>0.3082132045474411</v>
+        <v>0.310221098231573</v>
       </c>
       <c r="P178" t="n">
-        <v>0.359684229508581</v>
+        <v>0.357962016962774</v>
       </c>
       <c r="Q178" t="n">
-        <v>0.3321025659439781</v>
+        <v>0.3318168848056527</v>
       </c>
       <c r="R178" t="n">
         <v>1</v>
       </c>
       <c r="S178" t="n">
-        <v>0.06929352201122096</v>
+        <v>0.06757130946541395</v>
       </c>
       <c r="T178" t="n">
         <v>0</v>
       </c>
       <c r="U178" t="n">
-        <v>0.06929352201122096</v>
+        <v>0.06757130946541395</v>
       </c>
       <c r="V178" t="n">
-        <v>0.359684229508581</v>
+        <v>0.357962016962774</v>
       </c>
       <c r="W178" t="n">
         <v>3.2</v>
@@ -15427,10 +15491,10 @@
         </is>
       </c>
       <c r="Y178" t="n">
-        <v>2.427616492905725</v>
+        <v>4.280544241946123</v>
       </c>
       <c r="Z178" t="n">
-        <v>2.427616492905725</v>
+        <v>4.280544241946123</v>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
@@ -15571,28 +15635,28 @@
         <v>0</v>
       </c>
       <c r="O180" t="n">
-        <v>0.3272688283754523</v>
+        <v>0.3271006089805857</v>
       </c>
       <c r="P180" t="n">
-        <v>0.3746482331421275</v>
+        <v>0.3762116784915401</v>
       </c>
       <c r="Q180" t="n">
-        <v>0.2980829384824198</v>
+        <v>0.2966877125278745</v>
       </c>
       <c r="R180" t="n">
         <v>1</v>
       </c>
       <c r="S180" t="n">
-        <v>0.0851745489316012</v>
+        <v>0.08673799428101381</v>
       </c>
       <c r="T180" t="n">
         <v>0</v>
       </c>
       <c r="U180" t="n">
-        <v>0.0851745489316012</v>
+        <v>0.08673799428101381</v>
       </c>
       <c r="V180" t="n">
-        <v>0.3746482331421275</v>
+        <v>0.3762116784915401</v>
       </c>
       <c r="W180" t="n">
         <v>3.2</v>
@@ -15603,10 +15667,10 @@
         </is>
       </c>
       <c r="Y180" t="n">
-        <v>2.528613031092374</v>
+        <v>4.498775450489541</v>
       </c>
       <c r="Z180" t="n">
-        <v>2.528613031092374</v>
+        <v>4.498775450489541</v>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
@@ -15666,34 +15730,34 @@
         <v>0.07613636363636367</v>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>0.3943496459569794</v>
+        <v>0.3792582472531151</v>
       </c>
       <c r="P181" t="n">
-        <v>0.3799057602844827</v>
+        <v>0.3804626357347388</v>
       </c>
       <c r="Q181" t="n">
-        <v>0.2257445937585379</v>
+        <v>0.2402791170121459</v>
       </c>
       <c r="R181" t="n">
         <v>1</v>
       </c>
       <c r="S181" t="n">
-        <v>0.02264954036035843</v>
+        <v>0.09007192823737875</v>
       </c>
       <c r="T181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U181" t="n">
-        <v>0.02264954036035843</v>
+        <v>0.09007192823737875</v>
       </c>
       <c r="V181" t="n">
-        <v>0.3943496459569794</v>
+        <v>0.3804626357347388</v>
       </c>
       <c r="W181" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
@@ -15701,10 +15765,10 @@
         </is>
       </c>
       <c r="Y181" t="n">
-        <v>2.661583761413864</v>
+        <v>4.549608806230817</v>
       </c>
       <c r="Z181" t="n">
-        <v>2.661583761413864</v>
+        <v>4.549608806230817</v>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
@@ -15844,45 +15908,45 @@
         <v>0.06108374384236459</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O183" t="n">
-        <v>0.3674867332397739</v>
+        <v>0.3543207301500569</v>
       </c>
       <c r="P183" t="n">
-        <v>0.3843011769385412</v>
+        <v>0.3309504969275024</v>
       </c>
       <c r="Q183" t="n">
-        <v>0.2482120898216849</v>
+        <v>0.3147287729224407</v>
       </c>
       <c r="R183" t="n">
         <v>1</v>
       </c>
       <c r="S183" t="n">
-        <v>0.1599124428005034</v>
+        <v>-0.2956328445946042</v>
       </c>
       <c r="T183" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U183" t="n">
-        <v>0.1599124428005034</v>
+        <v>0.2956328445946042</v>
       </c>
       <c r="V183" t="n">
-        <v>0.3843011769385412</v>
+        <v>0.6456792698499432</v>
       </c>
       <c r="W183" t="n">
-        <v>4.2</v>
+        <v>2.692307692307693</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="Y183" t="n">
-        <v>7.863766199583208</v>
+        <v>9.885606821282982</v>
       </c>
       <c r="Z183" t="n">
-        <v>7.863766199583208</v>
+        <v>9.885606821282982</v>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
@@ -15921,66 +15985,66 @@
         <v>1481</v>
       </c>
       <c r="G184" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="H184" t="n">
         <v>3.4</v>
       </c>
       <c r="I184" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="J184" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.3781597573306371</v>
       </c>
       <c r="K184" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2780586450960567</v>
       </c>
       <c r="L184" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.3437815975733064</v>
       </c>
       <c r="M184" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.05775401069518704</v>
       </c>
       <c r="N184" t="n">
         <v>0</v>
       </c>
       <c r="O184" t="n">
-        <v>0.2977685999675609</v>
+        <v>0.3450016956237524</v>
       </c>
       <c r="P184" t="n">
-        <v>0.3540569072701464</v>
+        <v>0.371402254382207</v>
       </c>
       <c r="Q184" t="n">
-        <v>0.3481744927622927</v>
+        <v>0.2835960499940407</v>
       </c>
       <c r="R184" t="n">
         <v>1</v>
       </c>
       <c r="S184" t="n">
-        <v>0.07570639180622885</v>
+        <v>0.09334360928615032</v>
       </c>
       <c r="T184" t="n">
         <v>0</v>
       </c>
       <c r="U184" t="n">
-        <v>0.07570639180622885</v>
+        <v>0.09334360928615032</v>
       </c>
       <c r="V184" t="n">
-        <v>0.3540569072701464</v>
+        <v>0.371402254382207</v>
       </c>
       <c r="W184" t="n">
         <v>3.4</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y184" t="n">
-        <v>7.244892566553878</v>
+        <v>5.686316458965599</v>
       </c>
       <c r="Z184" t="n">
-        <v>7.244892566553878</v>
+        <v>5.686316458965599</v>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
@@ -16043,42 +16107,42 @@
         <v>0</v>
       </c>
       <c r="O185" t="n">
-        <v>0.3644976060688948</v>
+        <v>0.2917897629546954</v>
       </c>
       <c r="P185" t="n">
-        <v>0.3876858851927056</v>
+        <v>0.3558658345862208</v>
       </c>
       <c r="Q185" t="n">
-        <v>0.2478165087383996</v>
+        <v>0.3523444024590837</v>
       </c>
       <c r="R185" t="n">
         <v>1</v>
       </c>
       <c r="S185" t="n">
-        <v>0.1017416791841219</v>
+        <v>0.06992162857763712</v>
       </c>
       <c r="T185" t="n">
         <v>0</v>
       </c>
       <c r="U185" t="n">
-        <v>0.1017416791841219</v>
+        <v>0.06992162857763712</v>
       </c>
       <c r="V185" t="n">
-        <v>0.3876858851927056</v>
+        <v>0.3558658345862208</v>
       </c>
       <c r="W185" t="n">
         <v>3.3</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y185" t="n">
-        <v>7.933025821884092</v>
+        <v>5.448447683111589</v>
       </c>
       <c r="Z185" t="n">
-        <v>7.933025821884092</v>
+        <v>5.448447683111589</v>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
@@ -16141,42 +16205,42 @@
         <v>2</v>
       </c>
       <c r="O186" t="n">
-        <v>0.2490802893171681</v>
+        <v>0.1663911399929355</v>
       </c>
       <c r="P186" t="n">
-        <v>0.3653293906011599</v>
+        <v>0.3464497059716086</v>
       </c>
       <c r="Q186" t="n">
-        <v>0.3855903200816719</v>
+        <v>0.4871591540354559</v>
       </c>
       <c r="R186" t="n">
         <v>1</v>
       </c>
       <c r="S186" t="n">
-        <v>0.02347897733322735</v>
+        <v>0.1250478112870113</v>
       </c>
       <c r="T186" t="n">
         <v>2</v>
       </c>
       <c r="U186" t="n">
-        <v>0.02347897733322735</v>
+        <v>0.1250478112870113</v>
       </c>
       <c r="V186" t="n">
-        <v>0.3855903200816719</v>
+        <v>0.4871591540354559</v>
       </c>
       <c r="W186" t="n">
         <v>2.63</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y186" t="n">
-        <v>7.890145302442416</v>
+        <v>7.458600703260249</v>
       </c>
       <c r="Z186" t="n">
-        <v>7.890145302442416</v>
+        <v>7.458600703260249</v>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
@@ -16235,29 +16299,47 @@
       <c r="M187" t="n">
         <v>0.05842972440212746</v>
       </c>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
+      <c r="N187" t="n">
+        <v>1</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0.4014381059865235</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0.3129428747972791</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0.2856190192161973</v>
+      </c>
       <c r="R187" t="n">
         <v>1</v>
       </c>
-      <c r="S187" t="inlineStr"/>
+      <c r="S187" t="n">
+        <v>-0.1643079056797918</v>
+      </c>
       <c r="T187" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="U187" t="n">
+        <v>0.1643079056797918</v>
+      </c>
+      <c r="V187" t="n">
+        <v>0.5985618940134765</v>
+      </c>
       <c r="W187" t="n">
-        <v>1.294137466307278</v>
+        <v>2.175675675675676</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr"/>
-      <c r="Z187" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y187" t="n">
+        <v>9.164221028491188</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>9.164221028491188</v>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>spain</t>
@@ -16319,42 +16401,42 @@
         <v>2</v>
       </c>
       <c r="O188" t="n">
-        <v>0.1911693611669979</v>
+        <v>0.08782328920802665</v>
       </c>
       <c r="P188" t="n">
-        <v>0.3333557197207141</v>
+        <v>0.3046577231035404</v>
       </c>
       <c r="Q188" t="n">
-        <v>0.475474919112288</v>
+        <v>0.6075189876884329</v>
       </c>
       <c r="R188" t="n">
         <v>1</v>
       </c>
       <c r="S188" t="n">
-        <v>-0.06523654333830486</v>
+        <v>0.06680752523784006</v>
       </c>
       <c r="T188" t="n">
         <v>2</v>
       </c>
       <c r="U188" t="n">
-        <v>-0.06523654333830486</v>
+        <v>0.06680752523784006</v>
       </c>
       <c r="V188" t="n">
-        <v>0.475474919112288</v>
+        <v>0.6075189876884329</v>
       </c>
       <c r="W188" t="n">
         <v>1.75</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y188" t="n">
-        <v>9.729409697495484</v>
+        <v>9.301357700623464</v>
       </c>
       <c r="Z188" t="n">
-        <v>9.729409697495484</v>
+        <v>9.301357700623464</v>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
@@ -16417,42 +16499,42 @@
         <v>1</v>
       </c>
       <c r="O189" t="n">
-        <v>0.4260256512288893</v>
+        <v>0.5528953169629541</v>
       </c>
       <c r="P189" t="n">
-        <v>0.3704826390791036</v>
+        <v>0.2831583750474474</v>
       </c>
       <c r="Q189" t="n">
-        <v>0.2034917096920073</v>
+        <v>0.1639463079895984</v>
       </c>
       <c r="R189" t="n">
         <v>1</v>
       </c>
       <c r="S189" t="n">
-        <v>-0.1847649833147144</v>
+        <v>-0.05789531758064959</v>
       </c>
       <c r="T189" t="n">
         <v>1</v>
       </c>
       <c r="U189" t="n">
-        <v>-0.1847649833147144</v>
+        <v>-0.05789531758064959</v>
       </c>
       <c r="V189" t="n">
-        <v>0.4260256512288893</v>
+        <v>0.5528953169629541</v>
       </c>
       <c r="W189" t="n">
         <v>1.55</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y189" t="n">
-        <v>8.717553620255851</v>
+        <v>8.465047543023386</v>
       </c>
       <c r="Z189" t="n">
-        <v>8.717553620255851</v>
+        <v>8.465047543023386</v>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
@@ -16515,42 +16597,42 @@
         <v>2</v>
       </c>
       <c r="O190" t="n">
-        <v>0.137404684861135</v>
+        <v>0.08103257282901304</v>
       </c>
       <c r="P190" t="n">
-        <v>0.3356936919426209</v>
+        <v>0.2903271265316048</v>
       </c>
       <c r="Q190" t="n">
-        <v>0.5269016231962442</v>
+        <v>0.6286403006393823</v>
       </c>
       <c r="R190" t="n">
         <v>1</v>
       </c>
       <c r="S190" t="n">
-        <v>-0.07123405779805936</v>
+        <v>0.03050461964507867</v>
       </c>
       <c r="T190" t="n">
         <v>2</v>
       </c>
       <c r="U190" t="n">
-        <v>-0.07123405779805936</v>
+        <v>0.03050461964507867</v>
       </c>
       <c r="V190" t="n">
-        <v>0.5269016231962442</v>
+        <v>0.6286403006393823</v>
       </c>
       <c r="W190" t="n">
         <v>1.6</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y190" t="n">
-        <v>10.78172908031137</v>
+        <v>9.624733415366299</v>
       </c>
       <c r="Z190" t="n">
-        <v>10.78172908031137</v>
+        <v>9.624733415366299</v>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
@@ -16609,29 +16691,47 @@
       <c r="M191" t="n">
         <v>0.051747311827957</v>
       </c>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
+      <c r="N191" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0.3609999082839134</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0.3275469899490511</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0.3114531017670354</v>
+      </c>
       <c r="R191" t="n">
         <v>1</v>
       </c>
-      <c r="S191" t="inlineStr"/>
+      <c r="S191" t="n">
+        <v>-0.03516622590139018</v>
+      </c>
       <c r="T191" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U191" t="inlineStr"/>
-      <c r="V191" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U191" t="n">
+        <v>-0.03516622590139018</v>
+      </c>
+      <c r="V191" t="n">
+        <v>0.3609999082839134</v>
+      </c>
       <c r="W191" t="n">
-        <v>1.371428571428572</v>
+        <v>2.4</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr"/>
-      <c r="Z191" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y191" t="n">
+        <v>5.52705239653018</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>5.52705239653018</v>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>spain</t>
@@ -16669,66 +16769,66 @@
         <v>1481</v>
       </c>
       <c r="G192" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H192" t="n">
         <v>3.4</v>
       </c>
       <c r="I192" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="J192" t="n">
-        <v>0.3308443879577409</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="K192" t="n">
-        <v>0.2802446580347923</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="L192" t="n">
-        <v>0.3889109540074668</v>
+        <v>0.3947157726180944</v>
       </c>
       <c r="M192" t="n">
-        <v>0.04950313458716815</v>
+        <v>0.05561189993238691</v>
       </c>
       <c r="N192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>0.2360303609118284</v>
+        <v>0.2799751019411993</v>
       </c>
       <c r="P192" t="n">
-        <v>0.3436490407035404</v>
+        <v>0.364827133816587</v>
       </c>
       <c r="Q192" t="n">
-        <v>0.4203205983846311</v>
+        <v>0.3551977642422137</v>
       </c>
       <c r="R192" t="n">
         <v>1</v>
       </c>
       <c r="S192" t="n">
-        <v>0.03140964437716431</v>
+        <v>0.0862042354979321</v>
       </c>
       <c r="T192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U192" t="n">
-        <v>0.03140964437716431</v>
+        <v>0.0862042354979321</v>
       </c>
       <c r="V192" t="n">
-        <v>0.4203205983846311</v>
+        <v>0.364827133816587</v>
       </c>
       <c r="W192" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y192" t="n">
-        <v>8.600813926453956</v>
+        <v>5.585648743972431</v>
       </c>
       <c r="Z192" t="n">
-        <v>8.600813926453956</v>
+        <v>5.585648743972431</v>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
@@ -16777,13 +16877,13 @@
         <v>2</v>
       </c>
       <c r="O193" t="n">
-        <v>0.3380006120789301</v>
+        <v>0.1838937751487623</v>
       </c>
       <c r="P193" t="n">
-        <v>0.2429502572775514</v>
+        <v>0.2459078968870776</v>
       </c>
       <c r="Q193" t="n">
-        <v>0.4190491306435185</v>
+        <v>0.57019832796416</v>
       </c>
       <c r="R193" t="n">
         <v>1</v>
@@ -16794,19 +16894,19 @@
       </c>
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="n">
-        <v>0.5809508693564815</v>
+        <v>0.42980167203584</v>
       </c>
       <c r="W193" t="inlineStr"/>
       <c r="X193" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="Y193" t="n">
-        <v>11.88771225333662</v>
+        <v>6.580434806066749</v>
       </c>
       <c r="Z193" t="n">
-        <v>11.88771225333662</v>
+        <v>6.580434806066749</v>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
@@ -16855,13 +16955,13 @@
         <v>1</v>
       </c>
       <c r="O194" t="n">
-        <v>0.3970849127278552</v>
+        <v>0.7540168523407008</v>
       </c>
       <c r="P194" t="n">
-        <v>0.2458736909589887</v>
+        <v>0.131951511035547</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.3570413963131561</v>
+        <v>0.1140316366237523</v>
       </c>
       <c r="R194" t="n">
         <v>1</v>
@@ -16872,19 +16972,19 @@
       </c>
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="n">
-        <v>0.6029150872721448</v>
+        <v>0.2459831476592992</v>
       </c>
       <c r="W194" t="inlineStr"/>
       <c r="X194" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="Y194" t="n">
-        <v>12.33715525484243</v>
+        <v>3.766099975590909</v>
       </c>
       <c r="Z194" t="n">
-        <v>12.33715525484243</v>
+        <v>3.766099975590909</v>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
